--- a/Таблица сигналов.xlsx
+++ b/Таблица сигналов.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\SW002-LoadWizardPro_v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96284840-3357-44F0-BABF-94BAB1291D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F12DB8B4-A72F-499C-BAD9-DABF7CC9BB16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3432" yWindow="2424" windowWidth="17280" windowHeight="8832" xr2:uid="{0F8F6BBE-EBD7-4FEB-A239-792B86B6C8F6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0F8F6BBE-EBD7-4FEB-A239-792B86B6C8F6}"/>
   </bookViews>
   <sheets>
     <sheet name="IO ПЛК" sheetId="1" r:id="rId1"/>
     <sheet name="Fieldbus Робот" sheetId="2" r:id="rId2"/>
     <sheet name="Recipe Data" sheetId="5" r:id="rId3"/>
     <sheet name="Task Data" sheetId="4" r:id="rId4"/>
+    <sheet name="Error list" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="505">
   <si>
     <t>Комментарий</t>
   </si>
@@ -1479,13 +1480,90 @@
   </si>
   <si>
     <t>Режим Slow Repeat</t>
+  </si>
+  <si>
+    <t>Столбец1</t>
+  </si>
+  <si>
+    <t>Что сначала: открытие захвата или закрытие патрона
+0 - Открытие захвата первое
+1 - Закрытие патрона первое</t>
+  </si>
+  <si>
+    <t>Проверка датчиков открытия захвата</t>
+  </si>
+  <si>
+    <t>Код ошибки на роботе</t>
+  </si>
+  <si>
+    <t>Робот выключён</t>
+  </si>
+  <si>
+    <t>Давление воздуха отсутствует</t>
+  </si>
+  <si>
+    <t>Станок не готов к работе</t>
+  </si>
+  <si>
+    <t>Ошибка открытия полки</t>
+  </si>
+  <si>
+    <t>Error</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>P10001</t>
+  </si>
+  <si>
+    <t>Робот не готов</t>
+  </si>
+  <si>
+    <t>-P10003</t>
+  </si>
+  <si>
+    <t>P10004</t>
+  </si>
+  <si>
+    <t>P10005</t>
+  </si>
+  <si>
+    <t>-P10008</t>
+  </si>
+  <si>
+    <t>P1000B</t>
+  </si>
+  <si>
+    <t>P10009</t>
+  </si>
+  <si>
+    <t>P10012</t>
+  </si>
+  <si>
+    <t>P10032</t>
+  </si>
+  <si>
+    <t>-M00015</t>
+  </si>
+  <si>
+    <t>-M00030</t>
+  </si>
+  <si>
+    <t>M00138</t>
+  </si>
+  <si>
+    <t>P10003</t>
+  </si>
+  <si>
+    <t>P10008</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1524,7 +1602,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1541,6 +1619,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1585,7 +1669,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1619,11 +1703,19 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="58">
+  <dxfs count="59">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2435,124 +2527,125 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4FB99795-03B0-4E22-9C96-6842392B5901}" name="Таблица1" displayName="Таблица1" ref="A2:D18" totalsRowShown="0" headerRowDxfId="57" dataDxfId="56">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4FB99795-03B0-4E22-9C96-6842392B5901}" name="Таблица1" displayName="Таблица1" ref="A2:D18" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
   <autoFilter ref="A2:D18" xr:uid="{4FB99795-03B0-4E22-9C96-6842392B5901}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{7C2C7D8A-BD32-4120-BC88-EB134B0B60DA}" name="Физический адрес" dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{58BE04DE-C552-4F0B-8C7F-718DD4C443F7}" name="FORCE-адрес" dataDxfId="54"/>
-    <tableColumn id="3" xr3:uid="{C505C174-C638-47F1-BB97-D9759397B15D}" name="Программный адрес" dataDxfId="53"/>
-    <tableColumn id="4" xr3:uid="{ED8AA96B-A477-464A-A575-B0EC13A66BB1}" name="Комментарий" dataDxfId="52"/>
+    <tableColumn id="1" xr3:uid="{7C2C7D8A-BD32-4120-BC88-EB134B0B60DA}" name="Физический адрес" dataDxfId="56"/>
+    <tableColumn id="2" xr3:uid="{58BE04DE-C552-4F0B-8C7F-718DD4C443F7}" name="FORCE-адрес" dataDxfId="55"/>
+    <tableColumn id="3" xr3:uid="{C505C174-C638-47F1-BB97-D9759397B15D}" name="Программный адрес" dataDxfId="54"/>
+    <tableColumn id="4" xr3:uid="{ED8AA96B-A477-464A-A575-B0EC13A66BB1}" name="Комментарий" dataDxfId="53"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FA992103-97BB-4814-9335-4CEC99149701}" name="Таблица13" displayName="Таблица13" ref="F2:I18" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FA992103-97BB-4814-9335-4CEC99149701}" name="Таблица13" displayName="Таблица13" ref="F2:I18" totalsRowShown="0" headerRowDxfId="52" dataDxfId="51">
   <autoFilter ref="F2:I18" xr:uid="{FA992103-97BB-4814-9335-4CEC99149701}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{15E45CAB-51EB-4A75-90C9-CC44510A3E87}" name="Физический адрес" dataDxfId="49"/>
-    <tableColumn id="2" xr3:uid="{84700D99-E881-4E94-9044-61BD4F52065D}" name="FORCE-адрес" dataDxfId="48"/>
-    <tableColumn id="3" xr3:uid="{29C8761B-51E9-4932-B7ED-5626F8D910F1}" name="Программный адрес" dataDxfId="47"/>
-    <tableColumn id="4" xr3:uid="{07C2B09C-9E2B-4C86-8326-BFEBEDA30C7D}" name="Комментарий" dataDxfId="46"/>
+    <tableColumn id="1" xr3:uid="{15E45CAB-51EB-4A75-90C9-CC44510A3E87}" name="Физический адрес" dataDxfId="50"/>
+    <tableColumn id="2" xr3:uid="{84700D99-E881-4E94-9044-61BD4F52065D}" name="FORCE-адрес" dataDxfId="49"/>
+    <tableColumn id="3" xr3:uid="{29C8761B-51E9-4932-B7ED-5626F8D910F1}" name="Программный адрес" dataDxfId="48"/>
+    <tableColumn id="4" xr3:uid="{07C2B09C-9E2B-4C86-8326-BFEBEDA30C7D}" name="Комментарий" dataDxfId="47"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3DEB932C-F543-45DC-9FB9-1947721EC368}" name="Таблица14" displayName="Таблица14" ref="A21:D37" totalsRowShown="0" headerRowDxfId="45" dataDxfId="44">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3DEB932C-F543-45DC-9FB9-1947721EC368}" name="Таблица14" displayName="Таблица14" ref="A21:D37" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
   <autoFilter ref="A21:D37" xr:uid="{3DEB932C-F543-45DC-9FB9-1947721EC368}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{A7DD1111-3E4E-43E7-B963-E5371285786B}" name="Физический адрес" dataDxfId="43"/>
-    <tableColumn id="2" xr3:uid="{4E5A1EC3-7FCE-49BB-9C77-73886071420D}" name="FORCE-адрес" dataDxfId="42"/>
-    <tableColumn id="3" xr3:uid="{0D714DBB-8CDC-4AF9-A4A1-3CF9A9D9BE08}" name="Программный адрес" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{69F5BC8C-DEF4-48C0-9AF3-231A7A2B3763}" name="Комментарий" dataDxfId="40"/>
+    <tableColumn id="1" xr3:uid="{A7DD1111-3E4E-43E7-B963-E5371285786B}" name="Физический адрес" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{4E5A1EC3-7FCE-49BB-9C77-73886071420D}" name="FORCE-адрес" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{0D714DBB-8CDC-4AF9-A4A1-3CF9A9D9BE08}" name="Программный адрес" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{69F5BC8C-DEF4-48C0-9AF3-231A7A2B3763}" name="Комментарий" dataDxfId="41"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C15E88CC-063D-49C3-8C65-22A673E95F21}" name="Таблица135" displayName="Таблица135" ref="F21:I37" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C15E88CC-063D-49C3-8C65-22A673E95F21}" name="Таблица135" displayName="Таблица135" ref="F21:I37" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
   <autoFilter ref="F21:I37" xr:uid="{C15E88CC-063D-49C3-8C65-22A673E95F21}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{483490CB-F942-4B0F-9510-D82A61FB223D}" name="Физический адрес" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{0833CB7B-98AE-4D50-8F9A-95DE7CC11908}" name="FORCE-адрес" dataDxfId="36"/>
-    <tableColumn id="3" xr3:uid="{F23EFFBB-C4FA-4365-9FD2-75CD68D445D2}" name="Программный адрес" dataDxfId="35"/>
-    <tableColumn id="4" xr3:uid="{D1260B24-8F02-4295-A6CD-15B2B2283D2F}" name="Комментарий" dataDxfId="34"/>
+    <tableColumn id="1" xr3:uid="{483490CB-F942-4B0F-9510-D82A61FB223D}" name="Физический адрес" dataDxfId="38"/>
+    <tableColumn id="2" xr3:uid="{0833CB7B-98AE-4D50-8F9A-95DE7CC11908}" name="FORCE-адрес" dataDxfId="37"/>
+    <tableColumn id="3" xr3:uid="{F23EFFBB-C4FA-4365-9FD2-75CD68D445D2}" name="Программный адрес" dataDxfId="36"/>
+    <tableColumn id="4" xr3:uid="{D1260B24-8F02-4295-A6CD-15B2B2283D2F}" name="Комментарий" dataDxfId="35"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6D80E88C-685C-4063-856D-D2C15B34153F}" name="Таблица5" displayName="Таблица5" ref="A2:D898" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32" tableBorderDxfId="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6D80E88C-685C-4063-856D-D2C15B34153F}" name="Таблица5" displayName="Таблица5" ref="A2:D898" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33" tableBorderDxfId="32">
   <autoFilter ref="A2:D898" xr:uid="{6D80E88C-685C-4063-856D-D2C15B34153F}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{700DE593-4D2C-44F1-B1EB-946AFEAC5FA2}" name="Адрес на роботе" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{DFA6459F-0E72-4E10-AD20-6BA8A0B25186}" name="Программный адрес" dataDxfId="29">
+    <tableColumn id="1" xr3:uid="{700DE593-4D2C-44F1-B1EB-946AFEAC5FA2}" name="Адрес на роботе" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{DFA6459F-0E72-4E10-AD20-6BA8A0B25186}" name="Программный адрес" dataDxfId="30">
       <calculatedColumnFormula>"P"&amp;DEC2HEX(A3+65536-$A$3 +2*96, 5)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{4C1A065F-0479-4484-9301-8C183F79A8CD}" name="Адрес слова" dataDxfId="28">
+    <tableColumn id="3" xr3:uid="{4C1A065F-0479-4484-9301-8C183F79A8CD}" name="Адрес слова" dataDxfId="29">
       <calculatedColumnFormula>IF(RIGHT(B3,1)="0",LEFT(B3,5)," ")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{108B0066-3F14-4989-BED3-000B9011FB9C}" name="Комментарий" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{108B0066-3F14-4989-BED3-000B9011FB9C}" name="Комментарий" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B20DBADD-92EF-41AA-9EBD-54C39D77A466}" name="Таблица6" displayName="Таблица6" ref="F2:I898" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25" tableBorderDxfId="24">
-  <autoFilter ref="F2:I898" xr:uid="{B20DBADD-92EF-41AA-9EBD-54C39D77A466}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{A7F05EEE-147F-4EA1-86E9-D1D9D500A3C3}" name="Адрес на роботе" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{85BDCAFE-BAAB-49B6-9CBC-620DBED5D1CF}" name="Программный адрес" dataDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B20DBADD-92EF-41AA-9EBD-54C39D77A466}" name="Таблица6" displayName="Таблица6" ref="F2:J898" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26" tableBorderDxfId="25">
+  <autoFilter ref="F2:J898" xr:uid="{B20DBADD-92EF-41AA-9EBD-54C39D77A466}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{A7F05EEE-147F-4EA1-86E9-D1D9D500A3C3}" name="Адрес на роботе" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{85BDCAFE-BAAB-49B6-9CBC-620DBED5D1CF}" name="Программный адрес" dataDxfId="23">
       <calculatedColumnFormula>"P"&amp;DEC2HEX(F3+65536+4096 +2* 96-$F$3, 5)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{96B88C9C-25F3-47C9-B997-43B1C9FB4ECE}" name="Адрес слова" dataDxfId="21">
+    <tableColumn id="3" xr3:uid="{96B88C9C-25F3-47C9-B997-43B1C9FB4ECE}" name="Адрес слова" dataDxfId="22">
       <calculatedColumnFormula>IF(RIGHT(G3,1)="0",LEFT(G3,5)," ")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BB12B359-19DD-48D3-A11C-9EA26D87A7D4}" name="Комментарий" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{BB12B359-19DD-48D3-A11C-9EA26D87A7D4}" name="Комментарий" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{8C5C57C6-24CB-4FBE-B303-CAE2CBF8FE46}" name="Столбец1" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{922370A5-4286-4E2F-B3D7-F7B02AE73BA3}" name="Таблица19" displayName="Таблица19" ref="E2:G35" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{922370A5-4286-4E2F-B3D7-F7B02AE73BA3}" name="Таблица19" displayName="Таблица19" ref="E2:G35" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <autoFilter ref="E2:G35" xr:uid="{922370A5-4286-4E2F-B3D7-F7B02AE73BA3}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{030B20DE-3D3F-4F9E-9CF4-2797FEBBE639}" name="Физический адрес" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{FE7270F2-A91D-46D7-B053-943F33E91429}" name="Назначение" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{789B1D2D-EE14-45F0-AEF8-77EF04F1EE59}" name="Комментарий" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{030B20DE-3D3F-4F9E-9CF4-2797FEBBE639}" name="Физический адрес" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{FE7270F2-A91D-46D7-B053-943F33E91429}" name="Назначение" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{789B1D2D-EE14-45F0-AEF8-77EF04F1EE59}" name="Комментарий" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{DBF536A0-1787-4197-8344-E13C846DAF0F}" name="Таблица9" displayName="Таблица9" ref="A2:C35" totalsRowShown="0" headerRowDxfId="14" headerRowBorderDxfId="13" tableBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{DBF536A0-1787-4197-8344-E13C846DAF0F}" name="Таблица9" displayName="Таблица9" ref="A2:C35" totalsRowShown="0" headerRowDxfId="15" headerRowBorderDxfId="14" tableBorderDxfId="13">
   <autoFilter ref="A2:C35" xr:uid="{DBF536A0-1787-4197-8344-E13C846DAF0F}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0669B8C3-918B-41A1-8F32-AEE91E15EB1D}" name="Физический адрес" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{AC3FDE73-3420-4D74-8F9A-19CD06947E05}" name="Назначение" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{83B79EE0-0F25-4263-ACC2-A83B9403C818}" name="Комментарий" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{0669B8C3-918B-41A1-8F32-AEE91E15EB1D}" name="Физический адрес" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{AC3FDE73-3420-4D74-8F9A-19CD06947E05}" name="Назначение" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{83B79EE0-0F25-4263-ACC2-A83B9403C818}" name="Комментарий" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{D433E639-47C8-435B-BE62-40BBD3A85586}" name="Таблица7" displayName="Таблица7" ref="A1:E66" totalsRowShown="0" headerRowDxfId="8" dataDxfId="6" headerRowBorderDxfId="7" tableBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{D433E639-47C8-435B-BE62-40BBD3A85586}" name="Таблица7" displayName="Таблица7" ref="A1:E66" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6">
   <autoFilter ref="A1:E66" xr:uid="{D433E639-47C8-435B-BE62-40BBD3A85586}"/>
   <tableColumns count="5">
-    <tableColumn id="4" xr3:uid="{57905240-D78B-4866-948D-15CD0C7825F9}" name="№" dataDxfId="4"/>
-    <tableColumn id="1" xr3:uid="{C0C4E1FE-6EA6-4426-AC8B-A634B9C978EE}" name="Адрес слова" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{D830E9E6-B548-460D-A0E1-20E6927BC813}" name="Комментарий" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{92954912-D498-42AD-8489-14F9E7812192}" name="Размер" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{BE2FF70F-8E70-476F-BD8E-CD89F51A98F0}" name="Замечание" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{57905240-D78B-4866-948D-15CD0C7825F9}" name="№" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{C0C4E1FE-6EA6-4426-AC8B-A634B9C978EE}" name="Адрес слова" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{D830E9E6-B548-460D-A0E1-20E6927BC813}" name="Комментарий" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{92954912-D498-42AD-8489-14F9E7812192}" name="Размер" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{BE2FF70F-8E70-476F-BD8E-CD89F51A98F0}" name="Замечание" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2876,21 +2969,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF0C363D-E002-455D-AEBF-103AC5B10E47}">
   <dimension ref="A1:I37"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="21.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.8984375" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" style="2"/>
-    <col min="6" max="6" width="21.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.09765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.09765625" style="2"/>
+    <col min="6" max="6" width="21.8984375" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="49.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="2"/>
+    <col min="9" max="9" width="49.09765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.09765625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="15" thickBot="1">
       <c r="A1" s="11" t="s">
         <v>126</v>
       </c>
@@ -2904,7 +2997,7 @@
       <c r="H1" s="11"/>
       <c r="I1" s="11"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2930,7 +3023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -2956,7 +3049,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -2982,7 +3075,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -3008,7 +3101,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -3034,7 +3127,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -3060,7 +3153,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
@@ -3086,7 +3179,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -3112,7 +3205,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
@@ -3138,7 +3231,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -3164,7 +3257,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
         <v>36</v>
       </c>
@@ -3190,7 +3283,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
         <v>37</v>
       </c>
@@ -3216,7 +3309,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
         <v>38</v>
       </c>
@@ -3242,7 +3335,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
         <v>39</v>
       </c>
@@ -3268,7 +3361,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
         <v>40</v>
       </c>
@@ -3294,7 +3387,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
         <v>41</v>
       </c>
@@ -3320,7 +3413,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
         <v>42</v>
       </c>
@@ -3346,8 +3439,8 @@
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" ht="15" thickBot="1"/>
+    <row r="20" spans="1:9" ht="15" thickBot="1">
       <c r="A20" s="11" t="s">
         <v>129</v>
       </c>
@@ -3361,7 +3454,7 @@
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9">
       <c r="A21" s="2" t="s">
         <v>10</v>
       </c>
@@ -3387,7 +3480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9">
       <c r="A22" s="2" t="s">
         <v>130</v>
       </c>
@@ -3413,7 +3506,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9">
       <c r="A23" s="2" t="s">
         <v>131</v>
       </c>
@@ -3439,7 +3532,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9">
       <c r="A24" s="2" t="s">
         <v>132</v>
       </c>
@@ -3465,7 +3558,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9">
       <c r="A25" s="2" t="s">
         <v>133</v>
       </c>
@@ -3491,7 +3584,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9">
       <c r="A26" s="2" t="s">
         <v>134</v>
       </c>
@@ -3517,7 +3610,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9">
       <c r="A27" s="2" t="s">
         <v>135</v>
       </c>
@@ -3543,7 +3636,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9">
       <c r="A28" s="2" t="s">
         <v>136</v>
       </c>
@@ -3569,7 +3662,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9">
       <c r="A29" s="2" t="s">
         <v>137</v>
       </c>
@@ -3595,7 +3688,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9">
       <c r="A30" s="2" t="s">
         <v>28</v>
       </c>
@@ -3621,7 +3714,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9">
       <c r="A31" s="2" t="s">
         <v>29</v>
       </c>
@@ -3647,7 +3740,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9">
       <c r="A32" s="2" t="s">
         <v>30</v>
       </c>
@@ -3673,7 +3766,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9">
       <c r="A33" s="2" t="s">
         <v>31</v>
       </c>
@@ -3699,7 +3792,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9">
       <c r="A34" s="2" t="s">
         <v>32</v>
       </c>
@@ -3725,7 +3818,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9">
       <c r="A35" s="2" t="s">
         <v>33</v>
       </c>
@@ -3751,7 +3844,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9">
       <c r="A36" s="2" t="s">
         <v>34</v>
       </c>
@@ -3777,7 +3870,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9">
       <c r="A37" s="2" t="s">
         <v>35</v>
       </c>
@@ -3822,22 +3915,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40895EFA-86F2-45C7-8EA9-6C33984E31A6}">
-  <dimension ref="A1:I898"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J898"/>
+  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="43.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" style="1"/>
+    <col min="2" max="2" width="25.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="43.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.09765625" style="1"/>
     <col min="6" max="6" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.296875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="1"/>
+    <col min="10" max="16384" width="9.09765625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="14.4">
       <c r="A1" s="12" t="s">
         <v>243</v>
       </c>
@@ -3852,7 +3945,7 @@
       <c r="H1" s="12"/>
       <c r="I1" s="12"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="14.4">
       <c r="A2" s="2" t="s">
         <v>242</v>
       </c>
@@ -3878,8 +3971,11 @@
       <c r="I2" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J2" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="1">
         <v>65</v>
       </c>
@@ -3909,7 +4005,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="A4" s="1">
         <v>66</v>
       </c>
@@ -3939,7 +4035,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10">
       <c r="A5" s="1">
         <v>67</v>
       </c>
@@ -3969,7 +4065,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10">
       <c r="A6" s="1">
         <v>68</v>
       </c>
@@ -3999,7 +4095,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10">
       <c r="A7" s="1">
         <v>69</v>
       </c>
@@ -4029,7 +4125,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10">
       <c r="A8" s="1">
         <v>70</v>
       </c>
@@ -4059,7 +4155,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10">
       <c r="A9" s="1">
         <v>71</v>
       </c>
@@ -4089,7 +4185,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10">
       <c r="A10" s="1">
         <v>72</v>
       </c>
@@ -4116,7 +4212,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10">
       <c r="A11" s="1">
         <v>73</v>
       </c>
@@ -4143,7 +4239,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10">
       <c r="A12" s="1">
         <v>74</v>
       </c>
@@ -4170,7 +4266,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10">
       <c r="A13" s="1">
         <v>75</v>
       </c>
@@ -4197,7 +4293,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10">
       <c r="A14" s="1">
         <v>76</v>
       </c>
@@ -4224,7 +4320,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10">
       <c r="A15" s="1">
         <v>77</v>
       </c>
@@ -4251,7 +4347,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10">
       <c r="A16" s="1">
         <v>78</v>
       </c>
@@ -4275,7 +4371,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9">
       <c r="A17" s="1">
         <v>79</v>
       </c>
@@ -4299,7 +4395,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9">
       <c r="A18" s="1">
         <v>80</v>
       </c>
@@ -4323,7 +4419,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="14.4">
       <c r="A19" s="1">
         <v>81</v>
       </c>
@@ -4353,7 +4449,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="14.4">
       <c r="A20" s="1">
         <v>82</v>
       </c>
@@ -4383,7 +4479,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="14.4">
       <c r="A21" s="1">
         <v>83</v>
       </c>
@@ -4413,7 +4509,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="14.4">
       <c r="A22" s="1">
         <v>84</v>
       </c>
@@ -4443,7 +4539,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="14.4">
       <c r="A23" s="1">
         <v>85</v>
       </c>
@@ -4469,8 +4565,11 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I23" s="1" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="1">
         <v>86</v>
       </c>
@@ -4494,7 +4593,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="14.4">
       <c r="A25" s="1">
         <v>87</v>
       </c>
@@ -4519,7 +4618,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="14.4">
       <c r="A26" s="1">
         <v>88</v>
       </c>
@@ -4544,7 +4643,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="14.4">
       <c r="A27" s="1">
         <v>89</v>
       </c>
@@ -4569,7 +4668,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="14.4">
       <c r="A28" s="1">
         <v>90</v>
       </c>
@@ -4594,7 +4693,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="14.4">
       <c r="A29" s="1">
         <v>91</v>
       </c>
@@ -4619,7 +4718,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="14.4">
       <c r="A30" s="1">
         <v>92</v>
       </c>
@@ -4644,7 +4743,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="14.4">
       <c r="A31" s="1">
         <v>93</v>
       </c>
@@ -4669,7 +4768,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="14.4">
       <c r="A32" s="1">
         <v>94</v>
       </c>
@@ -4694,7 +4793,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="14.4">
       <c r="A33" s="1">
         <v>95</v>
       </c>
@@ -4719,7 +4818,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="14.4">
       <c r="A34" s="1">
         <v>96</v>
       </c>
@@ -4744,7 +4843,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="14.4">
       <c r="A35" s="1">
         <v>97</v>
       </c>
@@ -4774,7 +4873,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" ht="14.4">
       <c r="A36" s="1">
         <v>98</v>
       </c>
@@ -4804,7 +4903,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="14.4">
       <c r="A37" s="1">
         <v>99</v>
       </c>
@@ -4834,7 +4933,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="14.4">
       <c r="A38" s="1">
         <v>100</v>
       </c>
@@ -4864,7 +4963,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="14.4">
       <c r="A39" s="1">
         <v>101</v>
       </c>
@@ -4894,7 +4993,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9">
       <c r="A40" s="1">
         <v>102</v>
       </c>
@@ -4918,7 +5017,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" ht="14.4">
       <c r="A41" s="1">
         <v>103</v>
       </c>
@@ -4943,7 +5042,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" ht="14.4">
       <c r="A42" s="1">
         <v>104</v>
       </c>
@@ -4968,7 +5067,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" ht="14.4">
       <c r="A43" s="1">
         <v>105</v>
       </c>
@@ -4993,7 +5092,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" ht="14.4">
       <c r="A44" s="1">
         <v>106</v>
       </c>
@@ -5018,7 +5117,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" ht="14.4">
       <c r="A45" s="1">
         <v>107</v>
       </c>
@@ -5043,7 +5142,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="14.4">
       <c r="A46" s="1">
         <v>108</v>
       </c>
@@ -5068,7 +5167,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" ht="14.4">
       <c r="A47" s="1">
         <v>109</v>
       </c>
@@ -5093,7 +5192,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" ht="14.4">
       <c r="A48" s="1">
         <v>110</v>
       </c>
@@ -5118,7 +5217,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" ht="14.4">
       <c r="A49" s="1">
         <v>111</v>
       </c>
@@ -5143,7 +5242,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" ht="14.4">
       <c r="A50" s="1">
         <v>112</v>
       </c>
@@ -5168,7 +5267,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9">
       <c r="A51" s="1">
         <v>113</v>
       </c>
@@ -5198,7 +5297,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9">
       <c r="A52" s="1">
         <v>114</v>
       </c>
@@ -5220,8 +5319,11 @@
         <f t="shared" si="2"/>
         <v>P11031</v>
       </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I52" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" s="1">
         <v>115</v>
       </c>
@@ -5248,7 +5350,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9">
       <c r="A54" s="1">
         <v>116</v>
       </c>
@@ -5274,11 +5376,8 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I54" s="1" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" s="1">
         <v>117</v>
       </c>
@@ -5305,7 +5404,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9">
       <c r="A56" s="1">
         <v>118</v>
       </c>
@@ -5332,7 +5431,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9">
       <c r="A57" s="1">
         <v>119</v>
       </c>
@@ -5359,7 +5458,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9">
       <c r="A58" s="1">
         <v>120</v>
       </c>
@@ -5386,7 +5485,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9">
       <c r="A59" s="1">
         <v>121</v>
       </c>
@@ -5410,7 +5509,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9">
       <c r="A60" s="1">
         <v>122</v>
       </c>
@@ -5434,7 +5533,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9">
       <c r="A61" s="1">
         <v>123</v>
       </c>
@@ -5458,7 +5557,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9">
       <c r="A62" s="1">
         <v>124</v>
       </c>
@@ -5482,7 +5581,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9">
       <c r="A63" s="1">
         <v>125</v>
       </c>
@@ -5506,7 +5605,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9">
       <c r="A64" s="1">
         <v>126</v>
       </c>
@@ -5530,7 +5629,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9">
       <c r="A65" s="1">
         <v>127</v>
       </c>
@@ -5554,7 +5653,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9">
       <c r="A66" s="1">
         <v>128</v>
       </c>
@@ -5578,7 +5677,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9">
       <c r="A67" s="1">
         <v>129</v>
       </c>
@@ -5608,7 +5707,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9">
       <c r="A68" s="1">
         <v>130</v>
       </c>
@@ -5638,7 +5737,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9">
       <c r="A69" s="1">
         <v>131</v>
       </c>
@@ -5668,7 +5767,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9">
       <c r="A70" s="1">
         <v>132</v>
       </c>
@@ -5698,7 +5797,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9">
       <c r="A71" s="1">
         <v>133</v>
       </c>
@@ -5728,7 +5827,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9">
       <c r="A72" s="1">
         <v>134</v>
       </c>
@@ -5758,7 +5857,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9">
       <c r="A73" s="1">
         <v>135</v>
       </c>
@@ -5788,7 +5887,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9">
       <c r="A74" s="1">
         <v>136</v>
       </c>
@@ -5818,7 +5917,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9">
       <c r="A75" s="1">
         <v>137</v>
       </c>
@@ -5845,7 +5944,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9">
       <c r="A76" s="1">
         <v>138</v>
       </c>
@@ -5872,7 +5971,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9">
       <c r="A77" s="1">
         <v>139</v>
       </c>
@@ -5899,7 +5998,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9">
       <c r="A78" s="1">
         <v>140</v>
       </c>
@@ -5926,7 +6025,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9">
       <c r="A79" s="1">
         <v>141</v>
       </c>
@@ -5953,7 +6052,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9">
       <c r="A80" s="1">
         <v>142</v>
       </c>
@@ -5977,7 +6076,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8">
       <c r="A81" s="1">
         <v>143</v>
       </c>
@@ -6001,7 +6100,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8">
       <c r="A82" s="1">
         <v>144</v>
       </c>
@@ -6025,7 +6124,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8">
       <c r="A83" s="1">
         <v>145</v>
       </c>
@@ -6049,7 +6148,7 @@
         <v>P1105</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8">
       <c r="A84" s="1">
         <v>146</v>
       </c>
@@ -6073,7 +6172,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8">
       <c r="A85" s="1">
         <v>147</v>
       </c>
@@ -6097,7 +6196,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8">
       <c r="A86" s="1">
         <v>148</v>
       </c>
@@ -6121,7 +6220,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8">
       <c r="A87" s="1">
         <v>149</v>
       </c>
@@ -6145,7 +6244,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8">
       <c r="A88" s="1">
         <v>150</v>
       </c>
@@ -6169,7 +6268,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8">
       <c r="A89" s="1">
         <v>151</v>
       </c>
@@ -6193,7 +6292,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8">
       <c r="A90" s="1">
         <v>152</v>
       </c>
@@ -6217,7 +6316,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8">
       <c r="A91" s="1">
         <v>153</v>
       </c>
@@ -6241,7 +6340,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8">
       <c r="A92" s="1">
         <v>154</v>
       </c>
@@ -6265,7 +6364,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8">
       <c r="A93" s="1">
         <v>155</v>
       </c>
@@ -6289,7 +6388,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8">
       <c r="A94" s="1">
         <v>156</v>
       </c>
@@ -6313,7 +6412,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8">
       <c r="A95" s="1">
         <v>157</v>
       </c>
@@ -6337,7 +6436,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8">
       <c r="A96" s="1">
         <v>158</v>
       </c>
@@ -6361,7 +6460,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8">
       <c r="A97" s="1">
         <v>159</v>
       </c>
@@ -6385,7 +6484,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8">
       <c r="A98" s="1">
         <v>160</v>
       </c>
@@ -6409,7 +6508,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8">
       <c r="A99" s="1">
         <v>161</v>
       </c>
@@ -6433,7 +6532,7 @@
         <v>P1106</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8">
       <c r="A100" s="1">
         <v>162</v>
       </c>
@@ -6457,7 +6556,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8">
       <c r="A101" s="1">
         <v>163</v>
       </c>
@@ -6481,7 +6580,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8">
       <c r="A102" s="1">
         <v>164</v>
       </c>
@@ -6505,7 +6604,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8">
       <c r="A103" s="1">
         <v>165</v>
       </c>
@@ -6529,7 +6628,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8">
       <c r="A104" s="1">
         <v>166</v>
       </c>
@@ -6553,7 +6652,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8">
       <c r="A105" s="1">
         <v>167</v>
       </c>
@@ -6577,7 +6676,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8">
       <c r="A106" s="1">
         <v>168</v>
       </c>
@@ -6601,7 +6700,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8">
       <c r="A107" s="1">
         <v>169</v>
       </c>
@@ -6625,7 +6724,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8">
       <c r="A108" s="1">
         <v>170</v>
       </c>
@@ -6649,7 +6748,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8">
       <c r="A109" s="1">
         <v>171</v>
       </c>
@@ -6673,7 +6772,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8">
       <c r="A110" s="1">
         <v>172</v>
       </c>
@@ -6697,7 +6796,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8">
       <c r="A111" s="1">
         <v>173</v>
       </c>
@@ -6721,7 +6820,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8">
       <c r="A112" s="1">
         <v>174</v>
       </c>
@@ -6745,7 +6844,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8">
       <c r="A113" s="1">
         <v>175</v>
       </c>
@@ -6769,7 +6868,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8">
       <c r="A114" s="1">
         <v>176</v>
       </c>
@@ -6793,7 +6892,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8">
       <c r="A115" s="1">
         <v>177</v>
       </c>
@@ -6817,7 +6916,7 @@
         <v>P1107</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8">
       <c r="A116" s="1">
         <v>178</v>
       </c>
@@ -6841,7 +6940,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8">
       <c r="A117" s="1">
         <v>179</v>
       </c>
@@ -6865,7 +6964,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8">
       <c r="A118" s="1">
         <v>180</v>
       </c>
@@ -6889,7 +6988,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8">
       <c r="A119" s="1">
         <v>181</v>
       </c>
@@ -6913,7 +7012,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8">
       <c r="A120" s="1">
         <v>182</v>
       </c>
@@ -6937,7 +7036,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8">
       <c r="A121" s="1">
         <v>183</v>
       </c>
@@ -6961,7 +7060,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8">
       <c r="A122" s="1">
         <v>184</v>
       </c>
@@ -6985,7 +7084,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8">
       <c r="A123" s="1">
         <v>185</v>
       </c>
@@ -7009,7 +7108,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8">
       <c r="A124" s="1">
         <v>186</v>
       </c>
@@ -7033,7 +7132,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8">
       <c r="A125" s="1">
         <v>187</v>
       </c>
@@ -7057,7 +7156,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8">
       <c r="A126" s="1">
         <v>188</v>
       </c>
@@ -7081,7 +7180,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8">
       <c r="A127" s="1">
         <v>189</v>
       </c>
@@ -7105,7 +7204,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8">
       <c r="A128" s="1">
         <v>190</v>
       </c>
@@ -7129,7 +7228,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8">
       <c r="A129" s="1">
         <v>191</v>
       </c>
@@ -7153,7 +7252,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8">
       <c r="A130" s="1">
         <v>192</v>
       </c>
@@ -7177,7 +7276,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8">
       <c r="A131" s="1">
         <v>193</v>
       </c>
@@ -7201,7 +7300,7 @@
         <v>P1108</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8">
       <c r="A132" s="1">
         <v>194</v>
       </c>
@@ -7225,7 +7324,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8">
       <c r="A133" s="1">
         <v>195</v>
       </c>
@@ -7249,7 +7348,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8">
       <c r="A134" s="1">
         <v>196</v>
       </c>
@@ -7273,7 +7372,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8">
       <c r="A135" s="1">
         <v>197</v>
       </c>
@@ -7297,7 +7396,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8">
       <c r="A136" s="1">
         <v>198</v>
       </c>
@@ -7321,7 +7420,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8">
       <c r="A137" s="1">
         <v>199</v>
       </c>
@@ -7345,7 +7444,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8">
       <c r="A138" s="1">
         <v>200</v>
       </c>
@@ -7369,7 +7468,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8">
       <c r="A139" s="1">
         <v>201</v>
       </c>
@@ -7393,7 +7492,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8">
       <c r="A140" s="1">
         <v>202</v>
       </c>
@@ -7417,7 +7516,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8">
       <c r="A141" s="1">
         <v>203</v>
       </c>
@@ -7441,7 +7540,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8">
       <c r="A142" s="1">
         <v>204</v>
       </c>
@@ -7465,7 +7564,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8">
       <c r="A143" s="1">
         <v>205</v>
       </c>
@@ -7489,7 +7588,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:8">
       <c r="A144" s="1">
         <v>206</v>
       </c>
@@ -7513,7 +7612,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8">
       <c r="A145" s="1">
         <v>207</v>
       </c>
@@ -7537,7 +7636,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8">
       <c r="A146" s="1">
         <v>208</v>
       </c>
@@ -7561,7 +7660,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8">
       <c r="A147" s="1">
         <v>209</v>
       </c>
@@ -7585,7 +7684,7 @@
         <v>P1109</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8">
       <c r="A148" s="1">
         <v>210</v>
       </c>
@@ -7609,7 +7708,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8">
       <c r="A149" s="1">
         <v>211</v>
       </c>
@@ -7633,7 +7732,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8">
       <c r="A150" s="1">
         <v>212</v>
       </c>
@@ -7657,7 +7756,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8">
       <c r="A151" s="1">
         <v>213</v>
       </c>
@@ -7681,7 +7780,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8">
       <c r="A152" s="1">
         <v>214</v>
       </c>
@@ -7705,7 +7804,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:8">
       <c r="A153" s="1">
         <v>215</v>
       </c>
@@ -7729,7 +7828,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8">
       <c r="A154" s="1">
         <v>216</v>
       </c>
@@ -7753,7 +7852,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:8">
       <c r="A155" s="1">
         <v>217</v>
       </c>
@@ -7777,7 +7876,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:8">
       <c r="A156" s="1">
         <v>218</v>
       </c>
@@ -7801,7 +7900,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:8">
       <c r="A157" s="1">
         <v>219</v>
       </c>
@@ -7825,7 +7924,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:8">
       <c r="A158" s="1">
         <v>220</v>
       </c>
@@ -7849,7 +7948,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:8">
       <c r="A159" s="1">
         <v>221</v>
       </c>
@@ -7873,7 +7972,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:8">
       <c r="A160" s="1">
         <v>222</v>
       </c>
@@ -7897,7 +7996,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9">
       <c r="A161" s="1">
         <v>223</v>
       </c>
@@ -7921,7 +8020,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9">
       <c r="A162" s="1">
         <v>224</v>
       </c>
@@ -7945,7 +8044,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9">
       <c r="A163" s="1">
         <v>225</v>
       </c>
@@ -7975,7 +8074,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9">
       <c r="A164" s="1">
         <v>226</v>
       </c>
@@ -7999,7 +8098,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9">
       <c r="A165" s="1">
         <v>227</v>
       </c>
@@ -8023,7 +8122,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9">
       <c r="A166" s="1">
         <v>228</v>
       </c>
@@ -8047,7 +8146,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9">
       <c r="A167" s="1">
         <v>229</v>
       </c>
@@ -8071,7 +8170,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9">
       <c r="A168" s="1">
         <v>230</v>
       </c>
@@ -8095,7 +8194,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9">
       <c r="A169" s="1">
         <v>231</v>
       </c>
@@ -8119,7 +8218,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9">
       <c r="A170" s="1">
         <v>232</v>
       </c>
@@ -8143,7 +8242,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9">
       <c r="A171" s="1">
         <v>233</v>
       </c>
@@ -8167,7 +8266,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9">
       <c r="A172" s="1">
         <v>234</v>
       </c>
@@ -8191,7 +8290,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9">
       <c r="A173" s="1">
         <v>235</v>
       </c>
@@ -8215,7 +8314,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9">
       <c r="A174" s="1">
         <v>236</v>
       </c>
@@ -8239,7 +8338,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9">
       <c r="A175" s="1">
         <v>237</v>
       </c>
@@ -8263,7 +8362,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9">
       <c r="A176" s="1">
         <v>238</v>
       </c>
@@ -8287,7 +8386,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:8">
       <c r="A177" s="1">
         <v>239</v>
       </c>
@@ -8311,7 +8410,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8">
       <c r="A178" s="1">
         <v>240</v>
       </c>
@@ -8335,7 +8434,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:8">
       <c r="A179" s="1">
         <v>241</v>
       </c>
@@ -8362,7 +8461,7 @@
         <v>P1111</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:8">
       <c r="A180" s="1">
         <v>242</v>
       </c>
@@ -8386,7 +8485,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8">
       <c r="A181" s="1">
         <v>243</v>
       </c>
@@ -8410,7 +8509,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8">
       <c r="A182" s="1">
         <v>244</v>
       </c>
@@ -8434,7 +8533,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:8">
       <c r="A183" s="1">
         <v>245</v>
       </c>
@@ -8458,7 +8557,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:8">
       <c r="A184" s="1">
         <v>246</v>
       </c>
@@ -8482,7 +8581,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:8">
       <c r="A185" s="1">
         <v>247</v>
       </c>
@@ -8506,7 +8605,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:8">
       <c r="A186" s="1">
         <v>248</v>
       </c>
@@ -8530,7 +8629,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:8">
       <c r="A187" s="1">
         <v>249</v>
       </c>
@@ -8554,7 +8653,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:8">
       <c r="A188" s="1">
         <v>250</v>
       </c>
@@ -8578,7 +8677,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:8">
       <c r="A189" s="1">
         <v>251</v>
       </c>
@@ -8602,7 +8701,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:8">
       <c r="A190" s="1">
         <v>252</v>
       </c>
@@ -8626,7 +8725,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:8">
       <c r="A191" s="1">
         <v>253</v>
       </c>
@@ -8650,7 +8749,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:8">
       <c r="A192" s="1">
         <v>254</v>
       </c>
@@ -8674,7 +8773,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:8">
       <c r="A193" s="1">
         <v>255</v>
       </c>
@@ -8698,7 +8797,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:8">
       <c r="A194" s="1">
         <v>256</v>
       </c>
@@ -8722,7 +8821,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:8">
       <c r="A195" s="1">
         <v>257</v>
       </c>
@@ -8749,7 +8848,7 @@
         <v>P1112</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:8">
       <c r="A196" s="1">
         <v>258</v>
       </c>
@@ -8773,7 +8872,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:8">
       <c r="A197" s="1">
         <v>259</v>
       </c>
@@ -8797,7 +8896,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:8">
       <c r="A198" s="1">
         <v>260</v>
       </c>
@@ -8821,7 +8920,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:8">
       <c r="A199" s="1">
         <v>261</v>
       </c>
@@ -8845,7 +8944,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:8">
       <c r="A200" s="1">
         <v>262</v>
       </c>
@@ -8869,7 +8968,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8">
       <c r="A201" s="1">
         <v>263</v>
       </c>
@@ -8893,7 +8992,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8">
       <c r="A202" s="1">
         <v>264</v>
       </c>
@@ -8917,7 +9016,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8">
       <c r="A203" s="1">
         <v>265</v>
       </c>
@@ -8941,7 +9040,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:8">
       <c r="A204" s="1">
         <v>266</v>
       </c>
@@ -8965,7 +9064,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:8">
       <c r="A205" s="1">
         <v>267</v>
       </c>
@@ -8989,7 +9088,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:8">
       <c r="A206" s="1">
         <v>268</v>
       </c>
@@ -9013,7 +9112,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:8">
       <c r="A207" s="1">
         <v>269</v>
       </c>
@@ -9037,7 +9136,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:8">
       <c r="A208" s="1">
         <v>270</v>
       </c>
@@ -9061,7 +9160,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:8">
       <c r="A209" s="1">
         <v>271</v>
       </c>
@@ -9085,7 +9184,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:8">
       <c r="A210" s="1">
         <v>272</v>
       </c>
@@ -9109,7 +9208,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:8">
       <c r="A211" s="1">
         <v>273</v>
       </c>
@@ -9136,7 +9235,7 @@
         <v>P1113</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:8">
       <c r="A212" s="1">
         <v>274</v>
       </c>
@@ -9160,7 +9259,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:8">
       <c r="A213" s="1">
         <v>275</v>
       </c>
@@ -9184,7 +9283,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:8">
       <c r="A214" s="1">
         <v>276</v>
       </c>
@@ -9208,7 +9307,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:8">
       <c r="A215" s="1">
         <v>277</v>
       </c>
@@ -9232,7 +9331,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:8">
       <c r="A216" s="1">
         <v>278</v>
       </c>
@@ -9256,7 +9355,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:8">
       <c r="A217" s="1">
         <v>279</v>
       </c>
@@ -9280,7 +9379,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:8">
       <c r="A218" s="1">
         <v>280</v>
       </c>
@@ -9304,7 +9403,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:8">
       <c r="A219" s="1">
         <v>281</v>
       </c>
@@ -9328,7 +9427,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:8">
       <c r="A220" s="1">
         <v>282</v>
       </c>
@@ -9352,7 +9451,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:8">
       <c r="A221" s="1">
         <v>283</v>
       </c>
@@ -9376,7 +9475,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:8">
       <c r="A222" s="1">
         <v>284</v>
       </c>
@@ -9400,7 +9499,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:8">
       <c r="A223" s="1">
         <v>285</v>
       </c>
@@ -9424,7 +9523,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:8">
       <c r="A224" s="1">
         <v>286</v>
       </c>
@@ -9448,7 +9547,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:8">
       <c r="A225" s="1">
         <v>287</v>
       </c>
@@ -9472,7 +9571,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:8">
       <c r="A226" s="1">
         <v>288</v>
       </c>
@@ -9496,7 +9595,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:8">
       <c r="A227" s="1">
         <v>289</v>
       </c>
@@ -9523,7 +9622,7 @@
         <v>P1114</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:8">
       <c r="A228" s="1">
         <v>290</v>
       </c>
@@ -9547,7 +9646,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:8">
       <c r="A229" s="1">
         <v>291</v>
       </c>
@@ -9571,7 +9670,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:8">
       <c r="A230" s="1">
         <v>292</v>
       </c>
@@ -9595,7 +9694,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:8">
       <c r="A231" s="1">
         <v>293</v>
       </c>
@@ -9619,7 +9718,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:8">
       <c r="A232" s="1">
         <v>294</v>
       </c>
@@ -9643,7 +9742,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:8">
       <c r="A233" s="1">
         <v>295</v>
       </c>
@@ -9667,7 +9766,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:8">
       <c r="A234" s="1">
         <v>296</v>
       </c>
@@ -9691,7 +9790,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:8">
       <c r="A235" s="1">
         <v>297</v>
       </c>
@@ -9715,7 +9814,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:8">
       <c r="A236" s="1">
         <v>298</v>
       </c>
@@ -9739,7 +9838,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:8">
       <c r="A237" s="1">
         <v>299</v>
       </c>
@@ -9763,7 +9862,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:8">
       <c r="A238" s="1">
         <v>300</v>
       </c>
@@ -9787,7 +9886,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:8">
       <c r="A239" s="1">
         <v>301</v>
       </c>
@@ -9811,7 +9910,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:8">
       <c r="A240" s="1">
         <v>302</v>
       </c>
@@ -9835,7 +9934,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:8">
       <c r="A241" s="1">
         <v>303</v>
       </c>
@@ -9859,7 +9958,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:8">
       <c r="A242" s="1">
         <v>304</v>
       </c>
@@ -9883,7 +9982,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:8">
       <c r="A243" s="1">
         <v>305</v>
       </c>
@@ -9910,7 +10009,7 @@
         <v>P1115</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:8">
       <c r="A244" s="1">
         <v>306</v>
       </c>
@@ -9934,7 +10033,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:8">
       <c r="A245" s="1">
         <v>307</v>
       </c>
@@ -9958,7 +10057,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:8">
       <c r="A246" s="1">
         <v>308</v>
       </c>
@@ -9982,7 +10081,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:8">
       <c r="A247" s="1">
         <v>309</v>
       </c>
@@ -10006,7 +10105,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:8">
       <c r="A248" s="1">
         <v>310</v>
       </c>
@@ -10030,7 +10129,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:8">
       <c r="A249" s="1">
         <v>311</v>
       </c>
@@ -10054,7 +10153,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:8">
       <c r="A250" s="1">
         <v>312</v>
       </c>
@@ -10078,7 +10177,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:8">
       <c r="A251" s="1">
         <v>313</v>
       </c>
@@ -10102,7 +10201,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:8">
       <c r="A252" s="1">
         <v>314</v>
       </c>
@@ -10126,7 +10225,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:8">
       <c r="A253" s="1">
         <v>315</v>
       </c>
@@ -10150,7 +10249,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:8">
       <c r="A254" s="1">
         <v>316</v>
       </c>
@@ -10174,7 +10273,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:8">
       <c r="A255" s="1">
         <v>317</v>
       </c>
@@ -10198,7 +10297,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:8">
       <c r="A256" s="1">
         <v>318</v>
       </c>
@@ -10222,7 +10321,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:8">
       <c r="A257" s="1">
         <v>319</v>
       </c>
@@ -10246,7 +10345,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:8">
       <c r="A258" s="1">
         <v>320</v>
       </c>
@@ -10270,7 +10369,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:8">
       <c r="A259" s="1">
         <v>321</v>
       </c>
@@ -10282,6 +10381,9 @@
         <f t="shared" si="14"/>
         <v>P1016</v>
       </c>
+      <c r="D259" s="1" t="s">
+        <v>483</v>
+      </c>
       <c r="F259" s="1">
         <v>1321</v>
       </c>
@@ -10294,7 +10396,7 @@
         <v>P1116</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:8">
       <c r="A260" s="1">
         <v>322</v>
       </c>
@@ -10318,7 +10420,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:8">
       <c r="A261" s="1">
         <v>323</v>
       </c>
@@ -10342,7 +10444,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:8">
       <c r="A262" s="1">
         <v>324</v>
       </c>
@@ -10366,7 +10468,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:8">
       <c r="A263" s="1">
         <v>325</v>
       </c>
@@ -10390,7 +10492,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:8">
       <c r="A264" s="1">
         <v>326</v>
       </c>
@@ -10414,7 +10516,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:8">
       <c r="A265" s="1">
         <v>327</v>
       </c>
@@ -10438,7 +10540,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:8">
       <c r="A266" s="1">
         <v>328</v>
       </c>
@@ -10462,7 +10564,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:8">
       <c r="A267" s="1">
         <v>329</v>
       </c>
@@ -10486,7 +10588,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:8">
       <c r="A268" s="1">
         <v>330</v>
       </c>
@@ -10510,7 +10612,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:8">
       <c r="A269" s="1">
         <v>331</v>
       </c>
@@ -10534,7 +10636,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:8">
       <c r="A270" s="1">
         <v>332</v>
       </c>
@@ -10558,7 +10660,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:8">
       <c r="A271" s="1">
         <v>333</v>
       </c>
@@ -10582,7 +10684,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:8">
       <c r="A272" s="1">
         <v>334</v>
       </c>
@@ -10606,7 +10708,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:8">
       <c r="A273" s="1">
         <v>335</v>
       </c>
@@ -10630,7 +10732,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:8">
       <c r="A274" s="1">
         <v>336</v>
       </c>
@@ -10654,7 +10756,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:8">
       <c r="A275" s="1">
         <v>337</v>
       </c>
@@ -10678,7 +10780,7 @@
         <v>P1117</v>
       </c>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:8">
       <c r="A276" s="1">
         <v>338</v>
       </c>
@@ -10702,7 +10804,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:8">
       <c r="A277" s="1">
         <v>339</v>
       </c>
@@ -10726,7 +10828,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:8">
       <c r="A278" s="1">
         <v>340</v>
       </c>
@@ -10750,7 +10852,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:8">
       <c r="A279" s="1">
         <v>341</v>
       </c>
@@ -10774,7 +10876,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:8">
       <c r="A280" s="1">
         <v>342</v>
       </c>
@@ -10798,7 +10900,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:8">
       <c r="A281" s="1">
         <v>343</v>
       </c>
@@ -10822,7 +10924,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:8">
       <c r="A282" s="1">
         <v>344</v>
       </c>
@@ -10846,7 +10948,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:8">
       <c r="A283" s="1">
         <v>345</v>
       </c>
@@ -10870,7 +10972,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:8">
       <c r="A284" s="1">
         <v>346</v>
       </c>
@@ -10894,7 +10996,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:8">
       <c r="A285" s="1">
         <v>347</v>
       </c>
@@ -10918,7 +11020,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:8">
       <c r="A286" s="1">
         <v>348</v>
       </c>
@@ -10942,7 +11044,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:8">
       <c r="A287" s="1">
         <v>349</v>
       </c>
@@ -10966,7 +11068,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:8">
       <c r="A288" s="1">
         <v>350</v>
       </c>
@@ -10990,7 +11092,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:8">
       <c r="A289" s="1">
         <v>351</v>
       </c>
@@ -11014,7 +11116,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:8">
       <c r="A290" s="1">
         <v>352</v>
       </c>
@@ -11038,7 +11140,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:8">
       <c r="A291" s="1">
         <v>353</v>
       </c>
@@ -11062,7 +11164,7 @@
         <v>P1118</v>
       </c>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:8">
       <c r="A292" s="1">
         <v>354</v>
       </c>
@@ -11086,7 +11188,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:8">
       <c r="A293" s="1">
         <v>355</v>
       </c>
@@ -11110,7 +11212,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:8">
       <c r="A294" s="1">
         <v>356</v>
       </c>
@@ -11134,7 +11236,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:8">
       <c r="A295" s="1">
         <v>357</v>
       </c>
@@ -11158,7 +11260,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:8">
       <c r="A296" s="1">
         <v>358</v>
       </c>
@@ -11182,7 +11284,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:8">
       <c r="A297" s="1">
         <v>359</v>
       </c>
@@ -11206,7 +11308,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:8">
       <c r="A298" s="1">
         <v>360</v>
       </c>
@@ -11230,7 +11332,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:8">
       <c r="A299" s="1">
         <v>361</v>
       </c>
@@ -11254,7 +11356,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:8">
       <c r="A300" s="1">
         <v>362</v>
       </c>
@@ -11278,7 +11380,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:8">
       <c r="A301" s="1">
         <v>363</v>
       </c>
@@ -11302,7 +11404,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:8">
       <c r="A302" s="1">
         <v>364</v>
       </c>
@@ -11326,7 +11428,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:8">
       <c r="A303" s="1">
         <v>365</v>
       </c>
@@ -11350,7 +11452,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:8">
       <c r="A304" s="1">
         <v>366</v>
       </c>
@@ -11374,7 +11476,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:8">
       <c r="A305" s="1">
         <v>367</v>
       </c>
@@ -11398,7 +11500,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:8">
       <c r="A306" s="1">
         <v>368</v>
       </c>
@@ -11422,7 +11524,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:8">
       <c r="A307" s="1">
         <v>369</v>
       </c>
@@ -11446,7 +11548,7 @@
         <v>P1119</v>
       </c>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:8">
       <c r="A308" s="1">
         <v>370</v>
       </c>
@@ -11470,7 +11572,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:8">
       <c r="A309" s="1">
         <v>371</v>
       </c>
@@ -11494,7 +11596,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:8">
       <c r="A310" s="1">
         <v>372</v>
       </c>
@@ -11518,7 +11620,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:8">
       <c r="A311" s="1">
         <v>373</v>
       </c>
@@ -11542,7 +11644,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:8">
       <c r="A312" s="1">
         <v>374</v>
       </c>
@@ -11566,7 +11668,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:8">
       <c r="A313" s="1">
         <v>375</v>
       </c>
@@ -11590,7 +11692,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:8">
       <c r="A314" s="1">
         <v>376</v>
       </c>
@@ -11614,7 +11716,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:8">
       <c r="A315" s="1">
         <v>377</v>
       </c>
@@ -11638,7 +11740,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:8">
       <c r="A316" s="1">
         <v>378</v>
       </c>
@@ -11662,7 +11764,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:8">
       <c r="A317" s="1">
         <v>379</v>
       </c>
@@ -11686,7 +11788,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:8">
       <c r="A318" s="1">
         <v>380</v>
       </c>
@@ -11710,7 +11812,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:8">
       <c r="A319" s="1">
         <v>381</v>
       </c>
@@ -11734,7 +11836,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:8">
       <c r="A320" s="1">
         <v>382</v>
       </c>
@@ -11758,7 +11860,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:8">
       <c r="A321" s="1">
         <v>383</v>
       </c>
@@ -11782,7 +11884,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:8">
       <c r="A322" s="1">
         <v>384</v>
       </c>
@@ -11806,7 +11908,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:8">
       <c r="A323" s="1">
         <v>385</v>
       </c>
@@ -11830,7 +11932,7 @@
         <v>P1120</v>
       </c>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:8">
       <c r="A324" s="1">
         <v>386</v>
       </c>
@@ -11854,7 +11956,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:8">
       <c r="A325" s="1">
         <v>387</v>
       </c>
@@ -11878,7 +11980,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:8">
       <c r="A326" s="1">
         <v>388</v>
       </c>
@@ -11902,7 +12004,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:8">
       <c r="A327" s="1">
         <v>389</v>
       </c>
@@ -11926,7 +12028,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:8">
       <c r="A328" s="1">
         <v>390</v>
       </c>
@@ -11950,7 +12052,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:8">
       <c r="A329" s="1">
         <v>391</v>
       </c>
@@ -11974,7 +12076,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:8">
       <c r="A330" s="1">
         <v>392</v>
       </c>
@@ -11998,7 +12100,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:8">
       <c r="A331" s="1">
         <v>393</v>
       </c>
@@ -12022,7 +12124,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:8">
       <c r="A332" s="1">
         <v>394</v>
       </c>
@@ -12046,7 +12148,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:8">
       <c r="A333" s="1">
         <v>395</v>
       </c>
@@ -12070,7 +12172,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:8">
       <c r="A334" s="1">
         <v>396</v>
       </c>
@@ -12094,7 +12196,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:8">
       <c r="A335" s="1">
         <v>397</v>
       </c>
@@ -12118,7 +12220,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:8">
       <c r="A336" s="1">
         <v>398</v>
       </c>
@@ -12142,7 +12244,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:8">
       <c r="A337" s="1">
         <v>399</v>
       </c>
@@ -12166,7 +12268,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:8">
       <c r="A338" s="1">
         <v>400</v>
       </c>
@@ -12190,7 +12292,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:8">
       <c r="A339" s="1">
         <v>401</v>
       </c>
@@ -12214,7 +12316,7 @@
         <v>P1121</v>
       </c>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:8">
       <c r="A340" s="1">
         <v>402</v>
       </c>
@@ -12238,7 +12340,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:8">
       <c r="A341" s="1">
         <v>403</v>
       </c>
@@ -12262,7 +12364,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:8">
       <c r="A342" s="1">
         <v>404</v>
       </c>
@@ -12286,7 +12388,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:8">
       <c r="A343" s="1">
         <v>405</v>
       </c>
@@ -12310,7 +12412,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:8">
       <c r="A344" s="1">
         <v>406</v>
       </c>
@@ -12334,7 +12436,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:8">
       <c r="A345" s="1">
         <v>407</v>
       </c>
@@ -12358,7 +12460,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:8">
       <c r="A346" s="1">
         <v>408</v>
       </c>
@@ -12382,7 +12484,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:8">
       <c r="A347" s="1">
         <v>409</v>
       </c>
@@ -12406,7 +12508,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:8">
       <c r="A348" s="1">
         <v>410</v>
       </c>
@@ -12430,7 +12532,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:8">
       <c r="A349" s="1">
         <v>411</v>
       </c>
@@ -12454,7 +12556,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:8">
       <c r="A350" s="1">
         <v>412</v>
       </c>
@@ -12478,7 +12580,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:8">
       <c r="A351" s="1">
         <v>413</v>
       </c>
@@ -12502,7 +12604,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:8">
       <c r="A352" s="1">
         <v>414</v>
       </c>
@@ -12526,7 +12628,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:8">
       <c r="A353" s="1">
         <v>415</v>
       </c>
@@ -12550,7 +12652,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:8">
       <c r="A354" s="1">
         <v>416</v>
       </c>
@@ -12574,7 +12676,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:8">
       <c r="A355" s="1">
         <v>417</v>
       </c>
@@ -12598,7 +12700,7 @@
         <v>P1122</v>
       </c>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:8">
       <c r="A356" s="1">
         <v>418</v>
       </c>
@@ -12622,7 +12724,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:8">
       <c r="A357" s="1">
         <v>419</v>
       </c>
@@ -12646,7 +12748,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:8">
       <c r="A358" s="1">
         <v>420</v>
       </c>
@@ -12670,7 +12772,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:8">
       <c r="A359" s="1">
         <v>421</v>
       </c>
@@ -12694,7 +12796,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:8">
       <c r="A360" s="1">
         <v>422</v>
       </c>
@@ -12718,7 +12820,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:8">
       <c r="A361" s="1">
         <v>423</v>
       </c>
@@ -12742,7 +12844,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:8">
       <c r="A362" s="1">
         <v>424</v>
       </c>
@@ -12766,7 +12868,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:8">
       <c r="A363" s="1">
         <v>425</v>
       </c>
@@ -12790,7 +12892,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:8">
       <c r="A364" s="1">
         <v>426</v>
       </c>
@@ -12814,7 +12916,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:8">
       <c r="A365" s="1">
         <v>427</v>
       </c>
@@ -12838,7 +12940,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:8">
       <c r="A366" s="1">
         <v>428</v>
       </c>
@@ -12862,7 +12964,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:8">
       <c r="A367" s="1">
         <v>429</v>
       </c>
@@ -12886,7 +12988,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:8">
       <c r="A368" s="1">
         <v>430</v>
       </c>
@@ -12910,7 +13012,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:8">
       <c r="A369" s="1">
         <v>431</v>
       </c>
@@ -12934,7 +13036,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:8">
       <c r="A370" s="1">
         <v>432</v>
       </c>
@@ -12958,7 +13060,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:8">
       <c r="A371" s="1">
         <v>433</v>
       </c>
@@ -12982,7 +13084,7 @@
         <v>P1123</v>
       </c>
     </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:8">
       <c r="A372" s="1">
         <v>434</v>
       </c>
@@ -13006,7 +13108,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:8">
       <c r="A373" s="1">
         <v>435</v>
       </c>
@@ -13030,7 +13132,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:8">
       <c r="A374" s="1">
         <v>436</v>
       </c>
@@ -13054,7 +13156,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:8">
       <c r="A375" s="1">
         <v>437</v>
       </c>
@@ -13078,7 +13180,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:8">
       <c r="A376" s="1">
         <v>438</v>
       </c>
@@ -13102,7 +13204,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:8">
       <c r="A377" s="1">
         <v>439</v>
       </c>
@@ -13126,7 +13228,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:8">
       <c r="A378" s="1">
         <v>440</v>
       </c>
@@ -13150,7 +13252,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:8">
       <c r="A379" s="1">
         <v>441</v>
       </c>
@@ -13174,7 +13276,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:8">
       <c r="A380" s="1">
         <v>442</v>
       </c>
@@ -13198,7 +13300,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:8">
       <c r="A381" s="1">
         <v>443</v>
       </c>
@@ -13222,7 +13324,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:8">
       <c r="A382" s="1">
         <v>444</v>
       </c>
@@ -13246,7 +13348,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:8">
       <c r="A383" s="1">
         <v>445</v>
       </c>
@@ -13270,7 +13372,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:8">
       <c r="A384" s="1">
         <v>446</v>
       </c>
@@ -13294,7 +13396,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:8">
       <c r="A385" s="1">
         <v>447</v>
       </c>
@@ -13318,7 +13420,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:8">
       <c r="A386" s="1">
         <v>448</v>
       </c>
@@ -13342,7 +13444,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:8">
       <c r="A387" s="1">
         <v>449</v>
       </c>
@@ -13366,7 +13468,7 @@
         <v>P1124</v>
       </c>
     </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:8">
       <c r="A388" s="1">
         <v>450</v>
       </c>
@@ -13390,7 +13492,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:8">
       <c r="A389" s="1">
         <v>451</v>
       </c>
@@ -13414,7 +13516,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:8">
       <c r="A390" s="1">
         <v>452</v>
       </c>
@@ -13438,7 +13540,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:8">
       <c r="A391" s="1">
         <v>453</v>
       </c>
@@ -13462,7 +13564,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:8">
       <c r="A392" s="1">
         <v>454</v>
       </c>
@@ -13486,7 +13588,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:8">
       <c r="A393" s="1">
         <v>455</v>
       </c>
@@ -13510,7 +13612,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:8">
       <c r="A394" s="1">
         <v>456</v>
       </c>
@@ -13534,7 +13636,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:8">
       <c r="A395" s="1">
         <v>457</v>
       </c>
@@ -13558,7 +13660,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:8">
       <c r="A396" s="1">
         <v>458</v>
       </c>
@@ -13582,7 +13684,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:8">
       <c r="A397" s="1">
         <v>459</v>
       </c>
@@ -13606,7 +13708,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:8">
       <c r="A398" s="1">
         <v>460</v>
       </c>
@@ -13630,7 +13732,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:8">
       <c r="A399" s="1">
         <v>461</v>
       </c>
@@ -13654,7 +13756,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:8">
       <c r="A400" s="1">
         <v>462</v>
       </c>
@@ -13678,7 +13780,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:8">
       <c r="A401" s="1">
         <v>463</v>
       </c>
@@ -13702,7 +13804,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:8">
       <c r="A402" s="1">
         <v>464</v>
       </c>
@@ -13726,7 +13828,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:8">
       <c r="A403" s="1">
         <v>465</v>
       </c>
@@ -13750,7 +13852,7 @@
         <v>P1125</v>
       </c>
     </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:8">
       <c r="A404" s="1">
         <v>466</v>
       </c>
@@ -13774,7 +13876,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:8">
       <c r="A405" s="1">
         <v>467</v>
       </c>
@@ -13798,7 +13900,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:8">
       <c r="A406" s="1">
         <v>468</v>
       </c>
@@ -13822,7 +13924,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:8">
       <c r="A407" s="1">
         <v>469</v>
       </c>
@@ -13846,7 +13948,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:8">
       <c r="A408" s="1">
         <v>470</v>
       </c>
@@ -13870,7 +13972,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:8">
       <c r="A409" s="1">
         <v>471</v>
       </c>
@@ -13894,7 +13996,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:8">
       <c r="A410" s="1">
         <v>472</v>
       </c>
@@ -13918,7 +14020,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="411" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:8">
       <c r="A411" s="1">
         <v>473</v>
       </c>
@@ -13942,7 +14044,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="412" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:8">
       <c r="A412" s="1">
         <v>474</v>
       </c>
@@ -13966,7 +14068,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="413" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:8">
       <c r="A413" s="1">
         <v>475</v>
       </c>
@@ -13990,7 +14092,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="414" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:8">
       <c r="A414" s="1">
         <v>476</v>
       </c>
@@ -14014,7 +14116,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="415" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:8">
       <c r="A415" s="1">
         <v>477</v>
       </c>
@@ -14038,7 +14140,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="416" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:8">
       <c r="A416" s="1">
         <v>478</v>
       </c>
@@ -14062,7 +14164,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="417" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:8">
       <c r="A417" s="1">
         <v>479</v>
       </c>
@@ -14086,7 +14188,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="418" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:8">
       <c r="A418" s="1">
         <v>480</v>
       </c>
@@ -14110,7 +14212,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="419" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:8">
       <c r="A419" s="1">
         <v>481</v>
       </c>
@@ -14134,7 +14236,7 @@
         <v>P1126</v>
       </c>
     </row>
-    <row r="420" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:8">
       <c r="A420" s="1">
         <v>482</v>
       </c>
@@ -14158,7 +14260,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="421" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:8">
       <c r="A421" s="1">
         <v>483</v>
       </c>
@@ -14182,7 +14284,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="422" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:8">
       <c r="A422" s="1">
         <v>484</v>
       </c>
@@ -14206,7 +14308,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="423" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:8">
       <c r="A423" s="1">
         <v>485</v>
       </c>
@@ -14230,7 +14332,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="424" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:8">
       <c r="A424" s="1">
         <v>486</v>
       </c>
@@ -14254,7 +14356,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="425" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:8">
       <c r="A425" s="1">
         <v>487</v>
       </c>
@@ -14278,7 +14380,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="426" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:8">
       <c r="A426" s="1">
         <v>488</v>
       </c>
@@ -14302,7 +14404,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="427" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:8">
       <c r="A427" s="1">
         <v>489</v>
       </c>
@@ -14326,7 +14428,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="428" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:8">
       <c r="A428" s="1">
         <v>490</v>
       </c>
@@ -14350,7 +14452,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="429" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:8">
       <c r="A429" s="1">
         <v>491</v>
       </c>
@@ -14374,7 +14476,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="430" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:8">
       <c r="A430" s="1">
         <v>492</v>
       </c>
@@ -14398,7 +14500,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="431" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:8">
       <c r="A431" s="1">
         <v>493</v>
       </c>
@@ -14422,7 +14524,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="432" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:8">
       <c r="A432" s="1">
         <v>494</v>
       </c>
@@ -14446,7 +14548,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="433" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:8">
       <c r="A433" s="1">
         <v>495</v>
       </c>
@@ -14470,7 +14572,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="434" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:8">
       <c r="A434" s="1">
         <v>496</v>
       </c>
@@ -14494,7 +14596,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="435" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:8">
       <c r="A435" s="1">
         <v>497</v>
       </c>
@@ -14518,7 +14620,7 @@
         <v>P1127</v>
       </c>
     </row>
-    <row r="436" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:8">
       <c r="A436" s="1">
         <v>498</v>
       </c>
@@ -14542,7 +14644,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="437" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:8">
       <c r="A437" s="1">
         <v>499</v>
       </c>
@@ -14566,7 +14668,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="438" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:8">
       <c r="A438" s="1">
         <v>500</v>
       </c>
@@ -14590,7 +14692,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="439" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:8">
       <c r="A439" s="1">
         <v>501</v>
       </c>
@@ -14614,7 +14716,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="440" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:8">
       <c r="A440" s="1">
         <v>502</v>
       </c>
@@ -14638,7 +14740,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="441" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:8">
       <c r="A441" s="1">
         <v>503</v>
       </c>
@@ -14662,7 +14764,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="442" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:8">
       <c r="A442" s="1">
         <v>504</v>
       </c>
@@ -14686,7 +14788,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="443" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:8">
       <c r="A443" s="1">
         <v>505</v>
       </c>
@@ -14710,7 +14812,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="444" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:8">
       <c r="A444" s="1">
         <v>506</v>
       </c>
@@ -14734,7 +14836,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="445" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:8">
       <c r="A445" s="1">
         <v>507</v>
       </c>
@@ -14758,7 +14860,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="446" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:8">
       <c r="A446" s="1">
         <v>508</v>
       </c>
@@ -14782,7 +14884,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="447" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:8">
       <c r="A447" s="1">
         <v>509</v>
       </c>
@@ -14806,7 +14908,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="448" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:8">
       <c r="A448" s="1">
         <v>510</v>
       </c>
@@ -14830,7 +14932,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="449" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:8">
       <c r="A449" s="1">
         <v>511</v>
       </c>
@@ -14854,7 +14956,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="450" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:8">
       <c r="A450" s="1">
         <v>512</v>
       </c>
@@ -14878,7 +14980,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="451" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:8">
       <c r="A451" s="1">
         <v>513</v>
       </c>
@@ -14902,7 +15004,7 @@
         <v>P1128</v>
       </c>
     </row>
-    <row r="452" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:8">
       <c r="A452" s="1">
         <v>514</v>
       </c>
@@ -14926,7 +15028,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="453" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:8">
       <c r="A453" s="1">
         <v>515</v>
       </c>
@@ -14950,7 +15052,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="454" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:8">
       <c r="A454" s="1">
         <v>516</v>
       </c>
@@ -14974,7 +15076,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="455" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:8">
       <c r="A455" s="1">
         <v>517</v>
       </c>
@@ -14998,7 +15100,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="456" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:8">
       <c r="A456" s="1">
         <v>518</v>
       </c>
@@ -15022,7 +15124,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="457" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:8">
       <c r="A457" s="1">
         <v>519</v>
       </c>
@@ -15046,7 +15148,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="458" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:8">
       <c r="A458" s="1">
         <v>520</v>
       </c>
@@ -15070,7 +15172,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="459" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:8">
       <c r="A459" s="1">
         <v>521</v>
       </c>
@@ -15094,7 +15196,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="460" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:8">
       <c r="A460" s="1">
         <v>522</v>
       </c>
@@ -15118,7 +15220,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="461" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:8">
       <c r="A461" s="1">
         <v>523</v>
       </c>
@@ -15142,7 +15244,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="462" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:8">
       <c r="A462" s="1">
         <v>524</v>
       </c>
@@ -15166,7 +15268,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="463" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:8">
       <c r="A463" s="1">
         <v>525</v>
       </c>
@@ -15190,7 +15292,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="464" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:8">
       <c r="A464" s="1">
         <v>526</v>
       </c>
@@ -15214,7 +15316,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="465" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:8">
       <c r="A465" s="1">
         <v>527</v>
       </c>
@@ -15238,7 +15340,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="466" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:8">
       <c r="A466" s="1">
         <v>528</v>
       </c>
@@ -15262,7 +15364,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="467" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:8">
       <c r="A467" s="1">
         <v>529</v>
       </c>
@@ -15286,7 +15388,7 @@
         <v>P1129</v>
       </c>
     </row>
-    <row r="468" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:8">
       <c r="A468" s="1">
         <v>530</v>
       </c>
@@ -15310,7 +15412,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="469" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:8">
       <c r="A469" s="1">
         <v>531</v>
       </c>
@@ -15334,7 +15436,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="470" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:8">
       <c r="A470" s="1">
         <v>532</v>
       </c>
@@ -15358,7 +15460,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="471" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:8">
       <c r="A471" s="1">
         <v>533</v>
       </c>
@@ -15382,7 +15484,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="472" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:8">
       <c r="A472" s="1">
         <v>534</v>
       </c>
@@ -15406,7 +15508,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="473" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:8">
       <c r="A473" s="1">
         <v>535</v>
       </c>
@@ -15430,7 +15532,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="474" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:8">
       <c r="A474" s="1">
         <v>536</v>
       </c>
@@ -15454,7 +15556,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="475" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:8">
       <c r="A475" s="1">
         <v>537</v>
       </c>
@@ -15478,7 +15580,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="476" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:8">
       <c r="A476" s="1">
         <v>538</v>
       </c>
@@ -15502,7 +15604,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="477" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:8">
       <c r="A477" s="1">
         <v>539</v>
       </c>
@@ -15526,7 +15628,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="478" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:8">
       <c r="A478" s="1">
         <v>540</v>
       </c>
@@ -15550,7 +15652,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="479" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:8">
       <c r="A479" s="1">
         <v>541</v>
       </c>
@@ -15574,7 +15676,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="480" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:8">
       <c r="A480" s="1">
         <v>542</v>
       </c>
@@ -15598,7 +15700,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="481" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:8">
       <c r="A481" s="1">
         <v>543</v>
       </c>
@@ -15622,7 +15724,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="482" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:8">
       <c r="A482" s="1">
         <v>544</v>
       </c>
@@ -15646,7 +15748,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="483" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:8">
       <c r="A483" s="1">
         <v>545</v>
       </c>
@@ -15670,7 +15772,7 @@
         <v>P1130</v>
       </c>
     </row>
-    <row r="484" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:8">
       <c r="A484" s="1">
         <v>546</v>
       </c>
@@ -15694,7 +15796,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="485" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:8">
       <c r="A485" s="1">
         <v>547</v>
       </c>
@@ -15718,7 +15820,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="486" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:8">
       <c r="A486" s="1">
         <v>548</v>
       </c>
@@ -15742,7 +15844,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="487" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:8">
       <c r="A487" s="1">
         <v>549</v>
       </c>
@@ -15766,7 +15868,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="488" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:8">
       <c r="A488" s="1">
         <v>550</v>
       </c>
@@ -15790,7 +15892,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="489" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:8">
       <c r="A489" s="1">
         <v>551</v>
       </c>
@@ -15814,7 +15916,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="490" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:8">
       <c r="A490" s="1">
         <v>552</v>
       </c>
@@ -15838,7 +15940,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="491" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:8">
       <c r="A491" s="1">
         <v>553</v>
       </c>
@@ -15862,7 +15964,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="492" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:8">
       <c r="A492" s="1">
         <v>554</v>
       </c>
@@ -15886,7 +15988,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="493" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:8">
       <c r="A493" s="1">
         <v>555</v>
       </c>
@@ -15910,7 +16012,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="494" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:8">
       <c r="A494" s="1">
         <v>556</v>
       </c>
@@ -15934,7 +16036,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="495" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:8">
       <c r="A495" s="1">
         <v>557</v>
       </c>
@@ -15958,7 +16060,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="496" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:8">
       <c r="A496" s="1">
         <v>558</v>
       </c>
@@ -15982,7 +16084,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="497" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:8">
       <c r="A497" s="1">
         <v>559</v>
       </c>
@@ -16006,7 +16108,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="498" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:8">
       <c r="A498" s="1">
         <v>560</v>
       </c>
@@ -16030,7 +16132,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="499" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:8">
       <c r="A499" s="1">
         <v>561</v>
       </c>
@@ -16054,7 +16156,7 @@
         <v>P1131</v>
       </c>
     </row>
-    <row r="500" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:8">
       <c r="A500" s="1">
         <v>562</v>
       </c>
@@ -16078,7 +16180,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="501" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:8">
       <c r="A501" s="1">
         <v>563</v>
       </c>
@@ -16102,7 +16204,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="502" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:8">
       <c r="A502" s="1">
         <v>564</v>
       </c>
@@ -16126,7 +16228,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="503" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:8">
       <c r="A503" s="1">
         <v>565</v>
       </c>
@@ -16150,7 +16252,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="504" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:8">
       <c r="A504" s="1">
         <v>566</v>
       </c>
@@ -16174,7 +16276,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="505" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:8">
       <c r="A505" s="1">
         <v>567</v>
       </c>
@@ -16198,7 +16300,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="506" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:8">
       <c r="A506" s="1">
         <v>568</v>
       </c>
@@ -16222,7 +16324,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="507" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:8">
       <c r="A507" s="1">
         <v>569</v>
       </c>
@@ -16246,7 +16348,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="508" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:8">
       <c r="A508" s="1">
         <v>570</v>
       </c>
@@ -16270,7 +16372,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="509" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:8">
       <c r="A509" s="1">
         <v>571</v>
       </c>
@@ -16294,7 +16396,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="510" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:8">
       <c r="A510" s="1">
         <v>572</v>
       </c>
@@ -16318,7 +16420,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="511" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:8">
       <c r="A511" s="1">
         <v>573</v>
       </c>
@@ -16342,7 +16444,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="512" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:8">
       <c r="A512" s="1">
         <v>574</v>
       </c>
@@ -16366,7 +16468,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="513" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:8">
       <c r="A513" s="1">
         <v>575</v>
       </c>
@@ -16390,7 +16492,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="514" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:8">
       <c r="A514" s="1">
         <v>576</v>
       </c>
@@ -16414,7 +16516,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="515" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:8">
       <c r="A515" s="1">
         <v>577</v>
       </c>
@@ -16438,7 +16540,7 @@
         <v>P1132</v>
       </c>
     </row>
-    <row r="516" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:8">
       <c r="A516" s="1">
         <v>578</v>
       </c>
@@ -16462,7 +16564,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="517" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:8">
       <c r="A517" s="1">
         <v>579</v>
       </c>
@@ -16486,7 +16588,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="518" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:8">
       <c r="A518" s="1">
         <v>580</v>
       </c>
@@ -16510,7 +16612,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="519" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:8">
       <c r="A519" s="1">
         <v>581</v>
       </c>
@@ -16534,7 +16636,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="520" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:8">
       <c r="A520" s="1">
         <v>582</v>
       </c>
@@ -16558,7 +16660,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="521" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:8">
       <c r="A521" s="1">
         <v>583</v>
       </c>
@@ -16582,7 +16684,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="522" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:8">
       <c r="A522" s="1">
         <v>584</v>
       </c>
@@ -16606,7 +16708,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="523" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:8">
       <c r="A523" s="1">
         <v>585</v>
       </c>
@@ -16630,7 +16732,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="524" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:8">
       <c r="A524" s="1">
         <v>586</v>
       </c>
@@ -16654,7 +16756,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="525" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:8">
       <c r="A525" s="1">
         <v>587</v>
       </c>
@@ -16678,7 +16780,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="526" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:8">
       <c r="A526" s="1">
         <v>588</v>
       </c>
@@ -16702,7 +16804,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="527" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:8">
       <c r="A527" s="1">
         <v>589</v>
       </c>
@@ -16726,7 +16828,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="528" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:8">
       <c r="A528" s="1">
         <v>590</v>
       </c>
@@ -16750,7 +16852,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="529" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:8">
       <c r="A529" s="1">
         <v>591</v>
       </c>
@@ -16774,7 +16876,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="530" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:8">
       <c r="A530" s="1">
         <v>592</v>
       </c>
@@ -16798,7 +16900,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="531" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:8">
       <c r="A531" s="1">
         <v>593</v>
       </c>
@@ -16822,7 +16924,7 @@
         <v>P1133</v>
       </c>
     </row>
-    <row r="532" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:8">
       <c r="A532" s="1">
         <v>594</v>
       </c>
@@ -16846,7 +16948,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="533" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:8">
       <c r="A533" s="1">
         <v>595</v>
       </c>
@@ -16870,7 +16972,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="534" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:8">
       <c r="A534" s="1">
         <v>596</v>
       </c>
@@ -16894,7 +16996,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="535" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:8">
       <c r="A535" s="1">
         <v>597</v>
       </c>
@@ -16918,7 +17020,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="536" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:8">
       <c r="A536" s="1">
         <v>598</v>
       </c>
@@ -16942,7 +17044,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="537" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:8">
       <c r="A537" s="1">
         <v>599</v>
       </c>
@@ -16966,7 +17068,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="538" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:8">
       <c r="A538" s="1">
         <v>600</v>
       </c>
@@ -16990,7 +17092,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="539" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:8">
       <c r="A539" s="1">
         <v>601</v>
       </c>
@@ -17014,7 +17116,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="540" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:8">
       <c r="A540" s="1">
         <v>602</v>
       </c>
@@ -17038,7 +17140,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="541" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:8">
       <c r="A541" s="1">
         <v>603</v>
       </c>
@@ -17062,7 +17164,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="542" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:8">
       <c r="A542" s="1">
         <v>604</v>
       </c>
@@ -17086,7 +17188,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="543" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:8">
       <c r="A543" s="1">
         <v>605</v>
       </c>
@@ -17110,7 +17212,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="544" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:8">
       <c r="A544" s="1">
         <v>606</v>
       </c>
@@ -17134,7 +17236,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="545" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:8">
       <c r="A545" s="1">
         <v>607</v>
       </c>
@@ -17158,7 +17260,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="546" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:8">
       <c r="A546" s="1">
         <v>608</v>
       </c>
@@ -17182,7 +17284,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="547" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:8">
       <c r="A547" s="1">
         <v>609</v>
       </c>
@@ -17206,7 +17308,7 @@
         <v>P1134</v>
       </c>
     </row>
-    <row r="548" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:8">
       <c r="A548" s="1">
         <v>610</v>
       </c>
@@ -17230,7 +17332,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="549" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:8">
       <c r="A549" s="1">
         <v>611</v>
       </c>
@@ -17254,7 +17356,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="550" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:8">
       <c r="A550" s="1">
         <v>612</v>
       </c>
@@ -17278,7 +17380,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="551" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:8">
       <c r="A551" s="1">
         <v>613</v>
       </c>
@@ -17302,7 +17404,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="552" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:8">
       <c r="A552" s="1">
         <v>614</v>
       </c>
@@ -17326,7 +17428,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="553" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:8">
       <c r="A553" s="1">
         <v>615</v>
       </c>
@@ -17350,7 +17452,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="554" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:8">
       <c r="A554" s="1">
         <v>616</v>
       </c>
@@ -17374,7 +17476,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="555" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:8">
       <c r="A555" s="1">
         <v>617</v>
       </c>
@@ -17398,7 +17500,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="556" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:8">
       <c r="A556" s="1">
         <v>618</v>
       </c>
@@ -17422,7 +17524,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="557" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:8">
       <c r="A557" s="1">
         <v>619</v>
       </c>
@@ -17446,7 +17548,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="558" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:8">
       <c r="A558" s="1">
         <v>620</v>
       </c>
@@ -17470,7 +17572,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="559" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:8">
       <c r="A559" s="1">
         <v>621</v>
       </c>
@@ -17494,7 +17596,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="560" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:8">
       <c r="A560" s="1">
         <v>622</v>
       </c>
@@ -17518,7 +17620,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="561" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:8">
       <c r="A561" s="1">
         <v>623</v>
       </c>
@@ -17542,7 +17644,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="562" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:8">
       <c r="A562" s="1">
         <v>624</v>
       </c>
@@ -17566,7 +17668,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="563" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:8">
       <c r="A563" s="1">
         <v>625</v>
       </c>
@@ -17590,7 +17692,7 @@
         <v>P1135</v>
       </c>
     </row>
-    <row r="564" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:8">
       <c r="A564" s="1">
         <v>626</v>
       </c>
@@ -17614,7 +17716,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="565" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:8">
       <c r="A565" s="1">
         <v>627</v>
       </c>
@@ -17638,7 +17740,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="566" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:8">
       <c r="A566" s="1">
         <v>628</v>
       </c>
@@ -17662,7 +17764,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="567" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:8">
       <c r="A567" s="1">
         <v>629</v>
       </c>
@@ -17686,7 +17788,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="568" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:8">
       <c r="A568" s="1">
         <v>630</v>
       </c>
@@ -17710,7 +17812,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="569" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:8">
       <c r="A569" s="1">
         <v>631</v>
       </c>
@@ -17734,7 +17836,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="570" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:8">
       <c r="A570" s="1">
         <v>632</v>
       </c>
@@ -17758,7 +17860,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="571" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:8">
       <c r="A571" s="1">
         <v>633</v>
       </c>
@@ -17782,7 +17884,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="572" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:8">
       <c r="A572" s="1">
         <v>634</v>
       </c>
@@ -17806,7 +17908,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="573" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:8">
       <c r="A573" s="1">
         <v>635</v>
       </c>
@@ -17830,7 +17932,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="574" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:8">
       <c r="A574" s="1">
         <v>636</v>
       </c>
@@ -17854,7 +17956,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="575" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:8">
       <c r="A575" s="1">
         <v>637</v>
       </c>
@@ -17878,7 +17980,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="576" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:8">
       <c r="A576" s="1">
         <v>638</v>
       </c>
@@ -17902,7 +18004,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="577" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:9">
       <c r="A577" s="1">
         <v>639</v>
       </c>
@@ -17926,7 +18028,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="578" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:9" ht="14.4">
       <c r="A578" s="1">
         <v>640</v>
       </c>
@@ -17951,7 +18053,7 @@
       </c>
       <c r="I578" s="4"/>
     </row>
-    <row r="579" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:9" ht="14.4">
       <c r="A579" s="1">
         <v>641</v>
       </c>
@@ -17976,7 +18078,7 @@
       </c>
       <c r="I579" s="4"/>
     </row>
-    <row r="580" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:9" ht="14.4">
       <c r="A580" s="1">
         <v>642</v>
       </c>
@@ -18001,7 +18103,7 @@
       </c>
       <c r="I580" s="4"/>
     </row>
-    <row r="581" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:9" ht="14.4">
       <c r="A581" s="1">
         <v>643</v>
       </c>
@@ -18026,7 +18128,7 @@
       </c>
       <c r="I581" s="4"/>
     </row>
-    <row r="582" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:9" ht="14.4">
       <c r="A582" s="1">
         <v>644</v>
       </c>
@@ -18051,7 +18153,7 @@
       </c>
       <c r="I582" s="4"/>
     </row>
-    <row r="583" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:9" ht="14.4">
       <c r="A583" s="1">
         <v>645</v>
       </c>
@@ -18076,7 +18178,7 @@
       </c>
       <c r="I583" s="4"/>
     </row>
-    <row r="584" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:9" ht="14.4">
       <c r="A584" s="1">
         <v>646</v>
       </c>
@@ -18101,7 +18203,7 @@
       </c>
       <c r="I584" s="4"/>
     </row>
-    <row r="585" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:9" ht="14.4">
       <c r="A585" s="1">
         <v>647</v>
       </c>
@@ -18126,7 +18228,7 @@
       </c>
       <c r="I585" s="4"/>
     </row>
-    <row r="586" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:9" ht="14.4">
       <c r="A586" s="1">
         <v>648</v>
       </c>
@@ -18151,7 +18253,7 @@
       </c>
       <c r="I586" s="4"/>
     </row>
-    <row r="587" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:9" ht="14.4">
       <c r="A587" s="1">
         <v>649</v>
       </c>
@@ -18176,7 +18278,7 @@
       </c>
       <c r="I587" s="4"/>
     </row>
-    <row r="588" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:9" ht="14.4">
       <c r="A588" s="1">
         <v>650</v>
       </c>
@@ -18201,7 +18303,7 @@
       </c>
       <c r="I588" s="4"/>
     </row>
-    <row r="589" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:9" ht="14.4">
       <c r="A589" s="1">
         <v>651</v>
       </c>
@@ -18226,7 +18328,7 @@
       </c>
       <c r="I589" s="4"/>
     </row>
-    <row r="590" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:9" ht="14.4">
       <c r="A590" s="1">
         <v>652</v>
       </c>
@@ -18253,7 +18355,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="591" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:9" ht="14.4">
       <c r="A591" s="1">
         <v>653</v>
       </c>
@@ -18280,7 +18382,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="592" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:9" ht="14.4">
       <c r="A592" s="1">
         <v>654</v>
       </c>
@@ -18307,7 +18409,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="593" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:10" ht="14.4">
       <c r="A593" s="1">
         <v>655</v>
       </c>
@@ -18330,11 +18432,11 @@
         <f t="shared" si="44"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I593" s="4" t="s">
+      <c r="I593" s="14" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="594" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:10" ht="14.4">
       <c r="A594" s="1">
         <v>656</v>
       </c>
@@ -18357,11 +18459,11 @@
         <f t="shared" si="44"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I594" s="4" t="s">
+      <c r="I594" s="14" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="595" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:10" ht="14.4">
       <c r="A595" s="1">
         <v>657</v>
       </c>
@@ -18388,7 +18490,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="596" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:10">
       <c r="A596" s="1">
         <v>658</v>
       </c>
@@ -18412,7 +18514,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="597" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:10" ht="14.4">
       <c r="A597" s="1">
         <v>659</v>
       </c>
@@ -18439,7 +18541,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="598" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:10">
       <c r="A598" s="1">
         <v>660</v>
       </c>
@@ -18463,7 +18565,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="599" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:10" ht="14.4">
       <c r="A599" s="1">
         <v>661</v>
       </c>
@@ -18486,11 +18588,14 @@
         <f t="shared" si="44"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I599" s="4" t="s">
+      <c r="I599" s="14" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="600" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J599" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="600" spans="1:10">
       <c r="A600" s="1">
         <v>662</v>
       </c>
@@ -18514,7 +18619,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="601" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:10" ht="14.4">
       <c r="A601" s="1">
         <v>663</v>
       </c>
@@ -18537,11 +18642,14 @@
         <f t="shared" si="44"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I601" s="4" t="s">
+      <c r="I601" s="14" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="602" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J601" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="602" spans="1:10">
       <c r="A602" s="1">
         <v>664</v>
       </c>
@@ -18565,7 +18673,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="603" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:10" ht="14.4">
       <c r="A603" s="1">
         <v>665</v>
       </c>
@@ -18592,7 +18700,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="604" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:10">
       <c r="A604" s="1">
         <v>666</v>
       </c>
@@ -18616,7 +18724,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="605" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:10">
       <c r="A605" s="1">
         <v>667</v>
       </c>
@@ -18640,7 +18748,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="606" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:10">
       <c r="A606" s="1">
         <v>668</v>
       </c>
@@ -18664,7 +18772,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="607" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:10">
       <c r="A607" s="1">
         <v>669</v>
       </c>
@@ -18688,7 +18796,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="608" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:10">
       <c r="A608" s="1">
         <v>670</v>
       </c>
@@ -18712,7 +18820,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="609" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:9">
       <c r="A609" s="1">
         <v>671</v>
       </c>
@@ -18736,7 +18844,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="610" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:9">
       <c r="A610" s="1">
         <v>672</v>
       </c>
@@ -18760,7 +18868,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="611" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:9" ht="14.4">
       <c r="A611" s="1">
         <v>673</v>
       </c>
@@ -18787,7 +18895,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="612" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:9">
       <c r="A612" s="1">
         <v>674</v>
       </c>
@@ -18811,7 +18919,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="613" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:9">
       <c r="A613" s="1">
         <v>675</v>
       </c>
@@ -18835,7 +18943,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="614" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:9">
       <c r="A614" s="1">
         <v>676</v>
       </c>
@@ -18859,7 +18967,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="615" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:9">
       <c r="A615" s="1">
         <v>677</v>
       </c>
@@ -18883,7 +18991,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="616" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:9">
       <c r="A616" s="1">
         <v>678</v>
       </c>
@@ -18907,7 +19015,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="617" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:9">
       <c r="A617" s="1">
         <v>679</v>
       </c>
@@ -18931,7 +19039,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="618" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:9">
       <c r="A618" s="1">
         <v>680</v>
       </c>
@@ -18955,7 +19063,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="619" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:9">
       <c r="A619" s="1">
         <v>681</v>
       </c>
@@ -18979,7 +19087,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="620" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:9">
       <c r="A620" s="1">
         <v>682</v>
       </c>
@@ -19003,7 +19111,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="621" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:9">
       <c r="A621" s="1">
         <v>683</v>
       </c>
@@ -19027,7 +19135,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="622" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:9">
       <c r="A622" s="1">
         <v>684</v>
       </c>
@@ -19051,7 +19159,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="623" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:9">
       <c r="A623" s="1">
         <v>685</v>
       </c>
@@ -19075,7 +19183,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="624" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:9">
       <c r="A624" s="1">
         <v>686</v>
       </c>
@@ -19099,7 +19207,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="625" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:9">
       <c r="A625" s="1">
         <v>687</v>
       </c>
@@ -19123,7 +19231,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="626" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:9">
       <c r="A626" s="1">
         <v>688</v>
       </c>
@@ -19147,7 +19255,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="627" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:9" ht="14.4">
       <c r="A627" s="1">
         <v>689</v>
       </c>
@@ -19174,7 +19282,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="628" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:9">
       <c r="A628" s="1">
         <v>690</v>
       </c>
@@ -19198,7 +19306,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="629" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:9">
       <c r="A629" s="1">
         <v>691</v>
       </c>
@@ -19222,7 +19330,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="630" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:9">
       <c r="A630" s="1">
         <v>692</v>
       </c>
@@ -19246,7 +19354,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="631" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:9">
       <c r="A631" s="1">
         <v>693</v>
       </c>
@@ -19270,7 +19378,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="632" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:9">
       <c r="A632" s="1">
         <v>694</v>
       </c>
@@ -19294,7 +19402,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="633" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:9">
       <c r="A633" s="1">
         <v>695</v>
       </c>
@@ -19318,7 +19426,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="634" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:9">
       <c r="A634" s="1">
         <v>696</v>
       </c>
@@ -19342,7 +19450,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="635" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:9">
       <c r="A635" s="1">
         <v>697</v>
       </c>
@@ -19366,7 +19474,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="636" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:9">
       <c r="A636" s="1">
         <v>698</v>
       </c>
@@ -19390,7 +19498,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="637" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:9">
       <c r="A637" s="1">
         <v>699</v>
       </c>
@@ -19414,7 +19522,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="638" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:9">
       <c r="A638" s="1">
         <v>700</v>
       </c>
@@ -19438,7 +19546,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="639" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:9">
       <c r="A639" s="1">
         <v>701</v>
       </c>
@@ -19462,7 +19570,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="640" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:9">
       <c r="A640" s="1">
         <v>702</v>
       </c>
@@ -19486,7 +19594,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="641" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:9">
       <c r="A641" s="1">
         <v>703</v>
       </c>
@@ -19510,7 +19618,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="642" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:9">
       <c r="A642" s="1">
         <v>704</v>
       </c>
@@ -19534,7 +19642,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="643" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:9" ht="14.4">
       <c r="A643" s="1">
         <v>705</v>
       </c>
@@ -19561,7 +19669,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="644" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:9">
       <c r="A644" s="1">
         <v>706</v>
       </c>
@@ -19585,7 +19693,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="645" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:9">
       <c r="A645" s="1">
         <v>707</v>
       </c>
@@ -19609,7 +19717,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="646" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:9">
       <c r="A646" s="1">
         <v>708</v>
       </c>
@@ -19633,7 +19741,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="647" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:9">
       <c r="A647" s="1">
         <v>709</v>
       </c>
@@ -19657,7 +19765,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="648" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:9">
       <c r="A648" s="1">
         <v>710</v>
       </c>
@@ -19681,7 +19789,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="649" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:9">
       <c r="A649" s="1">
         <v>711</v>
       </c>
@@ -19705,7 +19813,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="650" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:9">
       <c r="A650" s="1">
         <v>712</v>
       </c>
@@ -19729,7 +19837,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="651" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:9">
       <c r="A651" s="1">
         <v>713</v>
       </c>
@@ -19753,7 +19861,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="652" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:9">
       <c r="A652" s="1">
         <v>714</v>
       </c>
@@ -19777,7 +19885,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="653" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:9">
       <c r="A653" s="1">
         <v>715</v>
       </c>
@@ -19801,7 +19909,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="654" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:9">
       <c r="A654" s="1">
         <v>716</v>
       </c>
@@ -19825,7 +19933,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="655" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:9">
       <c r="A655" s="1">
         <v>717</v>
       </c>
@@ -19849,7 +19957,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="656" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:9">
       <c r="A656" s="1">
         <v>718</v>
       </c>
@@ -19873,7 +19981,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="657" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:9">
       <c r="A657" s="1">
         <v>719</v>
       </c>
@@ -19897,7 +20005,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="658" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:9">
       <c r="A658" s="1">
         <v>720</v>
       </c>
@@ -19921,7 +20029,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="659" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:9" ht="14.4">
       <c r="A659" s="1">
         <v>721</v>
       </c>
@@ -19948,7 +20056,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="660" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:9">
       <c r="A660" s="1">
         <v>722</v>
       </c>
@@ -19972,7 +20080,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="661" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:9">
       <c r="A661" s="1">
         <v>723</v>
       </c>
@@ -19996,7 +20104,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="662" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:9">
       <c r="A662" s="1">
         <v>724</v>
       </c>
@@ -20020,7 +20128,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="663" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:9">
       <c r="A663" s="1">
         <v>725</v>
       </c>
@@ -20044,7 +20152,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="664" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:9">
       <c r="A664" s="1">
         <v>726</v>
       </c>
@@ -20068,7 +20176,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="665" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:9">
       <c r="A665" s="1">
         <v>727</v>
       </c>
@@ -20092,7 +20200,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="666" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:9">
       <c r="A666" s="1">
         <v>728</v>
       </c>
@@ -20116,7 +20224,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="667" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:9">
       <c r="A667" s="1">
         <v>729</v>
       </c>
@@ -20140,7 +20248,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="668" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:9">
       <c r="A668" s="1">
         <v>730</v>
       </c>
@@ -20164,7 +20272,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="669" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:9">
       <c r="A669" s="1">
         <v>731</v>
       </c>
@@ -20188,7 +20296,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="670" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:9">
       <c r="A670" s="1">
         <v>732</v>
       </c>
@@ -20212,7 +20320,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="671" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:9">
       <c r="A671" s="1">
         <v>733</v>
       </c>
@@ -20236,7 +20344,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="672" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:9">
       <c r="A672" s="1">
         <v>734</v>
       </c>
@@ -20260,7 +20368,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="673" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:9">
       <c r="A673" s="1">
         <v>735</v>
       </c>
@@ -20284,7 +20392,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="674" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:9">
       <c r="A674" s="1">
         <v>736</v>
       </c>
@@ -20308,7 +20416,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="675" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:9" ht="14.4">
       <c r="A675" s="1">
         <v>737</v>
       </c>
@@ -20335,7 +20443,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="676" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:9">
       <c r="A676" s="1">
         <v>738</v>
       </c>
@@ -20359,7 +20467,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="677" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:9">
       <c r="A677" s="1">
         <v>739</v>
       </c>
@@ -20383,7 +20491,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="678" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:9">
       <c r="A678" s="1">
         <v>740</v>
       </c>
@@ -20407,7 +20515,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="679" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:9">
       <c r="A679" s="1">
         <v>741</v>
       </c>
@@ -20431,7 +20539,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="680" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:9">
       <c r="A680" s="1">
         <v>742</v>
       </c>
@@ -20455,7 +20563,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="681" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:9">
       <c r="A681" s="1">
         <v>743</v>
       </c>
@@ -20479,7 +20587,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="682" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:9">
       <c r="A682" s="1">
         <v>744</v>
       </c>
@@ -20503,7 +20611,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="683" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:9">
       <c r="A683" s="1">
         <v>745</v>
       </c>
@@ -20527,7 +20635,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="684" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:9">
       <c r="A684" s="1">
         <v>746</v>
       </c>
@@ -20551,7 +20659,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="685" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:9">
       <c r="A685" s="1">
         <v>747</v>
       </c>
@@ -20575,7 +20683,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="686" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:9">
       <c r="A686" s="1">
         <v>748</v>
       </c>
@@ -20599,7 +20707,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="687" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:9">
       <c r="A687" s="1">
         <v>749</v>
       </c>
@@ -20623,7 +20731,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="688" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:9">
       <c r="A688" s="1">
         <v>750</v>
       </c>
@@ -20647,7 +20755,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="689" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:9">
       <c r="A689" s="1">
         <v>751</v>
       </c>
@@ -20671,7 +20779,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="690" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:9">
       <c r="A690" s="1">
         <v>752</v>
       </c>
@@ -20695,7 +20803,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="691" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:9" ht="14.4">
       <c r="A691" s="1">
         <v>753</v>
       </c>
@@ -20722,7 +20830,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="692" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:9">
       <c r="A692" s="1">
         <v>754</v>
       </c>
@@ -20746,7 +20854,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="693" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:9">
       <c r="A693" s="1">
         <v>755</v>
       </c>
@@ -20770,7 +20878,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="694" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:9">
       <c r="A694" s="1">
         <v>756</v>
       </c>
@@ -20794,7 +20902,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="695" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:9">
       <c r="A695" s="1">
         <v>757</v>
       </c>
@@ -20818,7 +20926,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="696" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:9">
       <c r="A696" s="1">
         <v>758</v>
       </c>
@@ -20842,7 +20950,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="697" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:9">
       <c r="A697" s="1">
         <v>759</v>
       </c>
@@ -20866,7 +20974,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="698" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:9">
       <c r="A698" s="1">
         <v>760</v>
       </c>
@@ -20890,7 +20998,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="699" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:9" ht="14.4">
       <c r="A699" s="1">
         <v>761</v>
       </c>
@@ -20917,7 +21025,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="700" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:9">
       <c r="A700" s="1">
         <v>762</v>
       </c>
@@ -20941,7 +21049,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="701" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:9">
       <c r="A701" s="1">
         <v>763</v>
       </c>
@@ -20965,7 +21073,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="702" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:9">
       <c r="A702" s="1">
         <v>764</v>
       </c>
@@ -20989,7 +21097,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="703" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:9">
       <c r="A703" s="1">
         <v>765</v>
       </c>
@@ -21013,7 +21121,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="704" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:9">
       <c r="A704" s="1">
         <v>766</v>
       </c>
@@ -21037,7 +21145,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="705" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:9">
       <c r="A705" s="1">
         <v>767</v>
       </c>
@@ -21061,7 +21169,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="706" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:9">
       <c r="A706" s="1">
         <v>768</v>
       </c>
@@ -21085,7 +21193,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="707" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:9" ht="14.4">
       <c r="A707" s="1">
         <v>769</v>
       </c>
@@ -21112,7 +21220,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="708" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:9">
       <c r="A708" s="1">
         <v>770</v>
       </c>
@@ -21136,7 +21244,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="709" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:9">
       <c r="A709" s="1">
         <v>771</v>
       </c>
@@ -21160,7 +21268,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="710" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:9">
       <c r="A710" s="1">
         <v>772</v>
       </c>
@@ -21184,7 +21292,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="711" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:9">
       <c r="A711" s="1">
         <v>773</v>
       </c>
@@ -21208,7 +21316,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="712" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:9">
       <c r="A712" s="1">
         <v>774</v>
       </c>
@@ -21232,7 +21340,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="713" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:9">
       <c r="A713" s="1">
         <v>775</v>
       </c>
@@ -21256,7 +21364,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="714" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:9">
       <c r="A714" s="1">
         <v>776</v>
       </c>
@@ -21280,7 +21388,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="715" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:9" ht="14.4">
       <c r="A715" s="1">
         <v>777</v>
       </c>
@@ -21307,7 +21415,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="716" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:9">
       <c r="A716" s="1">
         <v>778</v>
       </c>
@@ -21331,7 +21439,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="717" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:9">
       <c r="A717" s="1">
         <v>779</v>
       </c>
@@ -21355,7 +21463,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="718" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:9">
       <c r="A718" s="1">
         <v>780</v>
       </c>
@@ -21379,7 +21487,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="719" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:9">
       <c r="A719" s="1">
         <v>781</v>
       </c>
@@ -21403,7 +21511,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="720" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:9">
       <c r="A720" s="1">
         <v>782</v>
       </c>
@@ -21427,7 +21535,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="721" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:9">
       <c r="A721" s="1">
         <v>783</v>
       </c>
@@ -21451,7 +21559,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="722" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:9">
       <c r="A722" s="1">
         <v>784</v>
       </c>
@@ -21475,7 +21583,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="723" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:9" ht="14.4">
       <c r="A723" s="1">
         <v>785</v>
       </c>
@@ -21502,7 +21610,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="724" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:9">
       <c r="A724" s="1">
         <v>786</v>
       </c>
@@ -21526,7 +21634,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="725" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:9">
       <c r="A725" s="1">
         <v>787</v>
       </c>
@@ -21550,7 +21658,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="726" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:9">
       <c r="A726" s="1">
         <v>788</v>
       </c>
@@ -21574,7 +21682,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="727" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:9">
       <c r="A727" s="1">
         <v>789</v>
       </c>
@@ -21598,7 +21706,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="728" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:9">
       <c r="A728" s="1">
         <v>790</v>
       </c>
@@ -21622,7 +21730,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="729" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:9">
       <c r="A729" s="1">
         <v>791</v>
       </c>
@@ -21646,7 +21754,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="730" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:9">
       <c r="A730" s="1">
         <v>792</v>
       </c>
@@ -21670,7 +21778,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="731" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:9">
       <c r="A731" s="1">
         <v>793</v>
       </c>
@@ -21694,7 +21802,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="732" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:9">
       <c r="A732" s="1">
         <v>794</v>
       </c>
@@ -21718,7 +21826,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="733" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:9">
       <c r="A733" s="1">
         <v>795</v>
       </c>
@@ -21742,7 +21850,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="734" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:9">
       <c r="A734" s="1">
         <v>796</v>
       </c>
@@ -21766,7 +21874,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="735" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:9">
       <c r="A735" s="1">
         <v>797</v>
       </c>
@@ -21790,7 +21898,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="736" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:9">
       <c r="A736" s="1">
         <v>798</v>
       </c>
@@ -21814,7 +21922,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="737" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:9">
       <c r="A737" s="1">
         <v>799</v>
       </c>
@@ -21838,7 +21946,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="738" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:9">
       <c r="A738" s="1">
         <v>800</v>
       </c>
@@ -21862,7 +21970,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="739" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:9" ht="14.4">
       <c r="A739" s="1">
         <v>801</v>
       </c>
@@ -21889,7 +21997,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="740" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:9">
       <c r="A740" s="1">
         <v>802</v>
       </c>
@@ -21913,7 +22021,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="741" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:9">
       <c r="A741" s="1">
         <v>803</v>
       </c>
@@ -21937,7 +22045,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="742" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:9">
       <c r="A742" s="1">
         <v>804</v>
       </c>
@@ -21961,7 +22069,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="743" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:9">
       <c r="A743" s="1">
         <v>805</v>
       </c>
@@ -21985,7 +22093,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="744" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:9">
       <c r="A744" s="1">
         <v>806</v>
       </c>
@@ -22009,7 +22117,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="745" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:9">
       <c r="A745" s="1">
         <v>807</v>
       </c>
@@ -22033,7 +22141,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="746" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:9">
       <c r="A746" s="1">
         <v>808</v>
       </c>
@@ -22057,7 +22165,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="747" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:9">
       <c r="A747" s="1">
         <v>809</v>
       </c>
@@ -22081,7 +22189,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="748" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:9">
       <c r="A748" s="1">
         <v>810</v>
       </c>
@@ -22105,7 +22213,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="749" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:9">
       <c r="A749" s="1">
         <v>811</v>
       </c>
@@ -22129,7 +22237,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="750" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:9">
       <c r="A750" s="1">
         <v>812</v>
       </c>
@@ -22153,7 +22261,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="751" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:9">
       <c r="A751" s="1">
         <v>813</v>
       </c>
@@ -22177,7 +22285,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="752" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:9">
       <c r="A752" s="1">
         <v>814</v>
       </c>
@@ -22201,7 +22309,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="753" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:9">
       <c r="A753" s="1">
         <v>815</v>
       </c>
@@ -22225,7 +22333,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="754" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:9">
       <c r="A754" s="1">
         <v>816</v>
       </c>
@@ -22249,7 +22357,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="755" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:9" ht="14.4">
       <c r="A755" s="1">
         <v>817</v>
       </c>
@@ -22276,7 +22384,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="756" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:9">
       <c r="A756" s="1">
         <v>818</v>
       </c>
@@ -22300,7 +22408,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="757" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:9">
       <c r="A757" s="1">
         <v>819</v>
       </c>
@@ -22324,7 +22432,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="758" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:9">
       <c r="A758" s="1">
         <v>820</v>
       </c>
@@ -22348,7 +22456,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="759" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:9">
       <c r="A759" s="1">
         <v>821</v>
       </c>
@@ -22372,7 +22480,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="760" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:9">
       <c r="A760" s="1">
         <v>822</v>
       </c>
@@ -22396,7 +22504,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="761" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:9">
       <c r="A761" s="1">
         <v>823</v>
       </c>
@@ -22420,7 +22528,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="762" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:9">
       <c r="A762" s="1">
         <v>824</v>
       </c>
@@ -22444,7 +22552,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="763" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:9">
       <c r="A763" s="1">
         <v>825</v>
       </c>
@@ -22468,7 +22576,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="764" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:9">
       <c r="A764" s="1">
         <v>826</v>
       </c>
@@ -22492,7 +22600,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="765" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:9">
       <c r="A765" s="1">
         <v>827</v>
       </c>
@@ -22516,7 +22624,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="766" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:9">
       <c r="A766" s="1">
         <v>828</v>
       </c>
@@ -22540,7 +22648,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="767" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:9">
       <c r="A767" s="1">
         <v>829</v>
       </c>
@@ -22564,7 +22672,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="768" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:9">
       <c r="A768" s="1">
         <v>830</v>
       </c>
@@ -22588,7 +22696,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="769" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:9">
       <c r="A769" s="1">
         <v>831</v>
       </c>
@@ -22612,7 +22720,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="770" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:9">
       <c r="A770" s="1">
         <v>832</v>
       </c>
@@ -22636,7 +22744,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="771" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:9" ht="14.4">
       <c r="A771" s="1">
         <v>833</v>
       </c>
@@ -22663,7 +22771,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="772" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:9">
       <c r="A772" s="1">
         <v>834</v>
       </c>
@@ -22687,7 +22795,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="773" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:9">
       <c r="A773" s="1">
         <v>835</v>
       </c>
@@ -22711,7 +22819,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="774" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:9">
       <c r="A774" s="1">
         <v>836</v>
       </c>
@@ -22735,7 +22843,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="775" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:9">
       <c r="A775" s="1">
         <v>837</v>
       </c>
@@ -22759,7 +22867,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="776" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:9">
       <c r="A776" s="1">
         <v>838</v>
       </c>
@@ -22783,7 +22891,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="777" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:9">
       <c r="A777" s="1">
         <v>839</v>
       </c>
@@ -22807,7 +22915,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="778" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:9">
       <c r="A778" s="1">
         <v>840</v>
       </c>
@@ -22831,7 +22939,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="779" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:9">
       <c r="A779" s="1">
         <v>841</v>
       </c>
@@ -22855,7 +22963,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="780" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:9">
       <c r="A780" s="1">
         <v>842</v>
       </c>
@@ -22879,7 +22987,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="781" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:9">
       <c r="A781" s="1">
         <v>843</v>
       </c>
@@ -22903,7 +23011,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="782" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:9">
       <c r="A782" s="1">
         <v>844</v>
       </c>
@@ -22927,7 +23035,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="783" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:9">
       <c r="A783" s="1">
         <v>845</v>
       </c>
@@ -22951,7 +23059,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="784" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:9">
       <c r="A784" s="1">
         <v>846</v>
       </c>
@@ -22975,7 +23083,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="785" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:9">
       <c r="A785" s="1">
         <v>847</v>
       </c>
@@ -22999,7 +23107,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="786" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:9">
       <c r="A786" s="1">
         <v>848</v>
       </c>
@@ -23023,7 +23131,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="787" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:9" ht="14.4">
       <c r="A787" s="1">
         <v>849</v>
       </c>
@@ -23050,7 +23158,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="788" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:9">
       <c r="A788" s="1">
         <v>850</v>
       </c>
@@ -23074,7 +23182,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="789" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:9">
       <c r="A789" s="1">
         <v>851</v>
       </c>
@@ -23098,7 +23206,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="790" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:9">
       <c r="A790" s="1">
         <v>852</v>
       </c>
@@ -23122,7 +23230,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="791" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:9">
       <c r="A791" s="1">
         <v>853</v>
       </c>
@@ -23146,7 +23254,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="792" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:9">
       <c r="A792" s="1">
         <v>854</v>
       </c>
@@ -23170,7 +23278,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="793" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:9">
       <c r="A793" s="1">
         <v>855</v>
       </c>
@@ -23194,7 +23302,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="794" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:9">
       <c r="A794" s="1">
         <v>856</v>
       </c>
@@ -23218,7 +23326,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="795" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:9">
       <c r="A795" s="1">
         <v>857</v>
       </c>
@@ -23242,7 +23350,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="796" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:9">
       <c r="A796" s="1">
         <v>858</v>
       </c>
@@ -23266,7 +23374,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="797" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:9">
       <c r="A797" s="1">
         <v>859</v>
       </c>
@@ -23290,7 +23398,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="798" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:9">
       <c r="A798" s="1">
         <v>860</v>
       </c>
@@ -23314,7 +23422,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="799" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:9">
       <c r="A799" s="1">
         <v>861</v>
       </c>
@@ -23338,7 +23446,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="800" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:9">
       <c r="A800" s="1">
         <v>862</v>
       </c>
@@ -23362,7 +23470,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="801" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:9">
       <c r="A801" s="1">
         <v>863</v>
       </c>
@@ -23386,7 +23494,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="802" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:9">
       <c r="A802" s="1">
         <v>864</v>
       </c>
@@ -23410,7 +23518,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="803" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:9" ht="14.4">
       <c r="A803" s="1">
         <v>865</v>
       </c>
@@ -23437,7 +23545,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="804" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:9">
       <c r="A804" s="1">
         <v>866</v>
       </c>
@@ -23461,7 +23569,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="805" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:9">
       <c r="A805" s="1">
         <v>867</v>
       </c>
@@ -23485,7 +23593,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="806" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:9">
       <c r="A806" s="1">
         <v>868</v>
       </c>
@@ -23509,7 +23617,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="807" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:9">
       <c r="A807" s="1">
         <v>869</v>
       </c>
@@ -23533,7 +23641,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="808" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:9">
       <c r="A808" s="1">
         <v>870</v>
       </c>
@@ -23557,7 +23665,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="809" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:9">
       <c r="A809" s="1">
         <v>871</v>
       </c>
@@ -23581,7 +23689,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="810" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:9">
       <c r="A810" s="1">
         <v>872</v>
       </c>
@@ -23605,7 +23713,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="811" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:9">
       <c r="A811" s="1">
         <v>873</v>
       </c>
@@ -23629,7 +23737,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="812" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:9">
       <c r="A812" s="1">
         <v>874</v>
       </c>
@@ -23653,7 +23761,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="813" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:9">
       <c r="A813" s="1">
         <v>875</v>
       </c>
@@ -23677,7 +23785,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="814" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:9">
       <c r="A814" s="1">
         <v>876</v>
       </c>
@@ -23701,7 +23809,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="815" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:9">
       <c r="A815" s="1">
         <v>877</v>
       </c>
@@ -23725,7 +23833,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="816" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="816" spans="1:9">
       <c r="A816" s="1">
         <v>878</v>
       </c>
@@ -23749,7 +23857,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="817" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:9">
       <c r="A817" s="1">
         <v>879</v>
       </c>
@@ -23773,7 +23881,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="818" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:9">
       <c r="A818" s="1">
         <v>880</v>
       </c>
@@ -23797,7 +23905,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="819" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:9" ht="14.4">
       <c r="A819" s="1">
         <v>881</v>
       </c>
@@ -23824,7 +23932,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="820" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:9">
       <c r="A820" s="1">
         <v>882</v>
       </c>
@@ -23848,7 +23956,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="821" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:9">
       <c r="A821" s="1">
         <v>883</v>
       </c>
@@ -23872,7 +23980,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="822" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:9">
       <c r="A822" s="1">
         <v>884</v>
       </c>
@@ -23896,7 +24004,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="823" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:9">
       <c r="A823" s="1">
         <v>885</v>
       </c>
@@ -23920,7 +24028,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="824" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:9">
       <c r="A824" s="1">
         <v>886</v>
       </c>
@@ -23944,7 +24052,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="825" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:9">
       <c r="A825" s="1">
         <v>887</v>
       </c>
@@ -23968,7 +24076,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="826" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:9">
       <c r="A826" s="1">
         <v>888</v>
       </c>
@@ -23992,7 +24100,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="827" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:9">
       <c r="A827" s="1">
         <v>889</v>
       </c>
@@ -24016,7 +24124,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="828" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:9">
       <c r="A828" s="1">
         <v>890</v>
       </c>
@@ -24040,7 +24148,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="829" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:9">
       <c r="A829" s="1">
         <v>891</v>
       </c>
@@ -24064,7 +24172,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="830" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:9">
       <c r="A830" s="1">
         <v>892</v>
       </c>
@@ -24088,7 +24196,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="831" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:9">
       <c r="A831" s="1">
         <v>893</v>
       </c>
@@ -24112,7 +24220,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="832" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:9">
       <c r="A832" s="1">
         <v>894</v>
       </c>
@@ -24136,7 +24244,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="833" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="833" spans="1:9">
       <c r="A833" s="1">
         <v>895</v>
       </c>
@@ -24160,7 +24268,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="834" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="834" spans="1:9">
       <c r="A834" s="1">
         <v>896</v>
       </c>
@@ -24184,7 +24292,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="835" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="835" spans="1:9" ht="14.4">
       <c r="A835" s="1">
         <v>897</v>
       </c>
@@ -24211,7 +24319,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="836" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="836" spans="1:9">
       <c r="A836" s="1">
         <v>898</v>
       </c>
@@ -24235,7 +24343,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="837" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="837" spans="1:9">
       <c r="A837" s="1">
         <v>899</v>
       </c>
@@ -24259,7 +24367,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="838" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="838" spans="1:9">
       <c r="A838" s="1">
         <v>900</v>
       </c>
@@ -24283,7 +24391,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="839" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="839" spans="1:9">
       <c r="A839" s="1">
         <v>901</v>
       </c>
@@ -24307,7 +24415,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="840" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="840" spans="1:9">
       <c r="A840" s="1">
         <v>902</v>
       </c>
@@ -24331,7 +24439,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="841" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="841" spans="1:9">
       <c r="A841" s="1">
         <v>903</v>
       </c>
@@ -24355,7 +24463,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="842" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="842" spans="1:9">
       <c r="A842" s="1">
         <v>904</v>
       </c>
@@ -24379,7 +24487,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="843" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="843" spans="1:9">
       <c r="A843" s="1">
         <v>905</v>
       </c>
@@ -24403,7 +24511,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="844" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="844" spans="1:9">
       <c r="A844" s="1">
         <v>906</v>
       </c>
@@ -24427,7 +24535,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="845" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="845" spans="1:9">
       <c r="A845" s="1">
         <v>907</v>
       </c>
@@ -24451,7 +24559,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="846" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="846" spans="1:9">
       <c r="A846" s="1">
         <v>908</v>
       </c>
@@ -24475,7 +24583,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="847" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="847" spans="1:9">
       <c r="A847" s="1">
         <v>909</v>
       </c>
@@ -24499,7 +24607,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="848" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="848" spans="1:9">
       <c r="A848" s="1">
         <v>910</v>
       </c>
@@ -24523,7 +24631,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="849" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="849" spans="1:9">
       <c r="A849" s="1">
         <v>911</v>
       </c>
@@ -24547,7 +24655,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="850" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="850" spans="1:9">
       <c r="A850" s="1">
         <v>912</v>
       </c>
@@ -24571,7 +24679,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="851" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="851" spans="1:9" ht="14.4">
       <c r="A851" s="1">
         <v>913</v>
       </c>
@@ -24598,7 +24706,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="852" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="852" spans="1:9">
       <c r="A852" s="1">
         <v>914</v>
       </c>
@@ -24622,7 +24730,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="853" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="853" spans="1:9">
       <c r="A853" s="1">
         <v>915</v>
       </c>
@@ -24646,7 +24754,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="854" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="854" spans="1:9">
       <c r="A854" s="1">
         <v>916</v>
       </c>
@@ -24670,7 +24778,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="855" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="855" spans="1:9">
       <c r="A855" s="1">
         <v>917</v>
       </c>
@@ -24694,7 +24802,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="856" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="856" spans="1:9">
       <c r="A856" s="1">
         <v>918</v>
       </c>
@@ -24718,7 +24826,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="857" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="857" spans="1:9">
       <c r="A857" s="1">
         <v>919</v>
       </c>
@@ -24742,7 +24850,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="858" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="858" spans="1:9">
       <c r="A858" s="1">
         <v>920</v>
       </c>
@@ -24766,7 +24874,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="859" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="859" spans="1:9">
       <c r="A859" s="1">
         <v>921</v>
       </c>
@@ -24790,7 +24898,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="860" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="860" spans="1:9">
       <c r="A860" s="1">
         <v>922</v>
       </c>
@@ -24814,7 +24922,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="861" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="861" spans="1:9">
       <c r="A861" s="1">
         <v>923</v>
       </c>
@@ -24838,7 +24946,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="862" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="862" spans="1:9">
       <c r="A862" s="1">
         <v>924</v>
       </c>
@@ -24862,7 +24970,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="863" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="863" spans="1:9">
       <c r="A863" s="1">
         <v>925</v>
       </c>
@@ -24886,7 +24994,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="864" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="864" spans="1:9">
       <c r="A864" s="1">
         <v>926</v>
       </c>
@@ -24910,7 +25018,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="865" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="865" spans="1:9">
       <c r="A865" s="1">
         <v>927</v>
       </c>
@@ -24934,7 +25042,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="866" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="866" spans="1:9">
       <c r="A866" s="1">
         <v>928</v>
       </c>
@@ -24958,7 +25066,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="867" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="867" spans="1:9">
       <c r="A867" s="1">
         <v>929</v>
       </c>
@@ -24985,7 +25093,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="868" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="868" spans="1:9">
       <c r="A868" s="1">
         <v>930</v>
       </c>
@@ -25009,7 +25117,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="869" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="869" spans="1:9">
       <c r="A869" s="1">
         <v>931</v>
       </c>
@@ -25033,7 +25141,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="870" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="870" spans="1:9">
       <c r="A870" s="1">
         <v>932</v>
       </c>
@@ -25057,7 +25165,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="871" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="871" spans="1:9">
       <c r="A871" s="1">
         <v>933</v>
       </c>
@@ -25081,7 +25189,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="872" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="872" spans="1:9">
       <c r="A872" s="1">
         <v>934</v>
       </c>
@@ -25105,7 +25213,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="873" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="873" spans="1:9">
       <c r="A873" s="1">
         <v>935</v>
       </c>
@@ -25129,7 +25237,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="874" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="874" spans="1:9">
       <c r="A874" s="1">
         <v>936</v>
       </c>
@@ -25153,7 +25261,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="875" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="875" spans="1:9">
       <c r="A875" s="1">
         <v>937</v>
       </c>
@@ -25177,7 +25285,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="876" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="876" spans="1:9">
       <c r="A876" s="1">
         <v>938</v>
       </c>
@@ -25201,7 +25309,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="877" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="877" spans="1:9">
       <c r="A877" s="1">
         <v>939</v>
       </c>
@@ -25225,7 +25333,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="878" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="878" spans="1:9">
       <c r="A878" s="1">
         <v>940</v>
       </c>
@@ -25249,7 +25357,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="879" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="879" spans="1:9">
       <c r="A879" s="1">
         <v>941</v>
       </c>
@@ -25273,7 +25381,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="880" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="880" spans="1:9">
       <c r="A880" s="1">
         <v>942</v>
       </c>
@@ -25297,7 +25405,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="881" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="881" spans="1:9">
       <c r="A881" s="1">
         <v>943</v>
       </c>
@@ -25321,7 +25429,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="882" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="882" spans="1:9">
       <c r="A882" s="1">
         <v>944</v>
       </c>
@@ -25345,7 +25453,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="883" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="883" spans="1:9">
       <c r="A883" s="1">
         <v>945</v>
       </c>
@@ -25372,7 +25480,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="884" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="884" spans="1:9">
       <c r="A884" s="1">
         <v>946</v>
       </c>
@@ -25396,7 +25504,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="885" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="885" spans="1:9">
       <c r="A885" s="1">
         <v>947</v>
       </c>
@@ -25420,7 +25528,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="886" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="886" spans="1:9">
       <c r="A886" s="1">
         <v>948</v>
       </c>
@@ -25444,7 +25552,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="887" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="887" spans="1:9">
       <c r="A887" s="1">
         <v>949</v>
       </c>
@@ -25468,7 +25576,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="888" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="888" spans="1:9">
       <c r="A888" s="1">
         <v>950</v>
       </c>
@@ -25492,7 +25600,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="889" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="889" spans="1:9">
       <c r="A889" s="1">
         <v>951</v>
       </c>
@@ -25516,7 +25624,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="890" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="890" spans="1:9">
       <c r="A890" s="1">
         <v>952</v>
       </c>
@@ -25540,7 +25648,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="891" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="891" spans="1:9">
       <c r="A891" s="1">
         <v>953</v>
       </c>
@@ -25564,7 +25672,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="892" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="892" spans="1:9">
       <c r="A892" s="1">
         <v>954</v>
       </c>
@@ -25588,7 +25696,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="893" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="893" spans="1:9">
       <c r="A893" s="1">
         <v>955</v>
       </c>
@@ -25612,7 +25720,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="894" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="894" spans="1:9">
       <c r="A894" s="1">
         <v>956</v>
       </c>
@@ -25636,7 +25744,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="895" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="895" spans="1:9">
       <c r="A895" s="1">
         <v>957</v>
       </c>
@@ -25660,7 +25768,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="896" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="896" spans="1:9">
       <c r="A896" s="1">
         <v>958</v>
       </c>
@@ -25684,7 +25792,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="897" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="897" spans="1:8">
       <c r="A897" s="1">
         <v>959</v>
       </c>
@@ -25708,7 +25816,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="898" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="898" spans="1:8">
       <c r="A898" s="1">
         <v>960</v>
       </c>
@@ -25750,17 +25858,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B89C0430-D126-4193-BAE2-FD0F1DC784E3}">
   <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="21.44140625" customWidth="1"/>
-    <col min="2" max="2" width="50.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="24.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="39.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.8984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.8984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.09765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42.69921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15" thickBot="1">
       <c r="A1" s="11" t="s">
         <v>397</v>
       </c>
@@ -25772,7 +25880,7 @@
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="15" thickBot="1">
       <c r="A2" s="5" t="s">
         <v>10</v>
       </c>
@@ -25792,7 +25900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="14.4">
       <c r="A3" s="8" t="s">
         <v>398</v>
       </c>
@@ -25812,7 +25920,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="14.4">
       <c r="A4" s="2" t="s">
         <v>399</v>
       </c>
@@ -25832,7 +25940,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="14.4">
       <c r="A5" s="8" t="s">
         <v>400</v>
       </c>
@@ -25852,7 +25960,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="14.4">
       <c r="A6" s="2" t="s">
         <v>401</v>
       </c>
@@ -25872,7 +25980,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="14.4">
       <c r="A7" s="8" t="s">
         <v>402</v>
       </c>
@@ -25892,7 +26000,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="14.4">
       <c r="A8" s="2" t="s">
         <v>403</v>
       </c>
@@ -25912,7 +26020,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="14.4">
       <c r="A9" s="8" t="s">
         <v>404</v>
       </c>
@@ -25925,12 +26033,14 @@
       <c r="E9" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="F9" s="2"/>
+      <c r="F9" s="4" t="s">
+        <v>337</v>
+      </c>
       <c r="G9" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="14.4">
       <c r="A10" s="2" t="s">
         <v>405</v>
       </c>
@@ -25943,12 +26053,14 @@
       <c r="E10" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="F10" s="2"/>
+      <c r="F10" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="G10" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="14.4">
       <c r="A11" s="8" t="s">
         <v>406</v>
       </c>
@@ -25966,7 +26078,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="14.4">
       <c r="A12" s="2" t="s">
         <v>407</v>
       </c>
@@ -25984,7 +26096,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="14.4">
       <c r="A13" s="8" t="s">
         <v>408</v>
       </c>
@@ -26002,7 +26114,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="14.4">
       <c r="A14" s="2" t="s">
         <v>409</v>
       </c>
@@ -26020,7 +26132,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="14.4">
       <c r="A15" s="8" t="s">
         <v>410</v>
       </c>
@@ -26038,7 +26150,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="14.4">
       <c r="A16" s="2" t="s">
         <v>411</v>
       </c>
@@ -26056,7 +26168,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="14.4">
       <c r="A17" s="8" t="s">
         <v>412</v>
       </c>
@@ -26074,7 +26186,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="14.4">
       <c r="A18" s="2" t="s">
         <v>413</v>
       </c>
@@ -26090,7 +26202,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="14.4">
       <c r="A19" s="8" t="s">
         <v>414</v>
       </c>
@@ -26106,7 +26218,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="14.4">
       <c r="A20" s="2" t="s">
         <v>415</v>
       </c>
@@ -26124,7 +26236,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="14.4">
       <c r="A21" s="8" t="s">
         <v>416</v>
       </c>
@@ -26142,7 +26254,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="14.4">
       <c r="A22" s="2" t="s">
         <v>417</v>
       </c>
@@ -26160,7 +26272,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="14.4">
       <c r="A23" s="8" t="s">
         <v>418</v>
       </c>
@@ -26176,7 +26288,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="14.4">
       <c r="A24" s="2" t="s">
         <v>419</v>
       </c>
@@ -26192,11 +26304,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="43.2">
       <c r="A25" s="8" t="s">
         <v>420</v>
       </c>
-      <c r="B25" s="10"/>
+      <c r="B25" s="13" t="s">
+        <v>481</v>
+      </c>
       <c r="C25" s="9"/>
       <c r="E25" s="2" t="s">
         <v>460</v>
@@ -26206,7 +26320,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="14.4">
       <c r="A26" s="2" t="s">
         <v>421</v>
       </c>
@@ -26220,7 +26334,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="14.4">
       <c r="A27" s="8" t="s">
         <v>422</v>
       </c>
@@ -26234,7 +26348,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="14.4">
       <c r="A28" s="2" t="s">
         <v>423</v>
       </c>
@@ -26248,7 +26362,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="14.4">
       <c r="A29" s="8" t="s">
         <v>424</v>
       </c>
@@ -26262,7 +26376,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="14.4">
       <c r="A30" s="2" t="s">
         <v>425</v>
       </c>
@@ -26276,7 +26390,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="14.4">
       <c r="A31" s="8" t="s">
         <v>426</v>
       </c>
@@ -26290,7 +26404,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="14.4">
       <c r="A32" s="2" t="s">
         <v>427</v>
       </c>
@@ -26304,7 +26418,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="14.4">
       <c r="A33" s="8" t="s">
         <v>428</v>
       </c>
@@ -26318,7 +26432,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="14.4">
       <c r="A34" s="2" t="s">
         <v>429</v>
       </c>
@@ -26332,7 +26446,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="14.4">
       <c r="A35" s="8" t="s">
         <v>430</v>
       </c>
@@ -26363,16 +26477,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA144AF3-4E40-4942-9302-D3CD0ABECF4D}">
   <dimension ref="A1:E54"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="18.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.3984375" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="35" style="4" customWidth="1"/>
-    <col min="5" max="16384" width="9.109375" style="4"/>
+    <col min="5" max="16384" width="9.09765625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15" thickBot="1">
       <c r="A1" s="5" t="s">
         <v>373</v>
       </c>
@@ -26389,7 +26503,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -26406,7 +26520,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -26423,7 +26537,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -26440,7 +26554,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -26457,7 +26571,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -26474,7 +26588,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -26491,7 +26605,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -26508,7 +26622,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -26525,7 +26639,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -26542,7 +26656,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -26559,7 +26673,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -26576,7 +26690,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -26590,7 +26704,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -26601,7 +26715,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -26615,7 +26729,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -26626,7 +26740,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -26640,7 +26754,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -26657,7 +26771,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -26674,7 +26788,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -26691,7 +26805,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -26708,7 +26822,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -26722,7 +26836,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -26736,7 +26850,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -26750,7 +26864,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -26764,7 +26878,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -26778,7 +26892,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -26786,7 +26900,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -26794,7 +26908,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -26802,7 +26916,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -26810,7 +26924,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -26818,7 +26932,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -26826,7 +26940,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -26834,7 +26948,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -26842,7 +26956,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -26850,7 +26964,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -26861,7 +26975,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -26869,7 +26983,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -26877,7 +26991,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -26885,7 +26999,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -26893,7 +27007,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -26901,7 +27015,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -26909,7 +27023,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -26917,7 +27031,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3">
       <c r="A44" s="4">
         <v>43</v>
       </c>
@@ -26925,7 +27039,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -26933,7 +27047,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3">
       <c r="A46" s="4">
         <v>45</v>
       </c>
@@ -26941,42 +27055,42 @@
         <v>299</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3">
       <c r="B47" s="4" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3">
       <c r="B48" s="4" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:2">
       <c r="B49" s="4" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:2">
       <c r="B50" s="4" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:2">
       <c r="B51" s="4" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:2">
       <c r="B52" s="4" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:2">
       <c r="B53" s="4" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:2">
       <c r="B54" s="4" t="s">
         <v>291</v>
       </c>
@@ -26989,4 +27103,158 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A074D264-9A9F-4C97-8435-D1191E30740B}">
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="26.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>491</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>492</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>250</v>
+      </c>
+      <c r="B4" t="s">
+        <v>493</v>
+      </c>
+      <c r="D4" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B5" t="s">
+        <v>494</v>
+      </c>
+      <c r="D5" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>484</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>495</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>255</v>
+      </c>
+      <c r="B7" t="s">
+        <v>497</v>
+      </c>
+      <c r="D7" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>257</v>
+      </c>
+      <c r="B8" t="s">
+        <v>496</v>
+      </c>
+      <c r="D8" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>265</v>
+      </c>
+      <c r="B9" t="s">
+        <v>498</v>
+      </c>
+      <c r="D9" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>352</v>
+      </c>
+      <c r="B10" t="s">
+        <v>499</v>
+      </c>
+      <c r="D10" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>485</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>500</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>486</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>501</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>487</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>502</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Таблица сигналов.xlsx
+++ b/Таблица сигналов.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\SW002-LoadWizardPro_v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F12DB8B4-A72F-499C-BAD9-DABF7CC9BB16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3293C496-9A63-4D81-A60A-4D1AEE48F5DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0F8F6BBE-EBD7-4FEB-A239-792B86B6C8F6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{0F8F6BBE-EBD7-4FEB-A239-792B86B6C8F6}"/>
   </bookViews>
   <sheets>
     <sheet name="IO ПЛК" sheetId="1" r:id="rId1"/>
     <sheet name="Fieldbus Робот" sheetId="2" r:id="rId2"/>
-    <sheet name="Recipe Data" sheetId="5" r:id="rId3"/>
-    <sheet name="Task Data" sheetId="4" r:id="rId4"/>
-    <sheet name="Error list" sheetId="6" r:id="rId5"/>
+    <sheet name="Лист1" sheetId="7" r:id="rId3"/>
+    <sheet name="Recipe Data" sheetId="5" r:id="rId4"/>
+    <sheet name="Task Data" sheetId="4" r:id="rId5"/>
+    <sheet name="Error list" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="520">
   <si>
     <t>Комментарий</t>
   </si>
@@ -1557,13 +1558,58 @@
   </si>
   <si>
     <t>P10008</t>
+  </si>
+  <si>
+    <t>Прижим при захвате детали с полки</t>
+  </si>
+  <si>
+    <t>Прижим при установке деталь на полку</t>
+  </si>
+  <si>
+    <t>Прижим при захвате детали из патрона</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ожидание открытия кулачков патрона 1 после сигнала </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ожидание открытия кулачков патрона 2 после сигнала </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ожидание закрытия кулачков патрона 1 после сигнала </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ожидание закрытия кулачков патрона 2 после сигнала </t>
+  </si>
+  <si>
+    <t>Время открытия захвата 1</t>
+  </si>
+  <si>
+    <t>Время открытия захвата 2</t>
+  </si>
+  <si>
+    <t>Время закрытия захвата 1</t>
+  </si>
+  <si>
+    <t>Время закрытия захвата 2</t>
+  </si>
+  <si>
+    <t>Прижим при установки детали в патрон</t>
+  </si>
+  <si>
+    <t>Прижим при установке детали в патрон</t>
+  </si>
+  <si>
+    <t>Скорость поиска</t>
+  </si>
+  <si>
+    <t>Скоррость обдува</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1697,25 +1743,22 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="59">
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2067,6 +2110,9 @@
         <charset val="204"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2607,45 +2653,45 @@
       <calculatedColumnFormula>IF(RIGHT(G3,1)="0",LEFT(G3,5)," ")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{BB12B359-19DD-48D3-A11C-9EA26D87A7D4}" name="Комментарий" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{8C5C57C6-24CB-4FBE-B303-CAE2CBF8FE46}" name="Столбец1" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{8C5C57C6-24CB-4FBE-B303-CAE2CBF8FE46}" name="Столбец1" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{922370A5-4286-4E2F-B3D7-F7B02AE73BA3}" name="Таблица19" displayName="Таблица19" ref="E2:G35" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{922370A5-4286-4E2F-B3D7-F7B02AE73BA3}" name="Таблица19" displayName="Таблица19" ref="E2:G35" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <autoFilter ref="E2:G35" xr:uid="{922370A5-4286-4E2F-B3D7-F7B02AE73BA3}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{030B20DE-3D3F-4F9E-9CF4-2797FEBBE639}" name="Физический адрес" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{FE7270F2-A91D-46D7-B053-943F33E91429}" name="Назначение" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{789B1D2D-EE14-45F0-AEF8-77EF04F1EE59}" name="Комментарий" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{030B20DE-3D3F-4F9E-9CF4-2797FEBBE639}" name="Физический адрес" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{FE7270F2-A91D-46D7-B053-943F33E91429}" name="Назначение" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{789B1D2D-EE14-45F0-AEF8-77EF04F1EE59}" name="Комментарий" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{DBF536A0-1787-4197-8344-E13C846DAF0F}" name="Таблица9" displayName="Таблица9" ref="A2:C35" totalsRowShown="0" headerRowDxfId="15" headerRowBorderDxfId="14" tableBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{DBF536A0-1787-4197-8344-E13C846DAF0F}" name="Таблица9" displayName="Таблица9" ref="A2:C35" totalsRowShown="0" headerRowDxfId="14" headerRowBorderDxfId="13" tableBorderDxfId="12">
   <autoFilter ref="A2:C35" xr:uid="{DBF536A0-1787-4197-8344-E13C846DAF0F}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0669B8C3-918B-41A1-8F32-AEE91E15EB1D}" name="Физический адрес" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{AC3FDE73-3420-4D74-8F9A-19CD06947E05}" name="Назначение" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{83B79EE0-0F25-4263-ACC2-A83B9403C818}" name="Комментарий" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{0669B8C3-918B-41A1-8F32-AEE91E15EB1D}" name="Физический адрес" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{AC3FDE73-3420-4D74-8F9A-19CD06947E05}" name="Назначение" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{83B79EE0-0F25-4263-ACC2-A83B9403C818}" name="Комментарий" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{D433E639-47C8-435B-BE62-40BBD3A85586}" name="Таблица7" displayName="Таблица7" ref="A1:E66" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{D433E639-47C8-435B-BE62-40BBD3A85586}" name="Таблица7" displayName="Таблица7" ref="A1:E66" totalsRowShown="0" headerRowDxfId="8" dataDxfId="6" headerRowBorderDxfId="7" tableBorderDxfId="5">
   <autoFilter ref="A1:E66" xr:uid="{D433E639-47C8-435B-BE62-40BBD3A85586}"/>
   <tableColumns count="5">
-    <tableColumn id="4" xr3:uid="{57905240-D78B-4866-948D-15CD0C7825F9}" name="№" dataDxfId="5"/>
-    <tableColumn id="1" xr3:uid="{C0C4E1FE-6EA6-4426-AC8B-A634B9C978EE}" name="Адрес слова" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{D830E9E6-B548-460D-A0E1-20E6927BC813}" name="Комментарий" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{92954912-D498-42AD-8489-14F9E7812192}" name="Размер" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{BE2FF70F-8E70-476F-BD8E-CD89F51A98F0}" name="Замечание" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{57905240-D78B-4866-948D-15CD0C7825F9}" name="№" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{C0C4E1FE-6EA6-4426-AC8B-A634B9C978EE}" name="Адрес слова" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{D830E9E6-B548-460D-A0E1-20E6927BC813}" name="Комментарий" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{92954912-D498-42AD-8489-14F9E7812192}" name="Размер" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{BE2FF70F-8E70-476F-BD8E-CD89F51A98F0}" name="Замечание" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2969,35 +3015,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF0C363D-E002-455D-AEBF-103AC5B10E47}">
   <dimension ref="A1:I37"/>
-  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.8984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.09765625" style="2"/>
-    <col min="6" max="6" width="21.8984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" style="2"/>
+    <col min="6" max="6" width="21.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="49.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.09765625" style="2"/>
+    <col min="9" max="9" width="49.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" thickBot="1">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="F1" s="11" t="s">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="F1" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -3023,7 +3069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -3049,7 +3095,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -3075,7 +3121,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -3101,7 +3147,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -3127,7 +3173,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -3153,7 +3199,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
@@ -3179,7 +3225,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -3205,7 +3251,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
@@ -3231,7 +3277,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -3257,7 +3303,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>36</v>
       </c>
@@ -3283,7 +3329,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>37</v>
       </c>
@@ -3309,7 +3355,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>38</v>
       </c>
@@ -3335,7 +3381,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>39</v>
       </c>
@@ -3361,7 +3407,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>40</v>
       </c>
@@ -3387,7 +3433,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>41</v>
       </c>
@@ -3413,7 +3459,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>42</v>
       </c>
@@ -3439,22 +3485,22 @@
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15" thickBot="1"/>
-    <row r="20" spans="1:9" ht="15" thickBot="1">
-      <c r="A20" s="11" t="s">
+    <row r="19" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="F20" s="11" t="s">
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="F20" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>10</v>
       </c>
@@ -3480,7 +3526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>130</v>
       </c>
@@ -3506,7 +3552,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>131</v>
       </c>
@@ -3532,7 +3578,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>132</v>
       </c>
@@ -3558,7 +3604,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>133</v>
       </c>
@@ -3584,7 +3630,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>134</v>
       </c>
@@ -3610,7 +3656,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>135</v>
       </c>
@@ -3636,7 +3682,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>136</v>
       </c>
@@ -3662,7 +3708,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>137</v>
       </c>
@@ -3688,7 +3734,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>28</v>
       </c>
@@ -3714,7 +3760,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>29</v>
       </c>
@@ -3740,7 +3786,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>30</v>
       </c>
@@ -3766,7 +3812,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>31</v>
       </c>
@@ -3792,7 +3838,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>32</v>
       </c>
@@ -3818,7 +3864,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>33</v>
       </c>
@@ -3844,7 +3890,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>34</v>
       </c>
@@ -3870,7 +3916,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>35</v>
       </c>
@@ -3916,36 +3962,36 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40895EFA-86F2-45C7-8EA9-6C33984E31A6}">
   <dimension ref="A1:J898"/>
-  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="43.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.09765625" style="1"/>
+    <col min="2" max="2" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="43.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" style="1"/>
     <col min="6" max="6" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.09765625" style="1"/>
+    <col min="10" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="14.4">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
       <c r="E1" s="2"/>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-    </row>
-    <row r="2" spans="1:10" ht="14.4">
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>242</v>
       </c>
@@ -3975,7 +4021,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>65</v>
       </c>
@@ -4005,7 +4051,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>66</v>
       </c>
@@ -4035,7 +4081,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>67</v>
       </c>
@@ -4065,7 +4111,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>68</v>
       </c>
@@ -4095,7 +4141,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>69</v>
       </c>
@@ -4125,7 +4171,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>70</v>
       </c>
@@ -4155,7 +4201,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>71</v>
       </c>
@@ -4185,7 +4231,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>72</v>
       </c>
@@ -4212,7 +4258,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>73</v>
       </c>
@@ -4239,7 +4285,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>74</v>
       </c>
@@ -4266,7 +4312,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>75</v>
       </c>
@@ -4293,7 +4339,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>76</v>
       </c>
@@ -4320,7 +4366,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>77</v>
       </c>
@@ -4347,7 +4393,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>78</v>
       </c>
@@ -4371,7 +4417,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>79</v>
       </c>
@@ -4395,7 +4441,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>80</v>
       </c>
@@ -4419,7 +4465,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="14.4">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>81</v>
       </c>
@@ -4449,7 +4495,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="14.4">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>82</v>
       </c>
@@ -4479,7 +4525,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="14.4">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>83</v>
       </c>
@@ -4509,7 +4555,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="14.4">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>84</v>
       </c>
@@ -4539,7 +4585,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="14.4">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>85</v>
       </c>
@@ -4569,7 +4615,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>86</v>
       </c>
@@ -4593,7 +4639,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="14.4">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>87</v>
       </c>
@@ -4618,7 +4664,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="14.4">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>88</v>
       </c>
@@ -4643,7 +4689,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="14.4">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>89</v>
       </c>
@@ -4668,7 +4714,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="14.4">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>90</v>
       </c>
@@ -4693,7 +4739,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="14.4">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>91</v>
       </c>
@@ -4718,7 +4764,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="14.4">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>92</v>
       </c>
@@ -4743,7 +4789,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="14.4">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>93</v>
       </c>
@@ -4768,7 +4814,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="14.4">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>94</v>
       </c>
@@ -4793,7 +4839,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="14.4">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>95</v>
       </c>
@@ -4818,7 +4864,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="14.4">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>96</v>
       </c>
@@ -4843,7 +4889,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="14.4">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>97</v>
       </c>
@@ -4873,7 +4919,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="14.4">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>98</v>
       </c>
@@ -4903,7 +4949,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="14.4">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>99</v>
       </c>
@@ -4933,7 +4979,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="14.4">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>100</v>
       </c>
@@ -4963,7 +5009,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="14.4">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>101</v>
       </c>
@@ -4993,7 +5039,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>102</v>
       </c>
@@ -5017,7 +5063,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="14.4">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>103</v>
       </c>
@@ -5042,7 +5088,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="14.4">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>104</v>
       </c>
@@ -5067,7 +5113,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="14.4">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>105</v>
       </c>
@@ -5092,7 +5138,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="14.4">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>106</v>
       </c>
@@ -5117,7 +5163,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="14.4">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>107</v>
       </c>
@@ -5142,7 +5188,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="14.4">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>108</v>
       </c>
@@ -5167,7 +5213,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="14.4">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>109</v>
       </c>
@@ -5192,7 +5238,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="14.4">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>110</v>
       </c>
@@ -5217,7 +5263,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="14.4">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>111</v>
       </c>
@@ -5242,7 +5288,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="14.4">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>112</v>
       </c>
@@ -5267,7 +5313,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>113</v>
       </c>
@@ -5297,7 +5343,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>114</v>
       </c>
@@ -5323,7 +5369,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>115</v>
       </c>
@@ -5350,7 +5396,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>116</v>
       </c>
@@ -5377,7 +5423,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>117</v>
       </c>
@@ -5404,7 +5450,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>118</v>
       </c>
@@ -5431,7 +5477,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>119</v>
       </c>
@@ -5458,7 +5504,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>120</v>
       </c>
@@ -5485,7 +5531,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>121</v>
       </c>
@@ -5509,7 +5555,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>122</v>
       </c>
@@ -5533,7 +5579,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>123</v>
       </c>
@@ -5557,7 +5603,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>124</v>
       </c>
@@ -5581,7 +5627,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>125</v>
       </c>
@@ -5605,7 +5651,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>126</v>
       </c>
@@ -5629,7 +5675,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>127</v>
       </c>
@@ -5653,7 +5699,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>128</v>
       </c>
@@ -5677,7 +5723,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>129</v>
       </c>
@@ -5707,7 +5753,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>130</v>
       </c>
@@ -5737,7 +5783,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>131</v>
       </c>
@@ -5767,7 +5813,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>132</v>
       </c>
@@ -5797,7 +5843,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>133</v>
       </c>
@@ -5827,7 +5873,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>134</v>
       </c>
@@ -5857,7 +5903,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>135</v>
       </c>
@@ -5887,7 +5933,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>136</v>
       </c>
@@ -5917,7 +5963,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>137</v>
       </c>
@@ -5944,7 +5990,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>138</v>
       </c>
@@ -5971,7 +6017,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>139</v>
       </c>
@@ -5998,7 +6044,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>140</v>
       </c>
@@ -6025,7 +6071,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>141</v>
       </c>
@@ -6052,7 +6098,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>142</v>
       </c>
@@ -6076,7 +6122,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>143</v>
       </c>
@@ -6100,7 +6146,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>144</v>
       </c>
@@ -6124,7 +6170,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>145</v>
       </c>
@@ -6148,7 +6194,7 @@
         <v>P1105</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>146</v>
       </c>
@@ -6172,7 +6218,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>147</v>
       </c>
@@ -6196,7 +6242,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>148</v>
       </c>
@@ -6220,7 +6266,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>149</v>
       </c>
@@ -6244,7 +6290,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>150</v>
       </c>
@@ -6268,7 +6314,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>151</v>
       </c>
@@ -6292,7 +6338,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>152</v>
       </c>
@@ -6316,7 +6362,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>153</v>
       </c>
@@ -6340,7 +6386,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>154</v>
       </c>
@@ -6364,7 +6410,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>155</v>
       </c>
@@ -6388,7 +6434,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>156</v>
       </c>
@@ -6412,7 +6458,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>157</v>
       </c>
@@ -6436,7 +6482,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>158</v>
       </c>
@@ -6460,7 +6506,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>159</v>
       </c>
@@ -6484,7 +6530,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>160</v>
       </c>
@@ -6508,7 +6554,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>161</v>
       </c>
@@ -6532,7 +6578,7 @@
         <v>P1106</v>
       </c>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>162</v>
       </c>
@@ -6556,7 +6602,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>163</v>
       </c>
@@ -6580,7 +6626,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>164</v>
       </c>
@@ -6604,7 +6650,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>165</v>
       </c>
@@ -6628,7 +6674,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>166</v>
       </c>
@@ -6652,7 +6698,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>167</v>
       </c>
@@ -6676,7 +6722,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>168</v>
       </c>
@@ -6700,7 +6746,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>169</v>
       </c>
@@ -6724,7 +6770,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>170</v>
       </c>
@@ -6748,7 +6794,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>171</v>
       </c>
@@ -6772,7 +6818,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>172</v>
       </c>
@@ -6796,7 +6842,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>173</v>
       </c>
@@ -6820,7 +6866,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>174</v>
       </c>
@@ -6844,7 +6890,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>175</v>
       </c>
@@ -6868,7 +6914,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>176</v>
       </c>
@@ -6892,7 +6938,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>177</v>
       </c>
@@ -6916,7 +6962,7 @@
         <v>P1107</v>
       </c>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>178</v>
       </c>
@@ -6940,7 +6986,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>179</v>
       </c>
@@ -6964,7 +7010,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>180</v>
       </c>
@@ -6988,7 +7034,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>181</v>
       </c>
@@ -7012,7 +7058,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>182</v>
       </c>
@@ -7036,7 +7082,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>183</v>
       </c>
@@ -7060,7 +7106,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>184</v>
       </c>
@@ -7084,7 +7130,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>185</v>
       </c>
@@ -7108,7 +7154,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>186</v>
       </c>
@@ -7132,7 +7178,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>187</v>
       </c>
@@ -7156,7 +7202,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="126" spans="1:8">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>188</v>
       </c>
@@ -7180,7 +7226,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>189</v>
       </c>
@@ -7204,7 +7250,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>190</v>
       </c>
@@ -7228,7 +7274,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>191</v>
       </c>
@@ -7252,7 +7298,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="130" spans="1:8">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>192</v>
       </c>
@@ -7276,7 +7322,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>193</v>
       </c>
@@ -7300,7 +7346,7 @@
         <v>P1108</v>
       </c>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>194</v>
       </c>
@@ -7324,7 +7370,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>195</v>
       </c>
@@ -7348,7 +7394,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>196</v>
       </c>
@@ -7372,7 +7418,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>197</v>
       </c>
@@ -7396,7 +7442,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>198</v>
       </c>
@@ -7420,7 +7466,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>199</v>
       </c>
@@ -7444,7 +7490,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="138" spans="1:8">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>200</v>
       </c>
@@ -7468,7 +7514,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="139" spans="1:8">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>201</v>
       </c>
@@ -7492,7 +7538,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="140" spans="1:8">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>202</v>
       </c>
@@ -7516,7 +7562,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="141" spans="1:8">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>203</v>
       </c>
@@ -7540,7 +7586,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="142" spans="1:8">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>204</v>
       </c>
@@ -7564,7 +7610,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="143" spans="1:8">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>205</v>
       </c>
@@ -7588,7 +7634,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="144" spans="1:8">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>206</v>
       </c>
@@ -7612,7 +7658,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="145" spans="1:8">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>207</v>
       </c>
@@ -7636,7 +7682,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="146" spans="1:8">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>208</v>
       </c>
@@ -7660,7 +7706,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>209</v>
       </c>
@@ -7684,7 +7730,7 @@
         <v>P1109</v>
       </c>
     </row>
-    <row r="148" spans="1:8">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>210</v>
       </c>
@@ -7708,7 +7754,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>211</v>
       </c>
@@ -7732,7 +7778,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>212</v>
       </c>
@@ -7756,7 +7802,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="151" spans="1:8">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>213</v>
       </c>
@@ -7780,7 +7826,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="152" spans="1:8">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>214</v>
       </c>
@@ -7804,7 +7850,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>215</v>
       </c>
@@ -7828,7 +7874,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="154" spans="1:8">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>216</v>
       </c>
@@ -7852,7 +7898,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="155" spans="1:8">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>217</v>
       </c>
@@ -7876,7 +7922,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="156" spans="1:8">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>218</v>
       </c>
@@ -7900,7 +7946,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="157" spans="1:8">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>219</v>
       </c>
@@ -7924,7 +7970,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="158" spans="1:8">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>220</v>
       </c>
@@ -7948,7 +7994,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="159" spans="1:8">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>221</v>
       </c>
@@ -7972,7 +8018,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="160" spans="1:8">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>222</v>
       </c>
@@ -7996,7 +8042,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="161" spans="1:9">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>223</v>
       </c>
@@ -8020,7 +8066,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="162" spans="1:9">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>224</v>
       </c>
@@ -8044,7 +8090,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="163" spans="1:9">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>225</v>
       </c>
@@ -8074,7 +8120,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="164" spans="1:9">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>226</v>
       </c>
@@ -8098,7 +8144,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="165" spans="1:9">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>227</v>
       </c>
@@ -8122,7 +8168,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="166" spans="1:9">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>228</v>
       </c>
@@ -8146,7 +8192,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="167" spans="1:9">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>229</v>
       </c>
@@ -8170,7 +8216,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="168" spans="1:9">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>230</v>
       </c>
@@ -8194,7 +8240,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="169" spans="1:9">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>231</v>
       </c>
@@ -8218,7 +8264,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="170" spans="1:9">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>232</v>
       </c>
@@ -8242,7 +8288,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="171" spans="1:9">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>233</v>
       </c>
@@ -8266,7 +8312,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="172" spans="1:9">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>234</v>
       </c>
@@ -8290,7 +8336,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="173" spans="1:9">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>235</v>
       </c>
@@ -8314,7 +8360,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="174" spans="1:9">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>236</v>
       </c>
@@ -8338,7 +8384,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="175" spans="1:9">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>237</v>
       </c>
@@ -8362,7 +8408,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="176" spans="1:9">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>238</v>
       </c>
@@ -8386,7 +8432,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="177" spans="1:8">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>239</v>
       </c>
@@ -8410,7 +8456,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="178" spans="1:8">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>240</v>
       </c>
@@ -8434,7 +8480,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="179" spans="1:8">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>241</v>
       </c>
@@ -8460,8 +8506,11 @@
         <f t="shared" si="11"/>
         <v>P1111</v>
       </c>
-    </row>
-    <row r="180" spans="1:8">
+      <c r="I179" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>242</v>
       </c>
@@ -8485,7 +8534,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="181" spans="1:8">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>243</v>
       </c>
@@ -8509,7 +8558,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="182" spans="1:8">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>244</v>
       </c>
@@ -8533,7 +8582,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="183" spans="1:8">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>245</v>
       </c>
@@ -8557,7 +8606,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="184" spans="1:8">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>246</v>
       </c>
@@ -8581,7 +8630,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="185" spans="1:8">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>247</v>
       </c>
@@ -8605,7 +8654,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="186" spans="1:8">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>248</v>
       </c>
@@ -8629,7 +8678,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="187" spans="1:8">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>249</v>
       </c>
@@ -8652,8 +8701,11 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="188" spans="1:8">
+      <c r="I187" s="1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>250</v>
       </c>
@@ -8677,7 +8729,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="189" spans="1:8">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>251</v>
       </c>
@@ -8701,7 +8753,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="190" spans="1:8">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>252</v>
       </c>
@@ -8725,7 +8777,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="191" spans="1:8">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>253</v>
       </c>
@@ -8749,7 +8801,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="192" spans="1:8">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>254</v>
       </c>
@@ -8773,7 +8825,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="193" spans="1:8">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>255</v>
       </c>
@@ -8797,7 +8849,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="194" spans="1:8">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>256</v>
       </c>
@@ -8821,7 +8873,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="195" spans="1:8">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>257</v>
       </c>
@@ -8847,8 +8899,11 @@
         <f t="shared" si="11"/>
         <v>P1112</v>
       </c>
-    </row>
-    <row r="196" spans="1:8">
+      <c r="I195" s="1" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>258</v>
       </c>
@@ -8872,7 +8927,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="197" spans="1:8">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>259</v>
       </c>
@@ -8896,7 +8951,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="198" spans="1:8">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>260</v>
       </c>
@@ -8920,7 +8975,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="199" spans="1:8">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>261</v>
       </c>
@@ -8944,7 +8999,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="200" spans="1:8">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>262</v>
       </c>
@@ -8968,7 +9023,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="201" spans="1:8">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>263</v>
       </c>
@@ -8992,7 +9047,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="202" spans="1:8">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>264</v>
       </c>
@@ -9016,7 +9071,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="203" spans="1:8">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>265</v>
       </c>
@@ -9039,8 +9094,11 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="204" spans="1:8">
+      <c r="I203" s="1" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>266</v>
       </c>
@@ -9064,7 +9122,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="205" spans="1:8">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>267</v>
       </c>
@@ -9088,7 +9146,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="206" spans="1:8">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>268</v>
       </c>
@@ -9112,7 +9170,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="207" spans="1:8">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>269</v>
       </c>
@@ -9136,7 +9194,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="208" spans="1:8">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>270</v>
       </c>
@@ -9160,7 +9218,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="209" spans="1:8">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>271</v>
       </c>
@@ -9184,7 +9242,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="210" spans="1:8">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>272</v>
       </c>
@@ -9208,7 +9266,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="211" spans="1:8">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>273</v>
       </c>
@@ -9234,8 +9292,11 @@
         <f t="shared" si="15"/>
         <v>P1113</v>
       </c>
-    </row>
-    <row r="212" spans="1:8">
+      <c r="I211" s="1" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>274</v>
       </c>
@@ -9259,7 +9320,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="213" spans="1:8">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>275</v>
       </c>
@@ -9283,7 +9344,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="214" spans="1:8">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>276</v>
       </c>
@@ -9307,7 +9368,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="215" spans="1:8">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>277</v>
       </c>
@@ -9331,7 +9392,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="216" spans="1:8">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>278</v>
       </c>
@@ -9355,7 +9416,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="217" spans="1:8">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>279</v>
       </c>
@@ -9379,7 +9440,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="218" spans="1:8">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>280</v>
       </c>
@@ -9403,7 +9464,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="219" spans="1:8">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>281</v>
       </c>
@@ -9426,8 +9487,11 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="220" spans="1:8">
+      <c r="I219" s="1" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>282</v>
       </c>
@@ -9451,7 +9515,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="221" spans="1:8">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>283</v>
       </c>
@@ -9475,7 +9539,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="222" spans="1:8">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>284</v>
       </c>
@@ -9499,7 +9563,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="223" spans="1:8">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>285</v>
       </c>
@@ -9523,7 +9587,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="224" spans="1:8">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>286</v>
       </c>
@@ -9547,7 +9611,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="225" spans="1:8">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>287</v>
       </c>
@@ -9571,7 +9635,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="226" spans="1:8">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>288</v>
       </c>
@@ -9595,7 +9659,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="227" spans="1:8">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>289</v>
       </c>
@@ -9621,8 +9685,11 @@
         <f t="shared" si="15"/>
         <v>P1114</v>
       </c>
-    </row>
-    <row r="228" spans="1:8">
+      <c r="I227" s="1" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>290</v>
       </c>
@@ -9646,7 +9713,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="229" spans="1:8">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
         <v>291</v>
       </c>
@@ -9670,7 +9737,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="230" spans="1:8">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>292</v>
       </c>
@@ -9694,7 +9761,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="231" spans="1:8">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>293</v>
       </c>
@@ -9718,7 +9785,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="232" spans="1:8">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>294</v>
       </c>
@@ -9742,7 +9809,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="233" spans="1:8">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>295</v>
       </c>
@@ -9766,7 +9833,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="234" spans="1:8">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>296</v>
       </c>
@@ -9790,7 +9857,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="235" spans="1:8">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>297</v>
       </c>
@@ -9813,8 +9880,11 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="236" spans="1:8">
+      <c r="I235" s="1" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>298</v>
       </c>
@@ -9838,7 +9908,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="237" spans="1:8">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>299</v>
       </c>
@@ -9862,7 +9932,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="238" spans="1:8">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>300</v>
       </c>
@@ -9886,7 +9956,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="239" spans="1:8">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>301</v>
       </c>
@@ -9910,7 +9980,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="240" spans="1:8">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>302</v>
       </c>
@@ -9934,7 +10004,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="241" spans="1:8">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>303</v>
       </c>
@@ -9958,7 +10028,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="242" spans="1:8">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
         <v>304</v>
       </c>
@@ -9982,7 +10052,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="243" spans="1:8">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" s="1">
         <v>305</v>
       </c>
@@ -10008,8 +10078,11 @@
         <f t="shared" si="15"/>
         <v>P1115</v>
       </c>
-    </row>
-    <row r="244" spans="1:8">
+      <c r="I243" s="1" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" s="1">
         <v>306</v>
       </c>
@@ -10033,7 +10106,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="245" spans="1:8">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
         <v>307</v>
       </c>
@@ -10057,7 +10130,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="246" spans="1:8">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
         <v>308</v>
       </c>
@@ -10081,7 +10154,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="247" spans="1:8">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
         <v>309</v>
       </c>
@@ -10105,7 +10178,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="248" spans="1:8">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
         <v>310</v>
       </c>
@@ -10129,7 +10202,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="249" spans="1:8">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
         <v>311</v>
       </c>
@@ -10153,7 +10226,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="250" spans="1:8">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
         <v>312</v>
       </c>
@@ -10177,7 +10250,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="251" spans="1:8">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" s="1">
         <v>313</v>
       </c>
@@ -10200,8 +10273,11 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="252" spans="1:8">
+      <c r="I251" s="1" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>314</v>
       </c>
@@ -10225,7 +10301,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="253" spans="1:8">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>315</v>
       </c>
@@ -10249,7 +10325,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="254" spans="1:8">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>316</v>
       </c>
@@ -10273,7 +10349,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="255" spans="1:8">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>317</v>
       </c>
@@ -10297,7 +10373,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="256" spans="1:8">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>318</v>
       </c>
@@ -10321,7 +10397,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="257" spans="1:8">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>319</v>
       </c>
@@ -10345,7 +10421,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="258" spans="1:8">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>320</v>
       </c>
@@ -10369,7 +10445,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="259" spans="1:8">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>321</v>
       </c>
@@ -10395,8 +10471,11 @@
         <f t="shared" si="15"/>
         <v>P1116</v>
       </c>
-    </row>
-    <row r="260" spans="1:8">
+      <c r="I259" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>322</v>
       </c>
@@ -10420,7 +10499,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="261" spans="1:8">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>323</v>
       </c>
@@ -10444,7 +10523,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="262" spans="1:8">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>324</v>
       </c>
@@ -10468,7 +10547,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="263" spans="1:8">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>325</v>
       </c>
@@ -10492,7 +10571,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="264" spans="1:8">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
         <v>326</v>
       </c>
@@ -10516,7 +10595,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="265" spans="1:8">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
         <v>327</v>
       </c>
@@ -10540,7 +10619,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="266" spans="1:8">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266" s="1">
         <v>328</v>
       </c>
@@ -10564,7 +10643,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="267" spans="1:8">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A267" s="1">
         <v>329</v>
       </c>
@@ -10587,8 +10666,11 @@
         <f t="shared" si="19"/>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="268" spans="1:8">
+      <c r="I267" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268" s="1">
         <v>330</v>
       </c>
@@ -10612,7 +10694,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="269" spans="1:8">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
         <v>331</v>
       </c>
@@ -10636,7 +10718,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="270" spans="1:8">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
         <v>332</v>
       </c>
@@ -10660,7 +10742,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="271" spans="1:8">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
         <v>333</v>
       </c>
@@ -10684,7 +10766,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="272" spans="1:8">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
         <v>334</v>
       </c>
@@ -10708,7 +10790,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="273" spans="1:8">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A273" s="1">
         <v>335</v>
       </c>
@@ -10732,7 +10814,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="274" spans="1:8">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274" s="1">
         <v>336</v>
       </c>
@@ -10756,7 +10838,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="275" spans="1:8">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275" s="1">
         <v>337</v>
       </c>
@@ -10779,8 +10861,11 @@
         <f t="shared" si="19"/>
         <v>P1117</v>
       </c>
-    </row>
-    <row r="276" spans="1:8">
+      <c r="I275" s="1" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A276" s="1">
         <v>338</v>
       </c>
@@ -10804,7 +10889,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="277" spans="1:8">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A277" s="1">
         <v>339</v>
       </c>
@@ -10828,7 +10913,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="278" spans="1:8">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A278" s="1">
         <v>340</v>
       </c>
@@ -10852,7 +10937,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="279" spans="1:8">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
         <v>341</v>
       </c>
@@ -10876,7 +10961,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="280" spans="1:8">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A280" s="1">
         <v>342</v>
       </c>
@@ -10900,7 +10985,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="281" spans="1:8">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A281" s="1">
         <v>343</v>
       </c>
@@ -10924,7 +11009,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="282" spans="1:8">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A282" s="1">
         <v>344</v>
       </c>
@@ -10948,7 +11033,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="283" spans="1:8">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283" s="1">
         <v>345</v>
       </c>
@@ -10971,8 +11056,11 @@
         <f t="shared" si="19"/>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="284" spans="1:8">
+      <c r="I283" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284" s="1">
         <v>346</v>
       </c>
@@ -10996,7 +11084,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="285" spans="1:8">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285" s="1">
         <v>347</v>
       </c>
@@ -11020,7 +11108,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="286" spans="1:8">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A286" s="1">
         <v>348</v>
       </c>
@@ -11044,7 +11132,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="287" spans="1:8">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
         <v>349</v>
       </c>
@@ -11068,7 +11156,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="288" spans="1:8">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
         <v>350</v>
       </c>
@@ -11092,7 +11180,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="289" spans="1:8">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A289" s="1">
         <v>351</v>
       </c>
@@ -11116,7 +11204,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="290" spans="1:8">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A290" s="1">
         <v>352</v>
       </c>
@@ -11140,7 +11228,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="291" spans="1:8">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A291" s="1">
         <v>353</v>
       </c>
@@ -11164,7 +11252,7 @@
         <v>P1118</v>
       </c>
     </row>
-    <row r="292" spans="1:8">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A292" s="1">
         <v>354</v>
       </c>
@@ -11188,7 +11276,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="293" spans="1:8">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A293" s="1">
         <v>355</v>
       </c>
@@ -11212,7 +11300,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="294" spans="1:8">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>356</v>
       </c>
@@ -11236,7 +11324,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="295" spans="1:8">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>357</v>
       </c>
@@ -11260,7 +11348,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="296" spans="1:8">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>358</v>
       </c>
@@ -11284,7 +11372,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="297" spans="1:8">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>359</v>
       </c>
@@ -11308,7 +11396,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="298" spans="1:8">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>360</v>
       </c>
@@ -11332,7 +11420,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="299" spans="1:8">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>361</v>
       </c>
@@ -11356,7 +11444,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="300" spans="1:8">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>362</v>
       </c>
@@ -11380,7 +11468,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="301" spans="1:8">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>363</v>
       </c>
@@ -11404,7 +11492,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="302" spans="1:8">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>364</v>
       </c>
@@ -11428,7 +11516,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="303" spans="1:8">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>365</v>
       </c>
@@ -11452,7 +11540,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="304" spans="1:8">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>366</v>
       </c>
@@ -11476,7 +11564,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="305" spans="1:8">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>367</v>
       </c>
@@ -11500,7 +11588,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="306" spans="1:8">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>368</v>
       </c>
@@ -11524,7 +11612,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="307" spans="1:8">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>369</v>
       </c>
@@ -11548,7 +11636,7 @@
         <v>P1119</v>
       </c>
     </row>
-    <row r="308" spans="1:8">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>370</v>
       </c>
@@ -11572,7 +11660,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="309" spans="1:8">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>371</v>
       </c>
@@ -11596,7 +11684,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="310" spans="1:8">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A310" s="1">
         <v>372</v>
       </c>
@@ -11620,7 +11708,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="311" spans="1:8">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A311" s="1">
         <v>373</v>
       </c>
@@ -11644,7 +11732,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="312" spans="1:8">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A312" s="1">
         <v>374</v>
       </c>
@@ -11668,7 +11756,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="313" spans="1:8">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A313" s="1">
         <v>375</v>
       </c>
@@ -11692,7 +11780,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="314" spans="1:8">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
         <v>376</v>
       </c>
@@ -11716,7 +11804,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="315" spans="1:8">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A315" s="1">
         <v>377</v>
       </c>
@@ -11740,7 +11828,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="316" spans="1:8">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A316" s="1">
         <v>378</v>
       </c>
@@ -11764,7 +11852,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="317" spans="1:8">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A317" s="1">
         <v>379</v>
       </c>
@@ -11788,7 +11876,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="318" spans="1:8">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A318" s="1">
         <v>380</v>
       </c>
@@ -11812,7 +11900,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="319" spans="1:8">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
         <v>381</v>
       </c>
@@ -11836,7 +11924,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="320" spans="1:8">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A320" s="1">
         <v>382</v>
       </c>
@@ -11860,7 +11948,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="321" spans="1:8">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A321" s="1">
         <v>383</v>
       </c>
@@ -11884,7 +11972,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="322" spans="1:8">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A322" s="1">
         <v>384</v>
       </c>
@@ -11908,7 +11996,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="323" spans="1:8">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A323" s="1">
         <v>385</v>
       </c>
@@ -11932,7 +12020,7 @@
         <v>P1120</v>
       </c>
     </row>
-    <row r="324" spans="1:8">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A324" s="1">
         <v>386</v>
       </c>
@@ -11956,7 +12044,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="325" spans="1:8">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
         <v>387</v>
       </c>
@@ -11980,7 +12068,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="326" spans="1:8">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
         <v>388</v>
       </c>
@@ -12004,7 +12092,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="327" spans="1:8">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A327" s="1">
         <v>389</v>
       </c>
@@ -12028,7 +12116,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="328" spans="1:8">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A328" s="1">
         <v>390</v>
       </c>
@@ -12052,7 +12140,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="329" spans="1:8">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A329" s="1">
         <v>391</v>
       </c>
@@ -12076,7 +12164,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="330" spans="1:8">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A330" s="1">
         <v>392</v>
       </c>
@@ -12100,7 +12188,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="331" spans="1:8">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A331" s="1">
         <v>393</v>
       </c>
@@ -12124,7 +12212,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="332" spans="1:8">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A332" s="1">
         <v>394</v>
       </c>
@@ -12148,7 +12236,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="333" spans="1:8">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A333" s="1">
         <v>395</v>
       </c>
@@ -12172,7 +12260,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="334" spans="1:8">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A334" s="1">
         <v>396</v>
       </c>
@@ -12196,7 +12284,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="335" spans="1:8">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A335" s="1">
         <v>397</v>
       </c>
@@ -12220,7 +12308,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="336" spans="1:8">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A336" s="1">
         <v>398</v>
       </c>
@@ -12244,7 +12332,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="337" spans="1:8">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A337" s="1">
         <v>399</v>
       </c>
@@ -12268,7 +12356,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="338" spans="1:8">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A338" s="1">
         <v>400</v>
       </c>
@@ -12292,7 +12380,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="339" spans="1:8">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A339" s="1">
         <v>401</v>
       </c>
@@ -12316,7 +12404,7 @@
         <v>P1121</v>
       </c>
     </row>
-    <row r="340" spans="1:8">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A340" s="1">
         <v>402</v>
       </c>
@@ -12340,7 +12428,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="341" spans="1:8">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A341" s="1">
         <v>403</v>
       </c>
@@ -12364,7 +12452,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="342" spans="1:8">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A342" s="1">
         <v>404</v>
       </c>
@@ -12388,7 +12476,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="343" spans="1:8">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A343" s="1">
         <v>405</v>
       </c>
@@ -12412,7 +12500,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="344" spans="1:8">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A344" s="1">
         <v>406</v>
       </c>
@@ -12436,7 +12524,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="345" spans="1:8">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A345" s="1">
         <v>407</v>
       </c>
@@ -12460,7 +12548,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="346" spans="1:8">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A346" s="1">
         <v>408</v>
       </c>
@@ -12484,7 +12572,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="347" spans="1:8">
+    <row r="347" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A347" s="1">
         <v>409</v>
       </c>
@@ -12508,7 +12596,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="348" spans="1:8">
+    <row r="348" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A348" s="1">
         <v>410</v>
       </c>
@@ -12532,7 +12620,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="349" spans="1:8">
+    <row r="349" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A349" s="1">
         <v>411</v>
       </c>
@@ -12556,7 +12644,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="350" spans="1:8">
+    <row r="350" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A350" s="1">
         <v>412</v>
       </c>
@@ -12580,7 +12668,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="351" spans="1:8">
+    <row r="351" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A351" s="1">
         <v>413</v>
       </c>
@@ -12604,7 +12692,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="352" spans="1:8">
+    <row r="352" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A352" s="1">
         <v>414</v>
       </c>
@@ -12628,7 +12716,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="353" spans="1:8">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A353" s="1">
         <v>415</v>
       </c>
@@ -12652,7 +12740,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="354" spans="1:8">
+    <row r="354" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A354" s="1">
         <v>416</v>
       </c>
@@ -12676,7 +12764,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="355" spans="1:8">
+    <row r="355" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A355" s="1">
         <v>417</v>
       </c>
@@ -12700,7 +12788,7 @@
         <v>P1122</v>
       </c>
     </row>
-    <row r="356" spans="1:8">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A356" s="1">
         <v>418</v>
       </c>
@@ -12724,7 +12812,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="357" spans="1:8">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A357" s="1">
         <v>419</v>
       </c>
@@ -12748,7 +12836,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="358" spans="1:8">
+    <row r="358" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A358" s="1">
         <v>420</v>
       </c>
@@ -12772,7 +12860,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="359" spans="1:8">
+    <row r="359" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A359" s="1">
         <v>421</v>
       </c>
@@ -12796,7 +12884,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="360" spans="1:8">
+    <row r="360" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A360" s="1">
         <v>422</v>
       </c>
@@ -12820,7 +12908,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="361" spans="1:8">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A361" s="1">
         <v>423</v>
       </c>
@@ -12844,7 +12932,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="362" spans="1:8">
+    <row r="362" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A362" s="1">
         <v>424</v>
       </c>
@@ -12868,7 +12956,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="363" spans="1:8">
+    <row r="363" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A363" s="1">
         <v>425</v>
       </c>
@@ -12892,7 +12980,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="364" spans="1:8">
+    <row r="364" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A364" s="1">
         <v>426</v>
       </c>
@@ -12916,7 +13004,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="365" spans="1:8">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A365" s="1">
         <v>427</v>
       </c>
@@ -12940,7 +13028,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="366" spans="1:8">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A366" s="1">
         <v>428</v>
       </c>
@@ -12964,7 +13052,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="367" spans="1:8">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A367" s="1">
         <v>429</v>
       </c>
@@ -12988,7 +13076,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="368" spans="1:8">
+    <row r="368" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A368" s="1">
         <v>430</v>
       </c>
@@ -13012,7 +13100,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="369" spans="1:8">
+    <row r="369" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A369" s="1">
         <v>431</v>
       </c>
@@ -13036,7 +13124,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="370" spans="1:8">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A370" s="1">
         <v>432</v>
       </c>
@@ -13060,7 +13148,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="371" spans="1:8">
+    <row r="371" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A371" s="1">
         <v>433</v>
       </c>
@@ -13084,7 +13172,7 @@
         <v>P1123</v>
       </c>
     </row>
-    <row r="372" spans="1:8">
+    <row r="372" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A372" s="1">
         <v>434</v>
       </c>
@@ -13108,7 +13196,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="373" spans="1:8">
+    <row r="373" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A373" s="1">
         <v>435</v>
       </c>
@@ -13132,7 +13220,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="374" spans="1:8">
+    <row r="374" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A374" s="1">
         <v>436</v>
       </c>
@@ -13156,7 +13244,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="375" spans="1:8">
+    <row r="375" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A375" s="1">
         <v>437</v>
       </c>
@@ -13180,7 +13268,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="376" spans="1:8">
+    <row r="376" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A376" s="1">
         <v>438</v>
       </c>
@@ -13204,7 +13292,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="377" spans="1:8">
+    <row r="377" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A377" s="1">
         <v>439</v>
       </c>
@@ -13228,7 +13316,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="378" spans="1:8">
+    <row r="378" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A378" s="1">
         <v>440</v>
       </c>
@@ -13252,7 +13340,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="379" spans="1:8">
+    <row r="379" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A379" s="1">
         <v>441</v>
       </c>
@@ -13276,7 +13364,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="380" spans="1:8">
+    <row r="380" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A380" s="1">
         <v>442</v>
       </c>
@@ -13300,7 +13388,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="381" spans="1:8">
+    <row r="381" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A381" s="1">
         <v>443</v>
       </c>
@@ -13324,7 +13412,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="382" spans="1:8">
+    <row r="382" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A382" s="1">
         <v>444</v>
       </c>
@@ -13348,7 +13436,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="383" spans="1:8">
+    <row r="383" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A383" s="1">
         <v>445</v>
       </c>
@@ -13372,7 +13460,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="384" spans="1:8">
+    <row r="384" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A384" s="1">
         <v>446</v>
       </c>
@@ -13396,7 +13484,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="385" spans="1:8">
+    <row r="385" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A385" s="1">
         <v>447</v>
       </c>
@@ -13420,7 +13508,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="386" spans="1:8">
+    <row r="386" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A386" s="1">
         <v>448</v>
       </c>
@@ -13444,7 +13532,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="387" spans="1:8">
+    <row r="387" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A387" s="1">
         <v>449</v>
       </c>
@@ -13468,7 +13556,7 @@
         <v>P1124</v>
       </c>
     </row>
-    <row r="388" spans="1:8">
+    <row r="388" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A388" s="1">
         <v>450</v>
       </c>
@@ -13492,7 +13580,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="389" spans="1:8">
+    <row r="389" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A389" s="1">
         <v>451</v>
       </c>
@@ -13516,7 +13604,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="390" spans="1:8">
+    <row r="390" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A390" s="1">
         <v>452</v>
       </c>
@@ -13540,7 +13628,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="391" spans="1:8">
+    <row r="391" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A391" s="1">
         <v>453</v>
       </c>
@@ -13564,7 +13652,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="392" spans="1:8">
+    <row r="392" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A392" s="1">
         <v>454</v>
       </c>
@@ -13588,7 +13676,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="393" spans="1:8">
+    <row r="393" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A393" s="1">
         <v>455</v>
       </c>
@@ -13612,7 +13700,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="394" spans="1:8">
+    <row r="394" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A394" s="1">
         <v>456</v>
       </c>
@@ -13636,7 +13724,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="395" spans="1:8">
+    <row r="395" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A395" s="1">
         <v>457</v>
       </c>
@@ -13660,7 +13748,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="396" spans="1:8">
+    <row r="396" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A396" s="1">
         <v>458</v>
       </c>
@@ -13684,7 +13772,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="397" spans="1:8">
+    <row r="397" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A397" s="1">
         <v>459</v>
       </c>
@@ -13708,7 +13796,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="398" spans="1:8">
+    <row r="398" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A398" s="1">
         <v>460</v>
       </c>
@@ -13732,7 +13820,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="399" spans="1:8">
+    <row r="399" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A399" s="1">
         <v>461</v>
       </c>
@@ -13756,7 +13844,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="400" spans="1:8">
+    <row r="400" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A400" s="1">
         <v>462</v>
       </c>
@@ -13780,7 +13868,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="401" spans="1:8">
+    <row r="401" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A401" s="1">
         <v>463</v>
       </c>
@@ -13804,7 +13892,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="402" spans="1:8">
+    <row r="402" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A402" s="1">
         <v>464</v>
       </c>
@@ -13828,7 +13916,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="403" spans="1:8">
+    <row r="403" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A403" s="1">
         <v>465</v>
       </c>
@@ -13852,7 +13940,7 @@
         <v>P1125</v>
       </c>
     </row>
-    <row r="404" spans="1:8">
+    <row r="404" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A404" s="1">
         <v>466</v>
       </c>
@@ -13876,7 +13964,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="405" spans="1:8">
+    <row r="405" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A405" s="1">
         <v>467</v>
       </c>
@@ -13900,7 +13988,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="406" spans="1:8">
+    <row r="406" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A406" s="1">
         <v>468</v>
       </c>
@@ -13924,7 +14012,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="407" spans="1:8">
+    <row r="407" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A407" s="1">
         <v>469</v>
       </c>
@@ -13948,7 +14036,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="408" spans="1:8">
+    <row r="408" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A408" s="1">
         <v>470</v>
       </c>
@@ -13972,7 +14060,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="409" spans="1:8">
+    <row r="409" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A409" s="1">
         <v>471</v>
       </c>
@@ -13996,7 +14084,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="410" spans="1:8">
+    <row r="410" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A410" s="1">
         <v>472</v>
       </c>
@@ -14020,7 +14108,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="411" spans="1:8">
+    <row r="411" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A411" s="1">
         <v>473</v>
       </c>
@@ -14044,7 +14132,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="412" spans="1:8">
+    <row r="412" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A412" s="1">
         <v>474</v>
       </c>
@@ -14068,7 +14156,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="413" spans="1:8">
+    <row r="413" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A413" s="1">
         <v>475</v>
       </c>
@@ -14092,7 +14180,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="414" spans="1:8">
+    <row r="414" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A414" s="1">
         <v>476</v>
       </c>
@@ -14116,7 +14204,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="415" spans="1:8">
+    <row r="415" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A415" s="1">
         <v>477</v>
       </c>
@@ -14140,7 +14228,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="416" spans="1:8">
+    <row r="416" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A416" s="1">
         <v>478</v>
       </c>
@@ -14164,7 +14252,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="417" spans="1:8">
+    <row r="417" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A417" s="1">
         <v>479</v>
       </c>
@@ -14188,7 +14276,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="418" spans="1:8">
+    <row r="418" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A418" s="1">
         <v>480</v>
       </c>
@@ -14212,7 +14300,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="419" spans="1:8">
+    <row r="419" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A419" s="1">
         <v>481</v>
       </c>
@@ -14236,7 +14324,7 @@
         <v>P1126</v>
       </c>
     </row>
-    <row r="420" spans="1:8">
+    <row r="420" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A420" s="1">
         <v>482</v>
       </c>
@@ -14260,7 +14348,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="421" spans="1:8">
+    <row r="421" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A421" s="1">
         <v>483</v>
       </c>
@@ -14284,7 +14372,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="422" spans="1:8">
+    <row r="422" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A422" s="1">
         <v>484</v>
       </c>
@@ -14308,7 +14396,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="423" spans="1:8">
+    <row r="423" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A423" s="1">
         <v>485</v>
       </c>
@@ -14332,7 +14420,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="424" spans="1:8">
+    <row r="424" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A424" s="1">
         <v>486</v>
       </c>
@@ -14356,7 +14444,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="425" spans="1:8">
+    <row r="425" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A425" s="1">
         <v>487</v>
       </c>
@@ -14380,7 +14468,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="426" spans="1:8">
+    <row r="426" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A426" s="1">
         <v>488</v>
       </c>
@@ -14404,7 +14492,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="427" spans="1:8">
+    <row r="427" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A427" s="1">
         <v>489</v>
       </c>
@@ -14428,7 +14516,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="428" spans="1:8">
+    <row r="428" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A428" s="1">
         <v>490</v>
       </c>
@@ -14452,7 +14540,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="429" spans="1:8">
+    <row r="429" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A429" s="1">
         <v>491</v>
       </c>
@@ -14476,7 +14564,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="430" spans="1:8">
+    <row r="430" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A430" s="1">
         <v>492</v>
       </c>
@@ -14500,7 +14588,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="431" spans="1:8">
+    <row r="431" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A431" s="1">
         <v>493</v>
       </c>
@@ -14524,7 +14612,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="432" spans="1:8">
+    <row r="432" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A432" s="1">
         <v>494</v>
       </c>
@@ -14548,7 +14636,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="433" spans="1:8">
+    <row r="433" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A433" s="1">
         <v>495</v>
       </c>
@@ -14572,7 +14660,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="434" spans="1:8">
+    <row r="434" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A434" s="1">
         <v>496</v>
       </c>
@@ -14596,7 +14684,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="435" spans="1:8">
+    <row r="435" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A435" s="1">
         <v>497</v>
       </c>
@@ -14620,7 +14708,7 @@
         <v>P1127</v>
       </c>
     </row>
-    <row r="436" spans="1:8">
+    <row r="436" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A436" s="1">
         <v>498</v>
       </c>
@@ -14644,7 +14732,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="437" spans="1:8">
+    <row r="437" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A437" s="1">
         <v>499</v>
       </c>
@@ -14668,7 +14756,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="438" spans="1:8">
+    <row r="438" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A438" s="1">
         <v>500</v>
       </c>
@@ -14692,7 +14780,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="439" spans="1:8">
+    <row r="439" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A439" s="1">
         <v>501</v>
       </c>
@@ -14716,7 +14804,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="440" spans="1:8">
+    <row r="440" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A440" s="1">
         <v>502</v>
       </c>
@@ -14740,7 +14828,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="441" spans="1:8">
+    <row r="441" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A441" s="1">
         <v>503</v>
       </c>
@@ -14764,7 +14852,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="442" spans="1:8">
+    <row r="442" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A442" s="1">
         <v>504</v>
       </c>
@@ -14788,7 +14876,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="443" spans="1:8">
+    <row r="443" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A443" s="1">
         <v>505</v>
       </c>
@@ -14812,7 +14900,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="444" spans="1:8">
+    <row r="444" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A444" s="1">
         <v>506</v>
       </c>
@@ -14836,7 +14924,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="445" spans="1:8">
+    <row r="445" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A445" s="1">
         <v>507</v>
       </c>
@@ -14860,7 +14948,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="446" spans="1:8">
+    <row r="446" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A446" s="1">
         <v>508</v>
       </c>
@@ -14884,7 +14972,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="447" spans="1:8">
+    <row r="447" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A447" s="1">
         <v>509</v>
       </c>
@@ -14908,7 +14996,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="448" spans="1:8">
+    <row r="448" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A448" s="1">
         <v>510</v>
       </c>
@@ -14932,7 +15020,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="449" spans="1:8">
+    <row r="449" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A449" s="1">
         <v>511</v>
       </c>
@@ -14956,7 +15044,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="450" spans="1:8">
+    <row r="450" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A450" s="1">
         <v>512</v>
       </c>
@@ -14980,7 +15068,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="451" spans="1:8">
+    <row r="451" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A451" s="1">
         <v>513</v>
       </c>
@@ -15004,7 +15092,7 @@
         <v>P1128</v>
       </c>
     </row>
-    <row r="452" spans="1:8">
+    <row r="452" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A452" s="1">
         <v>514</v>
       </c>
@@ -15028,7 +15116,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="453" spans="1:8">
+    <row r="453" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A453" s="1">
         <v>515</v>
       </c>
@@ -15052,7 +15140,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="454" spans="1:8">
+    <row r="454" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A454" s="1">
         <v>516</v>
       </c>
@@ -15076,7 +15164,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="455" spans="1:8">
+    <row r="455" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A455" s="1">
         <v>517</v>
       </c>
@@ -15100,7 +15188,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="456" spans="1:8">
+    <row r="456" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A456" s="1">
         <v>518</v>
       </c>
@@ -15124,7 +15212,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="457" spans="1:8">
+    <row r="457" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A457" s="1">
         <v>519</v>
       </c>
@@ -15148,7 +15236,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="458" spans="1:8">
+    <row r="458" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A458" s="1">
         <v>520</v>
       </c>
@@ -15172,7 +15260,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="459" spans="1:8">
+    <row r="459" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A459" s="1">
         <v>521</v>
       </c>
@@ -15196,7 +15284,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="460" spans="1:8">
+    <row r="460" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A460" s="1">
         <v>522</v>
       </c>
@@ -15220,7 +15308,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="461" spans="1:8">
+    <row r="461" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A461" s="1">
         <v>523</v>
       </c>
@@ -15244,7 +15332,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="462" spans="1:8">
+    <row r="462" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A462" s="1">
         <v>524</v>
       </c>
@@ -15268,7 +15356,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="463" spans="1:8">
+    <row r="463" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A463" s="1">
         <v>525</v>
       </c>
@@ -15292,7 +15380,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="464" spans="1:8">
+    <row r="464" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A464" s="1">
         <v>526</v>
       </c>
@@ -15316,7 +15404,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="465" spans="1:8">
+    <row r="465" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A465" s="1">
         <v>527</v>
       </c>
@@ -15340,7 +15428,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="466" spans="1:8">
+    <row r="466" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A466" s="1">
         <v>528</v>
       </c>
@@ -15364,7 +15452,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="467" spans="1:8">
+    <row r="467" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A467" s="1">
         <v>529</v>
       </c>
@@ -15388,7 +15476,7 @@
         <v>P1129</v>
       </c>
     </row>
-    <row r="468" spans="1:8">
+    <row r="468" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A468" s="1">
         <v>530</v>
       </c>
@@ -15412,7 +15500,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="469" spans="1:8">
+    <row r="469" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A469" s="1">
         <v>531</v>
       </c>
@@ -15436,7 +15524,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="470" spans="1:8">
+    <row r="470" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A470" s="1">
         <v>532</v>
       </c>
@@ -15460,7 +15548,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="471" spans="1:8">
+    <row r="471" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A471" s="1">
         <v>533</v>
       </c>
@@ -15484,7 +15572,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="472" spans="1:8">
+    <row r="472" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A472" s="1">
         <v>534</v>
       </c>
@@ -15508,7 +15596,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="473" spans="1:8">
+    <row r="473" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A473" s="1">
         <v>535</v>
       </c>
@@ -15532,7 +15620,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="474" spans="1:8">
+    <row r="474" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A474" s="1">
         <v>536</v>
       </c>
@@ -15556,7 +15644,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="475" spans="1:8">
+    <row r="475" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A475" s="1">
         <v>537</v>
       </c>
@@ -15580,7 +15668,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="476" spans="1:8">
+    <row r="476" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A476" s="1">
         <v>538</v>
       </c>
@@ -15604,7 +15692,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="477" spans="1:8">
+    <row r="477" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A477" s="1">
         <v>539</v>
       </c>
@@ -15628,7 +15716,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="478" spans="1:8">
+    <row r="478" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A478" s="1">
         <v>540</v>
       </c>
@@ -15652,7 +15740,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="479" spans="1:8">
+    <row r="479" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A479" s="1">
         <v>541</v>
       </c>
@@ -15676,7 +15764,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="480" spans="1:8">
+    <row r="480" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A480" s="1">
         <v>542</v>
       </c>
@@ -15700,7 +15788,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="481" spans="1:8">
+    <row r="481" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A481" s="1">
         <v>543</v>
       </c>
@@ -15724,7 +15812,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="482" spans="1:8">
+    <row r="482" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A482" s="1">
         <v>544</v>
       </c>
@@ -15748,7 +15836,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="483" spans="1:8">
+    <row r="483" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A483" s="1">
         <v>545</v>
       </c>
@@ -15772,7 +15860,7 @@
         <v>P1130</v>
       </c>
     </row>
-    <row r="484" spans="1:8">
+    <row r="484" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A484" s="1">
         <v>546</v>
       </c>
@@ -15796,7 +15884,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="485" spans="1:8">
+    <row r="485" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A485" s="1">
         <v>547</v>
       </c>
@@ -15820,7 +15908,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="486" spans="1:8">
+    <row r="486" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A486" s="1">
         <v>548</v>
       </c>
@@ -15844,7 +15932,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="487" spans="1:8">
+    <row r="487" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A487" s="1">
         <v>549</v>
       </c>
@@ -15868,7 +15956,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="488" spans="1:8">
+    <row r="488" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A488" s="1">
         <v>550</v>
       </c>
@@ -15892,7 +15980,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="489" spans="1:8">
+    <row r="489" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A489" s="1">
         <v>551</v>
       </c>
@@ -15916,7 +16004,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="490" spans="1:8">
+    <row r="490" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A490" s="1">
         <v>552</v>
       </c>
@@ -15940,7 +16028,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="491" spans="1:8">
+    <row r="491" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A491" s="1">
         <v>553</v>
       </c>
@@ -15964,7 +16052,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="492" spans="1:8">
+    <row r="492" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A492" s="1">
         <v>554</v>
       </c>
@@ -15988,7 +16076,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="493" spans="1:8">
+    <row r="493" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A493" s="1">
         <v>555</v>
       </c>
@@ -16012,7 +16100,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="494" spans="1:8">
+    <row r="494" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A494" s="1">
         <v>556</v>
       </c>
@@ -16036,7 +16124,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="495" spans="1:8">
+    <row r="495" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A495" s="1">
         <v>557</v>
       </c>
@@ -16060,7 +16148,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="496" spans="1:8">
+    <row r="496" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A496" s="1">
         <v>558</v>
       </c>
@@ -16084,7 +16172,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="497" spans="1:8">
+    <row r="497" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A497" s="1">
         <v>559</v>
       </c>
@@ -16108,7 +16196,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="498" spans="1:8">
+    <row r="498" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A498" s="1">
         <v>560</v>
       </c>
@@ -16132,7 +16220,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="499" spans="1:8">
+    <row r="499" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A499" s="1">
         <v>561</v>
       </c>
@@ -16156,7 +16244,7 @@
         <v>P1131</v>
       </c>
     </row>
-    <row r="500" spans="1:8">
+    <row r="500" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A500" s="1">
         <v>562</v>
       </c>
@@ -16180,7 +16268,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="501" spans="1:8">
+    <row r="501" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A501" s="1">
         <v>563</v>
       </c>
@@ -16204,7 +16292,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="502" spans="1:8">
+    <row r="502" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A502" s="1">
         <v>564</v>
       </c>
@@ -16228,7 +16316,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="503" spans="1:8">
+    <row r="503" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A503" s="1">
         <v>565</v>
       </c>
@@ -16252,7 +16340,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="504" spans="1:8">
+    <row r="504" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A504" s="1">
         <v>566</v>
       </c>
@@ -16276,7 +16364,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="505" spans="1:8">
+    <row r="505" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A505" s="1">
         <v>567</v>
       </c>
@@ -16300,7 +16388,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="506" spans="1:8">
+    <row r="506" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A506" s="1">
         <v>568</v>
       </c>
@@ -16324,7 +16412,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="507" spans="1:8">
+    <row r="507" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A507" s="1">
         <v>569</v>
       </c>
@@ -16348,7 +16436,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="508" spans="1:8">
+    <row r="508" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A508" s="1">
         <v>570</v>
       </c>
@@ -16372,7 +16460,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="509" spans="1:8">
+    <row r="509" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A509" s="1">
         <v>571</v>
       </c>
@@ -16396,7 +16484,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="510" spans="1:8">
+    <row r="510" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A510" s="1">
         <v>572</v>
       </c>
@@ -16420,7 +16508,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="511" spans="1:8">
+    <row r="511" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A511" s="1">
         <v>573</v>
       </c>
@@ -16444,7 +16532,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="512" spans="1:8">
+    <row r="512" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A512" s="1">
         <v>574</v>
       </c>
@@ -16468,7 +16556,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="513" spans="1:8">
+    <row r="513" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A513" s="1">
         <v>575</v>
       </c>
@@ -16492,7 +16580,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="514" spans="1:8">
+    <row r="514" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A514" s="1">
         <v>576</v>
       </c>
@@ -16516,7 +16604,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="515" spans="1:8">
+    <row r="515" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A515" s="1">
         <v>577</v>
       </c>
@@ -16540,7 +16628,7 @@
         <v>P1132</v>
       </c>
     </row>
-    <row r="516" spans="1:8">
+    <row r="516" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A516" s="1">
         <v>578</v>
       </c>
@@ -16564,7 +16652,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="517" spans="1:8">
+    <row r="517" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A517" s="1">
         <v>579</v>
       </c>
@@ -16588,7 +16676,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="518" spans="1:8">
+    <row r="518" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A518" s="1">
         <v>580</v>
       </c>
@@ -16612,7 +16700,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="519" spans="1:8">
+    <row r="519" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A519" s="1">
         <v>581</v>
       </c>
@@ -16636,7 +16724,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="520" spans="1:8">
+    <row r="520" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A520" s="1">
         <v>582</v>
       </c>
@@ -16660,7 +16748,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="521" spans="1:8">
+    <row r="521" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A521" s="1">
         <v>583</v>
       </c>
@@ -16684,7 +16772,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="522" spans="1:8">
+    <row r="522" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A522" s="1">
         <v>584</v>
       </c>
@@ -16708,7 +16796,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="523" spans="1:8">
+    <row r="523" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A523" s="1">
         <v>585</v>
       </c>
@@ -16732,7 +16820,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="524" spans="1:8">
+    <row r="524" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A524" s="1">
         <v>586</v>
       </c>
@@ -16756,7 +16844,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="525" spans="1:8">
+    <row r="525" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A525" s="1">
         <v>587</v>
       </c>
@@ -16780,7 +16868,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="526" spans="1:8">
+    <row r="526" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A526" s="1">
         <v>588</v>
       </c>
@@ -16804,7 +16892,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="527" spans="1:8">
+    <row r="527" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A527" s="1">
         <v>589</v>
       </c>
@@ -16828,7 +16916,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="528" spans="1:8">
+    <row r="528" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A528" s="1">
         <v>590</v>
       </c>
@@ -16852,7 +16940,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="529" spans="1:8">
+    <row r="529" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A529" s="1">
         <v>591</v>
       </c>
@@ -16876,7 +16964,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="530" spans="1:8">
+    <row r="530" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A530" s="1">
         <v>592</v>
       </c>
@@ -16900,7 +16988,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="531" spans="1:8">
+    <row r="531" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A531" s="1">
         <v>593</v>
       </c>
@@ -16924,7 +17012,7 @@
         <v>P1133</v>
       </c>
     </row>
-    <row r="532" spans="1:8">
+    <row r="532" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A532" s="1">
         <v>594</v>
       </c>
@@ -16948,7 +17036,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="533" spans="1:8">
+    <row r="533" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A533" s="1">
         <v>595</v>
       </c>
@@ -16972,7 +17060,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="534" spans="1:8">
+    <row r="534" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A534" s="1">
         <v>596</v>
       </c>
@@ -16996,7 +17084,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="535" spans="1:8">
+    <row r="535" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A535" s="1">
         <v>597</v>
       </c>
@@ -17020,7 +17108,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="536" spans="1:8">
+    <row r="536" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A536" s="1">
         <v>598</v>
       </c>
@@ -17044,7 +17132,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="537" spans="1:8">
+    <row r="537" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A537" s="1">
         <v>599</v>
       </c>
@@ -17068,7 +17156,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="538" spans="1:8">
+    <row r="538" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A538" s="1">
         <v>600</v>
       </c>
@@ -17092,7 +17180,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="539" spans="1:8">
+    <row r="539" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A539" s="1">
         <v>601</v>
       </c>
@@ -17116,7 +17204,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="540" spans="1:8">
+    <row r="540" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A540" s="1">
         <v>602</v>
       </c>
@@ -17140,7 +17228,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="541" spans="1:8">
+    <row r="541" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A541" s="1">
         <v>603</v>
       </c>
@@ -17164,7 +17252,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="542" spans="1:8">
+    <row r="542" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A542" s="1">
         <v>604</v>
       </c>
@@ -17188,7 +17276,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="543" spans="1:8">
+    <row r="543" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A543" s="1">
         <v>605</v>
       </c>
@@ -17212,7 +17300,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="544" spans="1:8">
+    <row r="544" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A544" s="1">
         <v>606</v>
       </c>
@@ -17236,7 +17324,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="545" spans="1:8">
+    <row r="545" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A545" s="1">
         <v>607</v>
       </c>
@@ -17260,7 +17348,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="546" spans="1:8">
+    <row r="546" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A546" s="1">
         <v>608</v>
       </c>
@@ -17284,7 +17372,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="547" spans="1:8">
+    <row r="547" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A547" s="1">
         <v>609</v>
       </c>
@@ -17308,7 +17396,7 @@
         <v>P1134</v>
       </c>
     </row>
-    <row r="548" spans="1:8">
+    <row r="548" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A548" s="1">
         <v>610</v>
       </c>
@@ -17332,7 +17420,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="549" spans="1:8">
+    <row r="549" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A549" s="1">
         <v>611</v>
       </c>
@@ -17356,7 +17444,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="550" spans="1:8">
+    <row r="550" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A550" s="1">
         <v>612</v>
       </c>
@@ -17380,7 +17468,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="551" spans="1:8">
+    <row r="551" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A551" s="1">
         <v>613</v>
       </c>
@@ -17404,7 +17492,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="552" spans="1:8">
+    <row r="552" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A552" s="1">
         <v>614</v>
       </c>
@@ -17428,7 +17516,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="553" spans="1:8">
+    <row r="553" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A553" s="1">
         <v>615</v>
       </c>
@@ -17452,7 +17540,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="554" spans="1:8">
+    <row r="554" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A554" s="1">
         <v>616</v>
       </c>
@@ -17476,7 +17564,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="555" spans="1:8">
+    <row r="555" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A555" s="1">
         <v>617</v>
       </c>
@@ -17500,7 +17588,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="556" spans="1:8">
+    <row r="556" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A556" s="1">
         <v>618</v>
       </c>
@@ -17524,7 +17612,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="557" spans="1:8">
+    <row r="557" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A557" s="1">
         <v>619</v>
       </c>
@@ -17548,7 +17636,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="558" spans="1:8">
+    <row r="558" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A558" s="1">
         <v>620</v>
       </c>
@@ -17572,7 +17660,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="559" spans="1:8">
+    <row r="559" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A559" s="1">
         <v>621</v>
       </c>
@@ -17596,7 +17684,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="560" spans="1:8">
+    <row r="560" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A560" s="1">
         <v>622</v>
       </c>
@@ -17620,7 +17708,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="561" spans="1:8">
+    <row r="561" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A561" s="1">
         <v>623</v>
       </c>
@@ -17644,7 +17732,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="562" spans="1:8">
+    <row r="562" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A562" s="1">
         <v>624</v>
       </c>
@@ -17668,7 +17756,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="563" spans="1:8">
+    <row r="563" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A563" s="1">
         <v>625</v>
       </c>
@@ -17692,7 +17780,7 @@
         <v>P1135</v>
       </c>
     </row>
-    <row r="564" spans="1:8">
+    <row r="564" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A564" s="1">
         <v>626</v>
       </c>
@@ -17716,7 +17804,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="565" spans="1:8">
+    <row r="565" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A565" s="1">
         <v>627</v>
       </c>
@@ -17740,7 +17828,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="566" spans="1:8">
+    <row r="566" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A566" s="1">
         <v>628</v>
       </c>
@@ -17764,7 +17852,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="567" spans="1:8">
+    <row r="567" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A567" s="1">
         <v>629</v>
       </c>
@@ -17788,7 +17876,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="568" spans="1:8">
+    <row r="568" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A568" s="1">
         <v>630</v>
       </c>
@@ -17812,7 +17900,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="569" spans="1:8">
+    <row r="569" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A569" s="1">
         <v>631</v>
       </c>
@@ -17836,7 +17924,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="570" spans="1:8">
+    <row r="570" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A570" s="1">
         <v>632</v>
       </c>
@@ -17860,7 +17948,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="571" spans="1:8">
+    <row r="571" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A571" s="1">
         <v>633</v>
       </c>
@@ -17884,7 +17972,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="572" spans="1:8">
+    <row r="572" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A572" s="1">
         <v>634</v>
       </c>
@@ -17908,7 +17996,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="573" spans="1:8">
+    <row r="573" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A573" s="1">
         <v>635</v>
       </c>
@@ -17932,7 +18020,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="574" spans="1:8">
+    <row r="574" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A574" s="1">
         <v>636</v>
       </c>
@@ -17956,7 +18044,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="575" spans="1:8">
+    <row r="575" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A575" s="1">
         <v>637</v>
       </c>
@@ -17980,7 +18068,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="576" spans="1:8">
+    <row r="576" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A576" s="1">
         <v>638</v>
       </c>
@@ -18004,7 +18092,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="577" spans="1:9">
+    <row r="577" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A577" s="1">
         <v>639</v>
       </c>
@@ -18028,7 +18116,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="578" spans="1:9" ht="14.4">
+    <row r="578" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A578" s="1">
         <v>640</v>
       </c>
@@ -18053,7 +18141,7 @@
       </c>
       <c r="I578" s="4"/>
     </row>
-    <row r="579" spans="1:9" ht="14.4">
+    <row r="579" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A579" s="1">
         <v>641</v>
       </c>
@@ -18078,7 +18166,7 @@
       </c>
       <c r="I579" s="4"/>
     </row>
-    <row r="580" spans="1:9" ht="14.4">
+    <row r="580" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A580" s="1">
         <v>642</v>
       </c>
@@ -18103,7 +18191,7 @@
       </c>
       <c r="I580" s="4"/>
     </row>
-    <row r="581" spans="1:9" ht="14.4">
+    <row r="581" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A581" s="1">
         <v>643</v>
       </c>
@@ -18128,7 +18216,7 @@
       </c>
       <c r="I581" s="4"/>
     </row>
-    <row r="582" spans="1:9" ht="14.4">
+    <row r="582" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A582" s="1">
         <v>644</v>
       </c>
@@ -18153,7 +18241,7 @@
       </c>
       <c r="I582" s="4"/>
     </row>
-    <row r="583" spans="1:9" ht="14.4">
+    <row r="583" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A583" s="1">
         <v>645</v>
       </c>
@@ -18178,7 +18266,7 @@
       </c>
       <c r="I583" s="4"/>
     </row>
-    <row r="584" spans="1:9" ht="14.4">
+    <row r="584" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A584" s="1">
         <v>646</v>
       </c>
@@ -18203,7 +18291,7 @@
       </c>
       <c r="I584" s="4"/>
     </row>
-    <row r="585" spans="1:9" ht="14.4">
+    <row r="585" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A585" s="1">
         <v>647</v>
       </c>
@@ -18228,7 +18316,7 @@
       </c>
       <c r="I585" s="4"/>
     </row>
-    <row r="586" spans="1:9" ht="14.4">
+    <row r="586" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A586" s="1">
         <v>648</v>
       </c>
@@ -18253,7 +18341,7 @@
       </c>
       <c r="I586" s="4"/>
     </row>
-    <row r="587" spans="1:9" ht="14.4">
+    <row r="587" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A587" s="1">
         <v>649</v>
       </c>
@@ -18278,7 +18366,7 @@
       </c>
       <c r="I587" s="4"/>
     </row>
-    <row r="588" spans="1:9" ht="14.4">
+    <row r="588" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A588" s="1">
         <v>650</v>
       </c>
@@ -18303,7 +18391,7 @@
       </c>
       <c r="I588" s="4"/>
     </row>
-    <row r="589" spans="1:9" ht="14.4">
+    <row r="589" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A589" s="1">
         <v>651</v>
       </c>
@@ -18328,7 +18416,7 @@
       </c>
       <c r="I589" s="4"/>
     </row>
-    <row r="590" spans="1:9" ht="14.4">
+    <row r="590" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A590" s="1">
         <v>652</v>
       </c>
@@ -18355,7 +18443,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="591" spans="1:9" ht="14.4">
+    <row r="591" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A591" s="1">
         <v>653</v>
       </c>
@@ -18382,7 +18470,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="592" spans="1:9" ht="14.4">
+    <row r="592" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A592" s="1">
         <v>654</v>
       </c>
@@ -18409,7 +18497,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="593" spans="1:10" ht="14.4">
+    <row r="593" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A593" s="1">
         <v>655</v>
       </c>
@@ -18432,11 +18520,11 @@
         <f t="shared" si="44"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I593" s="14" t="s">
+      <c r="I593" s="12" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="594" spans="1:10" ht="14.4">
+    <row r="594" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A594" s="1">
         <v>656</v>
       </c>
@@ -18459,11 +18547,11 @@
         <f t="shared" si="44"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I594" s="14" t="s">
+      <c r="I594" s="12" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="595" spans="1:10" ht="14.4">
+    <row r="595" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A595" s="1">
         <v>657</v>
       </c>
@@ -18490,7 +18578,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="596" spans="1:10">
+    <row r="596" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A596" s="1">
         <v>658</v>
       </c>
@@ -18514,7 +18602,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="597" spans="1:10" ht="14.4">
+    <row r="597" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A597" s="1">
         <v>659</v>
       </c>
@@ -18541,7 +18629,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="598" spans="1:10">
+    <row r="598" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A598" s="1">
         <v>660</v>
       </c>
@@ -18565,7 +18653,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="599" spans="1:10" ht="14.4">
+    <row r="599" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A599" s="1">
         <v>661</v>
       </c>
@@ -18588,14 +18676,14 @@
         <f t="shared" si="44"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I599" s="14" t="s">
+      <c r="I599" s="12" t="s">
         <v>344</v>
       </c>
       <c r="J599" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="600" spans="1:10">
+    <row r="600" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A600" s="1">
         <v>662</v>
       </c>
@@ -18619,7 +18707,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="601" spans="1:10" ht="14.4">
+    <row r="601" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A601" s="1">
         <v>663</v>
       </c>
@@ -18642,14 +18730,14 @@
         <f t="shared" si="44"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I601" s="14" t="s">
+      <c r="I601" s="12" t="s">
         <v>343</v>
       </c>
       <c r="J601" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="602" spans="1:10">
+    <row r="602" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A602" s="1">
         <v>664</v>
       </c>
@@ -18673,7 +18761,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="603" spans="1:10" ht="14.4">
+    <row r="603" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A603" s="1">
         <v>665</v>
       </c>
@@ -18700,7 +18788,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="604" spans="1:10">
+    <row r="604" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A604" s="1">
         <v>666</v>
       </c>
@@ -18724,7 +18812,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="605" spans="1:10">
+    <row r="605" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A605" s="1">
         <v>667</v>
       </c>
@@ -18748,7 +18836,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="606" spans="1:10">
+    <row r="606" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A606" s="1">
         <v>668</v>
       </c>
@@ -18772,7 +18860,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="607" spans="1:10">
+    <row r="607" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A607" s="1">
         <v>669</v>
       </c>
@@ -18796,7 +18884,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="608" spans="1:10">
+    <row r="608" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A608" s="1">
         <v>670</v>
       </c>
@@ -18820,7 +18908,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="609" spans="1:9">
+    <row r="609" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A609" s="1">
         <v>671</v>
       </c>
@@ -18844,7 +18932,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="610" spans="1:9">
+    <row r="610" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A610" s="1">
         <v>672</v>
       </c>
@@ -18868,7 +18956,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="611" spans="1:9" ht="14.4">
+    <row r="611" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A611" s="1">
         <v>673</v>
       </c>
@@ -18895,7 +18983,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="612" spans="1:9">
+    <row r="612" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A612" s="1">
         <v>674</v>
       </c>
@@ -18919,7 +19007,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="613" spans="1:9">
+    <row r="613" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A613" s="1">
         <v>675</v>
       </c>
@@ -18943,7 +19031,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="614" spans="1:9">
+    <row r="614" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A614" s="1">
         <v>676</v>
       </c>
@@ -18967,7 +19055,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="615" spans="1:9">
+    <row r="615" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A615" s="1">
         <v>677</v>
       </c>
@@ -18991,7 +19079,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="616" spans="1:9">
+    <row r="616" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A616" s="1">
         <v>678</v>
       </c>
@@ -19015,7 +19103,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="617" spans="1:9">
+    <row r="617" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A617" s="1">
         <v>679</v>
       </c>
@@ -19039,7 +19127,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="618" spans="1:9">
+    <row r="618" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A618" s="1">
         <v>680</v>
       </c>
@@ -19063,7 +19151,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="619" spans="1:9">
+    <row r="619" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A619" s="1">
         <v>681</v>
       </c>
@@ -19087,7 +19175,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="620" spans="1:9">
+    <row r="620" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A620" s="1">
         <v>682</v>
       </c>
@@ -19111,7 +19199,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="621" spans="1:9">
+    <row r="621" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A621" s="1">
         <v>683</v>
       </c>
@@ -19135,7 +19223,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="622" spans="1:9">
+    <row r="622" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A622" s="1">
         <v>684</v>
       </c>
@@ -19159,7 +19247,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="623" spans="1:9">
+    <row r="623" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A623" s="1">
         <v>685</v>
       </c>
@@ -19183,7 +19271,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="624" spans="1:9">
+    <row r="624" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A624" s="1">
         <v>686</v>
       </c>
@@ -19207,7 +19295,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="625" spans="1:9">
+    <row r="625" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A625" s="1">
         <v>687</v>
       </c>
@@ -19231,7 +19319,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="626" spans="1:9">
+    <row r="626" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A626" s="1">
         <v>688</v>
       </c>
@@ -19255,7 +19343,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="627" spans="1:9" ht="14.4">
+    <row r="627" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A627" s="1">
         <v>689</v>
       </c>
@@ -19282,7 +19370,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="628" spans="1:9">
+    <row r="628" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A628" s="1">
         <v>690</v>
       </c>
@@ -19306,7 +19394,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="629" spans="1:9">
+    <row r="629" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A629" s="1">
         <v>691</v>
       </c>
@@ -19330,7 +19418,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="630" spans="1:9">
+    <row r="630" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A630" s="1">
         <v>692</v>
       </c>
@@ -19354,7 +19442,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="631" spans="1:9">
+    <row r="631" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A631" s="1">
         <v>693</v>
       </c>
@@ -19378,7 +19466,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="632" spans="1:9">
+    <row r="632" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A632" s="1">
         <v>694</v>
       </c>
@@ -19402,7 +19490,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="633" spans="1:9">
+    <row r="633" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A633" s="1">
         <v>695</v>
       </c>
@@ -19426,7 +19514,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="634" spans="1:9">
+    <row r="634" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A634" s="1">
         <v>696</v>
       </c>
@@ -19450,7 +19538,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="635" spans="1:9">
+    <row r="635" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A635" s="1">
         <v>697</v>
       </c>
@@ -19474,7 +19562,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="636" spans="1:9">
+    <row r="636" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A636" s="1">
         <v>698</v>
       </c>
@@ -19498,7 +19586,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="637" spans="1:9">
+    <row r="637" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A637" s="1">
         <v>699</v>
       </c>
@@ -19522,7 +19610,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="638" spans="1:9">
+    <row r="638" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A638" s="1">
         <v>700</v>
       </c>
@@ -19546,7 +19634,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="639" spans="1:9">
+    <row r="639" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A639" s="1">
         <v>701</v>
       </c>
@@ -19570,7 +19658,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="640" spans="1:9">
+    <row r="640" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A640" s="1">
         <v>702</v>
       </c>
@@ -19594,7 +19682,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="641" spans="1:9">
+    <row r="641" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A641" s="1">
         <v>703</v>
       </c>
@@ -19618,7 +19706,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="642" spans="1:9">
+    <row r="642" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A642" s="1">
         <v>704</v>
       </c>
@@ -19642,7 +19730,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="643" spans="1:9" ht="14.4">
+    <row r="643" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A643" s="1">
         <v>705</v>
       </c>
@@ -19669,7 +19757,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="644" spans="1:9">
+    <row r="644" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A644" s="1">
         <v>706</v>
       </c>
@@ -19693,7 +19781,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="645" spans="1:9">
+    <row r="645" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A645" s="1">
         <v>707</v>
       </c>
@@ -19717,7 +19805,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="646" spans="1:9">
+    <row r="646" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A646" s="1">
         <v>708</v>
       </c>
@@ -19741,7 +19829,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="647" spans="1:9">
+    <row r="647" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A647" s="1">
         <v>709</v>
       </c>
@@ -19765,7 +19853,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="648" spans="1:9">
+    <row r="648" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A648" s="1">
         <v>710</v>
       </c>
@@ -19789,7 +19877,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="649" spans="1:9">
+    <row r="649" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A649" s="1">
         <v>711</v>
       </c>
@@ -19813,7 +19901,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="650" spans="1:9">
+    <row r="650" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A650" s="1">
         <v>712</v>
       </c>
@@ -19837,7 +19925,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="651" spans="1:9">
+    <row r="651" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A651" s="1">
         <v>713</v>
       </c>
@@ -19861,7 +19949,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="652" spans="1:9">
+    <row r="652" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A652" s="1">
         <v>714</v>
       </c>
@@ -19885,7 +19973,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="653" spans="1:9">
+    <row r="653" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A653" s="1">
         <v>715</v>
       </c>
@@ -19909,7 +19997,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="654" spans="1:9">
+    <row r="654" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A654" s="1">
         <v>716</v>
       </c>
@@ -19933,7 +20021,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="655" spans="1:9">
+    <row r="655" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A655" s="1">
         <v>717</v>
       </c>
@@ -19957,7 +20045,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="656" spans="1:9">
+    <row r="656" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A656" s="1">
         <v>718</v>
       </c>
@@ -19981,7 +20069,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="657" spans="1:9">
+    <row r="657" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A657" s="1">
         <v>719</v>
       </c>
@@ -20005,7 +20093,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="658" spans="1:9">
+    <row r="658" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A658" s="1">
         <v>720</v>
       </c>
@@ -20029,7 +20117,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="659" spans="1:9" ht="14.4">
+    <row r="659" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A659" s="1">
         <v>721</v>
       </c>
@@ -20056,7 +20144,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="660" spans="1:9">
+    <row r="660" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A660" s="1">
         <v>722</v>
       </c>
@@ -20080,7 +20168,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="661" spans="1:9">
+    <row r="661" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A661" s="1">
         <v>723</v>
       </c>
@@ -20104,7 +20192,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="662" spans="1:9">
+    <row r="662" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A662" s="1">
         <v>724</v>
       </c>
@@ -20128,7 +20216,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="663" spans="1:9">
+    <row r="663" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A663" s="1">
         <v>725</v>
       </c>
@@ -20152,7 +20240,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="664" spans="1:9">
+    <row r="664" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A664" s="1">
         <v>726</v>
       </c>
@@ -20176,7 +20264,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="665" spans="1:9">
+    <row r="665" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A665" s="1">
         <v>727</v>
       </c>
@@ -20200,7 +20288,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="666" spans="1:9">
+    <row r="666" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A666" s="1">
         <v>728</v>
       </c>
@@ -20224,7 +20312,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="667" spans="1:9">
+    <row r="667" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A667" s="1">
         <v>729</v>
       </c>
@@ -20248,7 +20336,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="668" spans="1:9">
+    <row r="668" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A668" s="1">
         <v>730</v>
       </c>
@@ -20272,7 +20360,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="669" spans="1:9">
+    <row r="669" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A669" s="1">
         <v>731</v>
       </c>
@@ -20296,7 +20384,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="670" spans="1:9">
+    <row r="670" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A670" s="1">
         <v>732</v>
       </c>
@@ -20320,7 +20408,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="671" spans="1:9">
+    <row r="671" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A671" s="1">
         <v>733</v>
       </c>
@@ -20344,7 +20432,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="672" spans="1:9">
+    <row r="672" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A672" s="1">
         <v>734</v>
       </c>
@@ -20368,7 +20456,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="673" spans="1:9">
+    <row r="673" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A673" s="1">
         <v>735</v>
       </c>
@@ -20392,7 +20480,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="674" spans="1:9">
+    <row r="674" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A674" s="1">
         <v>736</v>
       </c>
@@ -20416,7 +20504,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="675" spans="1:9" ht="14.4">
+    <row r="675" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A675" s="1">
         <v>737</v>
       </c>
@@ -20443,7 +20531,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="676" spans="1:9">
+    <row r="676" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A676" s="1">
         <v>738</v>
       </c>
@@ -20467,7 +20555,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="677" spans="1:9">
+    <row r="677" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A677" s="1">
         <v>739</v>
       </c>
@@ -20491,7 +20579,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="678" spans="1:9">
+    <row r="678" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A678" s="1">
         <v>740</v>
       </c>
@@ -20515,7 +20603,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="679" spans="1:9">
+    <row r="679" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A679" s="1">
         <v>741</v>
       </c>
@@ -20539,7 +20627,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="680" spans="1:9">
+    <row r="680" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A680" s="1">
         <v>742</v>
       </c>
@@ -20563,7 +20651,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="681" spans="1:9">
+    <row r="681" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A681" s="1">
         <v>743</v>
       </c>
@@ -20587,7 +20675,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="682" spans="1:9">
+    <row r="682" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A682" s="1">
         <v>744</v>
       </c>
@@ -20611,7 +20699,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="683" spans="1:9">
+    <row r="683" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A683" s="1">
         <v>745</v>
       </c>
@@ -20635,7 +20723,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="684" spans="1:9">
+    <row r="684" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A684" s="1">
         <v>746</v>
       </c>
@@ -20659,7 +20747,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="685" spans="1:9">
+    <row r="685" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A685" s="1">
         <v>747</v>
       </c>
@@ -20683,7 +20771,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="686" spans="1:9">
+    <row r="686" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A686" s="1">
         <v>748</v>
       </c>
@@ -20707,7 +20795,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="687" spans="1:9">
+    <row r="687" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A687" s="1">
         <v>749</v>
       </c>
@@ -20731,7 +20819,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="688" spans="1:9">
+    <row r="688" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A688" s="1">
         <v>750</v>
       </c>
@@ -20755,7 +20843,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="689" spans="1:9">
+    <row r="689" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A689" s="1">
         <v>751</v>
       </c>
@@ -20779,7 +20867,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="690" spans="1:9">
+    <row r="690" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A690" s="1">
         <v>752</v>
       </c>
@@ -20803,7 +20891,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="691" spans="1:9" ht="14.4">
+    <row r="691" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A691" s="1">
         <v>753</v>
       </c>
@@ -20830,7 +20918,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="692" spans="1:9">
+    <row r="692" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A692" s="1">
         <v>754</v>
       </c>
@@ -20854,7 +20942,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="693" spans="1:9">
+    <row r="693" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A693" s="1">
         <v>755</v>
       </c>
@@ -20878,7 +20966,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="694" spans="1:9">
+    <row r="694" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A694" s="1">
         <v>756</v>
       </c>
@@ -20902,7 +20990,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="695" spans="1:9">
+    <row r="695" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A695" s="1">
         <v>757</v>
       </c>
@@ -20926,7 +21014,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="696" spans="1:9">
+    <row r="696" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A696" s="1">
         <v>758</v>
       </c>
@@ -20950,7 +21038,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="697" spans="1:9">
+    <row r="697" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A697" s="1">
         <v>759</v>
       </c>
@@ -20974,7 +21062,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="698" spans="1:9">
+    <row r="698" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A698" s="1">
         <v>760</v>
       </c>
@@ -20998,7 +21086,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="699" spans="1:9" ht="14.4">
+    <row r="699" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A699" s="1">
         <v>761</v>
       </c>
@@ -21025,7 +21113,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="700" spans="1:9">
+    <row r="700" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A700" s="1">
         <v>762</v>
       </c>
@@ -21049,7 +21137,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="701" spans="1:9">
+    <row r="701" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A701" s="1">
         <v>763</v>
       </c>
@@ -21073,7 +21161,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="702" spans="1:9">
+    <row r="702" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A702" s="1">
         <v>764</v>
       </c>
@@ -21097,7 +21185,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="703" spans="1:9">
+    <row r="703" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A703" s="1">
         <v>765</v>
       </c>
@@ -21121,7 +21209,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="704" spans="1:9">
+    <row r="704" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A704" s="1">
         <v>766</v>
       </c>
@@ -21145,7 +21233,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="705" spans="1:9">
+    <row r="705" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A705" s="1">
         <v>767</v>
       </c>
@@ -21169,7 +21257,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="706" spans="1:9">
+    <row r="706" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A706" s="1">
         <v>768</v>
       </c>
@@ -21193,7 +21281,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="707" spans="1:9" ht="14.4">
+    <row r="707" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A707" s="1">
         <v>769</v>
       </c>
@@ -21220,7 +21308,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="708" spans="1:9">
+    <row r="708" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A708" s="1">
         <v>770</v>
       </c>
@@ -21244,7 +21332,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="709" spans="1:9">
+    <row r="709" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A709" s="1">
         <v>771</v>
       </c>
@@ -21268,7 +21356,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="710" spans="1:9">
+    <row r="710" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A710" s="1">
         <v>772</v>
       </c>
@@ -21292,7 +21380,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="711" spans="1:9">
+    <row r="711" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A711" s="1">
         <v>773</v>
       </c>
@@ -21316,7 +21404,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="712" spans="1:9">
+    <row r="712" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A712" s="1">
         <v>774</v>
       </c>
@@ -21340,7 +21428,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="713" spans="1:9">
+    <row r="713" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A713" s="1">
         <v>775</v>
       </c>
@@ -21364,7 +21452,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="714" spans="1:9">
+    <row r="714" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A714" s="1">
         <v>776</v>
       </c>
@@ -21388,7 +21476,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="715" spans="1:9" ht="14.4">
+    <row r="715" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A715" s="1">
         <v>777</v>
       </c>
@@ -21415,7 +21503,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="716" spans="1:9">
+    <row r="716" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A716" s="1">
         <v>778</v>
       </c>
@@ -21439,7 +21527,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="717" spans="1:9">
+    <row r="717" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A717" s="1">
         <v>779</v>
       </c>
@@ -21463,7 +21551,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="718" spans="1:9">
+    <row r="718" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A718" s="1">
         <v>780</v>
       </c>
@@ -21487,7 +21575,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="719" spans="1:9">
+    <row r="719" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A719" s="1">
         <v>781</v>
       </c>
@@ -21511,7 +21599,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="720" spans="1:9">
+    <row r="720" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A720" s="1">
         <v>782</v>
       </c>
@@ -21535,7 +21623,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="721" spans="1:9">
+    <row r="721" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A721" s="1">
         <v>783</v>
       </c>
@@ -21559,7 +21647,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="722" spans="1:9">
+    <row r="722" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A722" s="1">
         <v>784</v>
       </c>
@@ -21583,7 +21671,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="723" spans="1:9" ht="14.4">
+    <row r="723" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A723" s="1">
         <v>785</v>
       </c>
@@ -21610,7 +21698,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="724" spans="1:9">
+    <row r="724" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A724" s="1">
         <v>786</v>
       </c>
@@ -21634,7 +21722,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="725" spans="1:9">
+    <row r="725" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A725" s="1">
         <v>787</v>
       </c>
@@ -21658,7 +21746,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="726" spans="1:9">
+    <row r="726" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A726" s="1">
         <v>788</v>
       </c>
@@ -21682,7 +21770,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="727" spans="1:9">
+    <row r="727" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A727" s="1">
         <v>789</v>
       </c>
@@ -21706,7 +21794,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="728" spans="1:9">
+    <row r="728" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A728" s="1">
         <v>790</v>
       </c>
@@ -21730,7 +21818,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="729" spans="1:9">
+    <row r="729" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A729" s="1">
         <v>791</v>
       </c>
@@ -21754,7 +21842,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="730" spans="1:9">
+    <row r="730" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A730" s="1">
         <v>792</v>
       </c>
@@ -21778,7 +21866,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="731" spans="1:9">
+    <row r="731" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A731" s="1">
         <v>793</v>
       </c>
@@ -21802,7 +21890,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="732" spans="1:9">
+    <row r="732" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A732" s="1">
         <v>794</v>
       </c>
@@ -21826,7 +21914,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="733" spans="1:9">
+    <row r="733" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A733" s="1">
         <v>795</v>
       </c>
@@ -21850,7 +21938,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="734" spans="1:9">
+    <row r="734" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A734" s="1">
         <v>796</v>
       </c>
@@ -21874,7 +21962,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="735" spans="1:9">
+    <row r="735" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A735" s="1">
         <v>797</v>
       </c>
@@ -21898,7 +21986,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="736" spans="1:9">
+    <row r="736" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A736" s="1">
         <v>798</v>
       </c>
@@ -21922,7 +22010,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="737" spans="1:9">
+    <row r="737" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A737" s="1">
         <v>799</v>
       </c>
@@ -21946,7 +22034,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="738" spans="1:9">
+    <row r="738" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A738" s="1">
         <v>800</v>
       </c>
@@ -21970,7 +22058,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="739" spans="1:9" ht="14.4">
+    <row r="739" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A739" s="1">
         <v>801</v>
       </c>
@@ -21997,7 +22085,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="740" spans="1:9">
+    <row r="740" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A740" s="1">
         <v>802</v>
       </c>
@@ -22021,7 +22109,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="741" spans="1:9">
+    <row r="741" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A741" s="1">
         <v>803</v>
       </c>
@@ -22045,7 +22133,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="742" spans="1:9">
+    <row r="742" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A742" s="1">
         <v>804</v>
       </c>
@@ -22069,7 +22157,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="743" spans="1:9">
+    <row r="743" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A743" s="1">
         <v>805</v>
       </c>
@@ -22093,7 +22181,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="744" spans="1:9">
+    <row r="744" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A744" s="1">
         <v>806</v>
       </c>
@@ -22117,7 +22205,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="745" spans="1:9">
+    <row r="745" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A745" s="1">
         <v>807</v>
       </c>
@@ -22141,7 +22229,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="746" spans="1:9">
+    <row r="746" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A746" s="1">
         <v>808</v>
       </c>
@@ -22165,7 +22253,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="747" spans="1:9">
+    <row r="747" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A747" s="1">
         <v>809</v>
       </c>
@@ -22189,7 +22277,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="748" spans="1:9">
+    <row r="748" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A748" s="1">
         <v>810</v>
       </c>
@@ -22213,7 +22301,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="749" spans="1:9">
+    <row r="749" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A749" s="1">
         <v>811</v>
       </c>
@@ -22237,7 +22325,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="750" spans="1:9">
+    <row r="750" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A750" s="1">
         <v>812</v>
       </c>
@@ -22261,7 +22349,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="751" spans="1:9">
+    <row r="751" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A751" s="1">
         <v>813</v>
       </c>
@@ -22285,7 +22373,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="752" spans="1:9">
+    <row r="752" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A752" s="1">
         <v>814</v>
       </c>
@@ -22309,7 +22397,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="753" spans="1:9">
+    <row r="753" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A753" s="1">
         <v>815</v>
       </c>
@@ -22333,7 +22421,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="754" spans="1:9">
+    <row r="754" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A754" s="1">
         <v>816</v>
       </c>
@@ -22357,7 +22445,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="755" spans="1:9" ht="14.4">
+    <row r="755" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A755" s="1">
         <v>817</v>
       </c>
@@ -22384,7 +22472,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="756" spans="1:9">
+    <row r="756" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A756" s="1">
         <v>818</v>
       </c>
@@ -22408,7 +22496,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="757" spans="1:9">
+    <row r="757" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A757" s="1">
         <v>819</v>
       </c>
@@ -22432,7 +22520,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="758" spans="1:9">
+    <row r="758" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A758" s="1">
         <v>820</v>
       </c>
@@ -22456,7 +22544,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="759" spans="1:9">
+    <row r="759" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A759" s="1">
         <v>821</v>
       </c>
@@ -22480,7 +22568,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="760" spans="1:9">
+    <row r="760" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A760" s="1">
         <v>822</v>
       </c>
@@ -22504,7 +22592,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="761" spans="1:9">
+    <row r="761" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A761" s="1">
         <v>823</v>
       </c>
@@ -22528,7 +22616,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="762" spans="1:9">
+    <row r="762" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A762" s="1">
         <v>824</v>
       </c>
@@ -22552,7 +22640,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="763" spans="1:9">
+    <row r="763" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A763" s="1">
         <v>825</v>
       </c>
@@ -22576,7 +22664,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="764" spans="1:9">
+    <row r="764" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A764" s="1">
         <v>826</v>
       </c>
@@ -22600,7 +22688,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="765" spans="1:9">
+    <row r="765" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A765" s="1">
         <v>827</v>
       </c>
@@ -22624,7 +22712,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="766" spans="1:9">
+    <row r="766" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A766" s="1">
         <v>828</v>
       </c>
@@ -22648,7 +22736,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="767" spans="1:9">
+    <row r="767" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A767" s="1">
         <v>829</v>
       </c>
@@ -22672,7 +22760,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="768" spans="1:9">
+    <row r="768" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A768" s="1">
         <v>830</v>
       </c>
@@ -22696,7 +22784,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="769" spans="1:9">
+    <row r="769" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A769" s="1">
         <v>831</v>
       </c>
@@ -22720,7 +22808,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="770" spans="1:9">
+    <row r="770" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A770" s="1">
         <v>832</v>
       </c>
@@ -22744,7 +22832,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="771" spans="1:9" ht="14.4">
+    <row r="771" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A771" s="1">
         <v>833</v>
       </c>
@@ -22771,7 +22859,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="772" spans="1:9">
+    <row r="772" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A772" s="1">
         <v>834</v>
       </c>
@@ -22795,7 +22883,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="773" spans="1:9">
+    <row r="773" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A773" s="1">
         <v>835</v>
       </c>
@@ -22819,7 +22907,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="774" spans="1:9">
+    <row r="774" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A774" s="1">
         <v>836</v>
       </c>
@@ -22843,7 +22931,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="775" spans="1:9">
+    <row r="775" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A775" s="1">
         <v>837</v>
       </c>
@@ -22867,7 +22955,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="776" spans="1:9">
+    <row r="776" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A776" s="1">
         <v>838</v>
       </c>
@@ -22891,7 +22979,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="777" spans="1:9">
+    <row r="777" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A777" s="1">
         <v>839</v>
       </c>
@@ -22915,7 +23003,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="778" spans="1:9">
+    <row r="778" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A778" s="1">
         <v>840</v>
       </c>
@@ -22939,7 +23027,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="779" spans="1:9">
+    <row r="779" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A779" s="1">
         <v>841</v>
       </c>
@@ -22963,7 +23051,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="780" spans="1:9">
+    <row r="780" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A780" s="1">
         <v>842</v>
       </c>
@@ -22987,7 +23075,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="781" spans="1:9">
+    <row r="781" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A781" s="1">
         <v>843</v>
       </c>
@@ -23011,7 +23099,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="782" spans="1:9">
+    <row r="782" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A782" s="1">
         <v>844</v>
       </c>
@@ -23035,7 +23123,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="783" spans="1:9">
+    <row r="783" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A783" s="1">
         <v>845</v>
       </c>
@@ -23059,7 +23147,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="784" spans="1:9">
+    <row r="784" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A784" s="1">
         <v>846</v>
       </c>
@@ -23083,7 +23171,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="785" spans="1:9">
+    <row r="785" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A785" s="1">
         <v>847</v>
       </c>
@@ -23107,7 +23195,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="786" spans="1:9">
+    <row r="786" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A786" s="1">
         <v>848</v>
       </c>
@@ -23131,7 +23219,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="787" spans="1:9" ht="14.4">
+    <row r="787" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A787" s="1">
         <v>849</v>
       </c>
@@ -23158,7 +23246,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="788" spans="1:9">
+    <row r="788" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A788" s="1">
         <v>850</v>
       </c>
@@ -23182,7 +23270,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="789" spans="1:9">
+    <row r="789" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A789" s="1">
         <v>851</v>
       </c>
@@ -23206,7 +23294,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="790" spans="1:9">
+    <row r="790" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A790" s="1">
         <v>852</v>
       </c>
@@ -23230,7 +23318,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="791" spans="1:9">
+    <row r="791" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A791" s="1">
         <v>853</v>
       </c>
@@ -23254,7 +23342,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="792" spans="1:9">
+    <row r="792" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A792" s="1">
         <v>854</v>
       </c>
@@ -23278,7 +23366,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="793" spans="1:9">
+    <row r="793" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A793" s="1">
         <v>855</v>
       </c>
@@ -23302,7 +23390,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="794" spans="1:9">
+    <row r="794" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A794" s="1">
         <v>856</v>
       </c>
@@ -23326,7 +23414,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="795" spans="1:9">
+    <row r="795" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A795" s="1">
         <v>857</v>
       </c>
@@ -23350,7 +23438,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="796" spans="1:9">
+    <row r="796" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A796" s="1">
         <v>858</v>
       </c>
@@ -23374,7 +23462,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="797" spans="1:9">
+    <row r="797" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A797" s="1">
         <v>859</v>
       </c>
@@ -23398,7 +23486,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="798" spans="1:9">
+    <row r="798" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A798" s="1">
         <v>860</v>
       </c>
@@ -23422,7 +23510,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="799" spans="1:9">
+    <row r="799" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A799" s="1">
         <v>861</v>
       </c>
@@ -23446,7 +23534,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="800" spans="1:9">
+    <row r="800" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A800" s="1">
         <v>862</v>
       </c>
@@ -23470,7 +23558,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="801" spans="1:9">
+    <row r="801" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A801" s="1">
         <v>863</v>
       </c>
@@ -23494,7 +23582,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="802" spans="1:9">
+    <row r="802" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A802" s="1">
         <v>864</v>
       </c>
@@ -23518,7 +23606,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="803" spans="1:9" ht="14.4">
+    <row r="803" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A803" s="1">
         <v>865</v>
       </c>
@@ -23545,7 +23633,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="804" spans="1:9">
+    <row r="804" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A804" s="1">
         <v>866</v>
       </c>
@@ -23569,7 +23657,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="805" spans="1:9">
+    <row r="805" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A805" s="1">
         <v>867</v>
       </c>
@@ -23593,7 +23681,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="806" spans="1:9">
+    <row r="806" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A806" s="1">
         <v>868</v>
       </c>
@@ -23617,7 +23705,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="807" spans="1:9">
+    <row r="807" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A807" s="1">
         <v>869</v>
       </c>
@@ -23641,7 +23729,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="808" spans="1:9">
+    <row r="808" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A808" s="1">
         <v>870</v>
       </c>
@@ -23665,7 +23753,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="809" spans="1:9">
+    <row r="809" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A809" s="1">
         <v>871</v>
       </c>
@@ -23689,7 +23777,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="810" spans="1:9">
+    <row r="810" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A810" s="1">
         <v>872</v>
       </c>
@@ -23713,7 +23801,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="811" spans="1:9">
+    <row r="811" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A811" s="1">
         <v>873</v>
       </c>
@@ -23737,7 +23825,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="812" spans="1:9">
+    <row r="812" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A812" s="1">
         <v>874</v>
       </c>
@@ -23761,7 +23849,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="813" spans="1:9">
+    <row r="813" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A813" s="1">
         <v>875</v>
       </c>
@@ -23785,7 +23873,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="814" spans="1:9">
+    <row r="814" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A814" s="1">
         <v>876</v>
       </c>
@@ -23809,7 +23897,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="815" spans="1:9">
+    <row r="815" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A815" s="1">
         <v>877</v>
       </c>
@@ -23833,7 +23921,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="816" spans="1:9">
+    <row r="816" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A816" s="1">
         <v>878</v>
       </c>
@@ -23857,7 +23945,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="817" spans="1:9">
+    <row r="817" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A817" s="1">
         <v>879</v>
       </c>
@@ -23881,7 +23969,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="818" spans="1:9">
+    <row r="818" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A818" s="1">
         <v>880</v>
       </c>
@@ -23905,7 +23993,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="819" spans="1:9" ht="14.4">
+    <row r="819" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A819" s="1">
         <v>881</v>
       </c>
@@ -23932,7 +24020,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="820" spans="1:9">
+    <row r="820" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A820" s="1">
         <v>882</v>
       </c>
@@ -23956,7 +24044,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="821" spans="1:9">
+    <row r="821" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A821" s="1">
         <v>883</v>
       </c>
@@ -23980,7 +24068,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="822" spans="1:9">
+    <row r="822" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A822" s="1">
         <v>884</v>
       </c>
@@ -24004,7 +24092,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="823" spans="1:9">
+    <row r="823" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A823" s="1">
         <v>885</v>
       </c>
@@ -24028,7 +24116,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="824" spans="1:9">
+    <row r="824" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A824" s="1">
         <v>886</v>
       </c>
@@ -24052,7 +24140,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="825" spans="1:9">
+    <row r="825" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A825" s="1">
         <v>887</v>
       </c>
@@ -24076,7 +24164,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="826" spans="1:9">
+    <row r="826" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A826" s="1">
         <v>888</v>
       </c>
@@ -24100,7 +24188,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="827" spans="1:9">
+    <row r="827" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A827" s="1">
         <v>889</v>
       </c>
@@ -24124,7 +24212,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="828" spans="1:9">
+    <row r="828" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A828" s="1">
         <v>890</v>
       </c>
@@ -24148,7 +24236,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="829" spans="1:9">
+    <row r="829" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A829" s="1">
         <v>891</v>
       </c>
@@ -24172,7 +24260,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="830" spans="1:9">
+    <row r="830" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A830" s="1">
         <v>892</v>
       </c>
@@ -24196,7 +24284,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="831" spans="1:9">
+    <row r="831" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A831" s="1">
         <v>893</v>
       </c>
@@ -24220,7 +24308,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="832" spans="1:9">
+    <row r="832" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A832" s="1">
         <v>894</v>
       </c>
@@ -24244,7 +24332,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="833" spans="1:9">
+    <row r="833" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A833" s="1">
         <v>895</v>
       </c>
@@ -24268,7 +24356,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="834" spans="1:9">
+    <row r="834" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A834" s="1">
         <v>896</v>
       </c>
@@ -24292,7 +24380,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="835" spans="1:9" ht="14.4">
+    <row r="835" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A835" s="1">
         <v>897</v>
       </c>
@@ -24319,7 +24407,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="836" spans="1:9">
+    <row r="836" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A836" s="1">
         <v>898</v>
       </c>
@@ -24343,7 +24431,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="837" spans="1:9">
+    <row r="837" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A837" s="1">
         <v>899</v>
       </c>
@@ -24367,7 +24455,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="838" spans="1:9">
+    <row r="838" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A838" s="1">
         <v>900</v>
       </c>
@@ -24391,7 +24479,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="839" spans="1:9">
+    <row r="839" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A839" s="1">
         <v>901</v>
       </c>
@@ -24415,7 +24503,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="840" spans="1:9">
+    <row r="840" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A840" s="1">
         <v>902</v>
       </c>
@@ -24439,7 +24527,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="841" spans="1:9">
+    <row r="841" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A841" s="1">
         <v>903</v>
       </c>
@@ -24463,7 +24551,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="842" spans="1:9">
+    <row r="842" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A842" s="1">
         <v>904</v>
       </c>
@@ -24487,7 +24575,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="843" spans="1:9">
+    <row r="843" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A843" s="1">
         <v>905</v>
       </c>
@@ -24511,7 +24599,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="844" spans="1:9">
+    <row r="844" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A844" s="1">
         <v>906</v>
       </c>
@@ -24535,7 +24623,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="845" spans="1:9">
+    <row r="845" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A845" s="1">
         <v>907</v>
       </c>
@@ -24559,7 +24647,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="846" spans="1:9">
+    <row r="846" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A846" s="1">
         <v>908</v>
       </c>
@@ -24583,7 +24671,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="847" spans="1:9">
+    <row r="847" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A847" s="1">
         <v>909</v>
       </c>
@@ -24607,7 +24695,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="848" spans="1:9">
+    <row r="848" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A848" s="1">
         <v>910</v>
       </c>
@@ -24631,7 +24719,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="849" spans="1:9">
+    <row r="849" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A849" s="1">
         <v>911</v>
       </c>
@@ -24655,7 +24743,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="850" spans="1:9">
+    <row r="850" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A850" s="1">
         <v>912</v>
       </c>
@@ -24679,7 +24767,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="851" spans="1:9" ht="14.4">
+    <row r="851" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A851" s="1">
         <v>913</v>
       </c>
@@ -24706,7 +24794,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="852" spans="1:9">
+    <row r="852" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A852" s="1">
         <v>914</v>
       </c>
@@ -24730,7 +24818,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="853" spans="1:9">
+    <row r="853" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A853" s="1">
         <v>915</v>
       </c>
@@ -24754,7 +24842,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="854" spans="1:9">
+    <row r="854" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A854" s="1">
         <v>916</v>
       </c>
@@ -24778,7 +24866,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="855" spans="1:9">
+    <row r="855" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A855" s="1">
         <v>917</v>
       </c>
@@ -24802,7 +24890,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="856" spans="1:9">
+    <row r="856" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A856" s="1">
         <v>918</v>
       </c>
@@ -24826,7 +24914,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="857" spans="1:9">
+    <row r="857" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A857" s="1">
         <v>919</v>
       </c>
@@ -24850,7 +24938,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="858" spans="1:9">
+    <row r="858" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A858" s="1">
         <v>920</v>
       </c>
@@ -24874,7 +24962,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="859" spans="1:9">
+    <row r="859" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A859" s="1">
         <v>921</v>
       </c>
@@ -24898,7 +24986,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="860" spans="1:9">
+    <row r="860" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A860" s="1">
         <v>922</v>
       </c>
@@ -24922,7 +25010,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="861" spans="1:9">
+    <row r="861" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A861" s="1">
         <v>923</v>
       </c>
@@ -24946,7 +25034,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="862" spans="1:9">
+    <row r="862" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A862" s="1">
         <v>924</v>
       </c>
@@ -24970,7 +25058,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="863" spans="1:9">
+    <row r="863" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A863" s="1">
         <v>925</v>
       </c>
@@ -24994,7 +25082,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="864" spans="1:9">
+    <row r="864" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A864" s="1">
         <v>926</v>
       </c>
@@ -25018,7 +25106,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="865" spans="1:9">
+    <row r="865" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A865" s="1">
         <v>927</v>
       </c>
@@ -25042,7 +25130,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="866" spans="1:9">
+    <row r="866" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A866" s="1">
         <v>928</v>
       </c>
@@ -25066,7 +25154,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="867" spans="1:9">
+    <row r="867" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A867" s="1">
         <v>929</v>
       </c>
@@ -25093,7 +25181,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="868" spans="1:9">
+    <row r="868" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A868" s="1">
         <v>930</v>
       </c>
@@ -25117,7 +25205,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="869" spans="1:9">
+    <row r="869" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A869" s="1">
         <v>931</v>
       </c>
@@ -25141,7 +25229,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="870" spans="1:9">
+    <row r="870" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A870" s="1">
         <v>932</v>
       </c>
@@ -25165,7 +25253,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="871" spans="1:9">
+    <row r="871" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A871" s="1">
         <v>933</v>
       </c>
@@ -25189,7 +25277,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="872" spans="1:9">
+    <row r="872" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A872" s="1">
         <v>934</v>
       </c>
@@ -25213,7 +25301,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="873" spans="1:9">
+    <row r="873" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A873" s="1">
         <v>935</v>
       </c>
@@ -25237,7 +25325,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="874" spans="1:9">
+    <row r="874" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A874" s="1">
         <v>936</v>
       </c>
@@ -25261,7 +25349,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="875" spans="1:9">
+    <row r="875" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A875" s="1">
         <v>937</v>
       </c>
@@ -25285,7 +25373,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="876" spans="1:9">
+    <row r="876" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A876" s="1">
         <v>938</v>
       </c>
@@ -25309,7 +25397,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="877" spans="1:9">
+    <row r="877" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A877" s="1">
         <v>939</v>
       </c>
@@ -25333,7 +25421,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="878" spans="1:9">
+    <row r="878" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A878" s="1">
         <v>940</v>
       </c>
@@ -25357,7 +25445,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="879" spans="1:9">
+    <row r="879" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A879" s="1">
         <v>941</v>
       </c>
@@ -25381,7 +25469,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="880" spans="1:9">
+    <row r="880" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A880" s="1">
         <v>942</v>
       </c>
@@ -25405,7 +25493,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="881" spans="1:9">
+    <row r="881" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A881" s="1">
         <v>943</v>
       </c>
@@ -25429,7 +25517,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="882" spans="1:9">
+    <row r="882" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A882" s="1">
         <v>944</v>
       </c>
@@ -25453,7 +25541,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="883" spans="1:9">
+    <row r="883" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A883" s="1">
         <v>945</v>
       </c>
@@ -25480,7 +25568,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="884" spans="1:9">
+    <row r="884" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A884" s="1">
         <v>946</v>
       </c>
@@ -25504,7 +25592,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="885" spans="1:9">
+    <row r="885" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A885" s="1">
         <v>947</v>
       </c>
@@ -25528,7 +25616,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="886" spans="1:9">
+    <row r="886" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A886" s="1">
         <v>948</v>
       </c>
@@ -25552,7 +25640,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="887" spans="1:9">
+    <row r="887" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A887" s="1">
         <v>949</v>
       </c>
@@ -25576,7 +25664,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="888" spans="1:9">
+    <row r="888" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A888" s="1">
         <v>950</v>
       </c>
@@ -25600,7 +25688,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="889" spans="1:9">
+    <row r="889" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A889" s="1">
         <v>951</v>
       </c>
@@ -25624,7 +25712,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="890" spans="1:9">
+    <row r="890" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A890" s="1">
         <v>952</v>
       </c>
@@ -25648,7 +25736,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="891" spans="1:9">
+    <row r="891" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A891" s="1">
         <v>953</v>
       </c>
@@ -25672,7 +25760,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="892" spans="1:9">
+    <row r="892" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A892" s="1">
         <v>954</v>
       </c>
@@ -25696,7 +25784,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="893" spans="1:9">
+    <row r="893" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A893" s="1">
         <v>955</v>
       </c>
@@ -25720,7 +25808,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="894" spans="1:9">
+    <row r="894" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A894" s="1">
         <v>956</v>
       </c>
@@ -25744,7 +25832,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="895" spans="1:9">
+    <row r="895" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A895" s="1">
         <v>957</v>
       </c>
@@ -25768,7 +25856,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="896" spans="1:9">
+    <row r="896" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A896" s="1">
         <v>958</v>
       </c>
@@ -25792,7 +25880,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="897" spans="1:8">
+    <row r="897" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A897" s="1">
         <v>959</v>
       </c>
@@ -25816,7 +25904,7 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="898" spans="1:8">
+    <row r="898" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A898" s="1">
         <v>960</v>
       </c>
@@ -25856,31 +25944,101 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3951076A-BA52-4960-B879-802BD7215810}">
+  <dimension ref="A1:A13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>507</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B89C0430-D126-4193-BAE2-FD0F1DC784E3}">
   <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.09765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="51.8984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.8984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.09765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="42.69921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.8984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="14" t="s">
         <v>397</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="E1" s="11" t="s">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="E1" s="14" t="s">
         <v>397</v>
       </c>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-    </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1">
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+    </row>
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>10</v>
       </c>
@@ -25900,7 +26058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="14.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>398</v>
       </c>
@@ -25920,7 +26078,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="14.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>399</v>
       </c>
@@ -25940,7 +26098,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="14.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>400</v>
       </c>
@@ -25960,7 +26118,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="14.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>401</v>
       </c>
@@ -25980,7 +26138,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="14.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>402</v>
       </c>
@@ -26000,7 +26158,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="14.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>403</v>
       </c>
@@ -26020,7 +26178,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="14.4">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>404</v>
       </c>
@@ -26040,7 +26198,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="14.4">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>405</v>
       </c>
@@ -26060,7 +26218,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="14.4">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>406</v>
       </c>
@@ -26078,7 +26236,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="14.4">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>407</v>
       </c>
@@ -26096,7 +26254,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="14.4">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>408</v>
       </c>
@@ -26114,7 +26272,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="14.4">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>409</v>
       </c>
@@ -26132,7 +26290,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="14.4">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>410</v>
       </c>
@@ -26150,7 +26308,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="14.4">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>411</v>
       </c>
@@ -26168,7 +26326,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="14.4">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>412</v>
       </c>
@@ -26186,7 +26344,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="14.4">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>413</v>
       </c>
@@ -26202,7 +26360,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="14.4">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>414</v>
       </c>
@@ -26218,7 +26376,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="14.4">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>415</v>
       </c>
@@ -26236,7 +26394,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="14.4">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>416</v>
       </c>
@@ -26254,7 +26412,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="14.4">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>417</v>
       </c>
@@ -26272,7 +26430,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="14.4">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>418</v>
       </c>
@@ -26288,7 +26446,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="14.4">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>419</v>
       </c>
@@ -26304,11 +26462,11 @@
         <v>52</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="43.2">
+    <row r="25" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>420</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="11" t="s">
         <v>481</v>
       </c>
       <c r="C25" s="9"/>
@@ -26320,7 +26478,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="14.4">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>421</v>
       </c>
@@ -26334,7 +26492,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="14.4">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>422</v>
       </c>
@@ -26348,7 +26506,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="14.4">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>423</v>
       </c>
@@ -26362,7 +26520,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="14.4">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
         <v>424</v>
       </c>
@@ -26376,7 +26534,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="14.4">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>425</v>
       </c>
@@ -26390,7 +26548,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="14.4">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>426</v>
       </c>
@@ -26404,7 +26562,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="14.4">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>427</v>
       </c>
@@ -26418,7 +26576,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="14.4">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>428</v>
       </c>
@@ -26432,7 +26590,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="14.4">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>429</v>
       </c>
@@ -26446,7 +26604,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="14.4">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>430</v>
       </c>
@@ -26474,19 +26632,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA144AF3-4E40-4942-9302-D3CD0ABECF4D}">
   <dimension ref="A1:E54"/>
-  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.44140625" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="35" style="4" customWidth="1"/>
-    <col min="5" max="16384" width="9.09765625" style="4"/>
+    <col min="5" max="16384" width="9.109375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>373</v>
       </c>
@@ -26503,7 +26661,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -26520,7 +26678,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -26537,7 +26695,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -26554,7 +26712,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -26571,7 +26729,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -26588,7 +26746,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -26605,7 +26763,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -26622,7 +26780,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -26639,7 +26797,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -26656,7 +26814,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -26673,7 +26831,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -26690,7 +26848,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -26704,7 +26862,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -26715,7 +26873,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -26729,7 +26887,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -26740,7 +26898,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -26754,7 +26912,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -26771,7 +26929,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -26788,7 +26946,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -26805,7 +26963,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -26822,7 +26980,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -26836,7 +26994,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -26850,7 +27008,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -26864,7 +27022,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -26878,7 +27036,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -26892,7 +27050,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -26900,7 +27058,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -26908,7 +27066,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -26916,7 +27074,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -26924,7 +27082,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -26932,7 +27090,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -26940,7 +27098,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -26948,7 +27106,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -26956,7 +27114,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -26964,7 +27122,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -26975,7 +27133,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -26983,7 +27141,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -26991,7 +27149,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -26999,7 +27157,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -27007,7 +27165,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -27015,7 +27173,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -27023,7 +27181,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -27031,7 +27189,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>43</v>
       </c>
@@ -27039,7 +27197,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -27047,7 +27205,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>45</v>
       </c>
@@ -27055,42 +27213,42 @@
         <v>299</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B47" s="4" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B48" s="4" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="49" spans="2:2">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B49" s="4" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="50" spans="2:2">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="51" spans="2:2">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="52" spans="2:2">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B52" s="4" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="53" spans="2:2">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="54" spans="2:2">
+    <row r="54" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="s">
         <v>291</v>
       </c>
@@ -27105,16 +27263,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A074D264-9A9F-4C97-8435-D1191E30740B}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.09765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>488</v>
       </c>
@@ -27122,7 +27280,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>247</v>
       </c>
@@ -27133,18 +27291,18 @@
         <v>490</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>491</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="13" t="s">
         <v>492</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="13" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>250</v>
       </c>
@@ -27155,7 +27313,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>251</v>
       </c>
@@ -27166,18 +27324,18 @@
         <v>494</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>484</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="13" t="s">
         <v>495</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="13" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>255</v>
       </c>
@@ -27188,7 +27346,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>257</v>
       </c>
@@ -27199,7 +27357,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>265</v>
       </c>
@@ -27210,7 +27368,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>352</v>
       </c>
@@ -27221,36 +27379,36 @@
         <v>499</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>485</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="13" t="s">
         <v>500</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="13" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>486</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="13" t="s">
         <v>501</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="13" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>487</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="13" t="s">
         <v>502</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="13" t="s">
         <v>502</v>
       </c>
     </row>
